--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -662,49 +662,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 65637억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 65636억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 64655억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 65475억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 64668억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 64648억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 63916억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 63896억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 63012억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 62993억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 62370억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 62351억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 61037억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 61017억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 59250억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 59230억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -788,7 +788,7 @@
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
@@ -848,7 +848,7 @@
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.4% + 실측 차이 +1.7%p</t>
+자회사 OPM 12.6% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
@@ -914,37 +914,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 187433억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 187689억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 198430억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 198684억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 209358억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 209611억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 220200억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 220450억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 222453억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 222702억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 233456억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 233703억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1889,49 +1889,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 65637억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 65636억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 64655억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 65475억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 64668억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 64648억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 63916억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 63896억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 63012억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 62993억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 62370억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 62351억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 61037억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 61017억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 59250억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 59230억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2135,28 +2135,28 @@
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
+        <t>추정: 매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="AH9" authorId="0" shapeId="0">
+      <text>
         <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="AH9" authorId="0" shapeId="0">
+    <comment ref="AI9" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="AI9" authorId="0" shapeId="0">
+    <comment ref="AK9" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="AK9" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
-[ratio]</t>
-      </text>
-    </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)
@@ -2290,28 +2290,28 @@
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
+        <t>추정: 자회사 OPM 12.6% + 실측 차이 +1.7%p
+[yoy]</t>
+      </text>
+    </comment>
+    <comment ref="AH10" authorId="0" shapeId="0">
+      <text>
         <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="AH10" authorId="0" shapeId="0">
+    <comment ref="AI10" authorId="0" shapeId="0">
       <text>
         <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="AI10" authorId="0" shapeId="0">
+    <comment ref="AK10" authorId="0" shapeId="0">
       <text>
         <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="AK10" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
-[yoy]</t>
-      </text>
-    </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
         <t>추정: 자회사 OPM 12.6% + 실측 차이 +1.7%p
@@ -2356,37 +2356,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 187433억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 187689억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 198430억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 198684억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 209358억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 209611억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 220200억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 220450억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 222453억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 222702억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 233456억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 233703억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4630,7 +4630,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.8, "op_wape_pct": 34.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "subsidiary_yard_scaled", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 74060.36, "rev_act": 75814.36, "op_pred": 8360.92, "op_act": 10537.75}, {"q": "2025Q4", "rev_pred": 74060.36, "rev_act": 81516.57, "op_pred": 8360.92, "op_act": 10379.19}, {"q": "2026Q1", "rev_pred": 73789.71, "rev_act": 81408.9, "op_pred": 8330.35, "op_act": 13559.7}, {"q": "2026Q2", "rev_pred": 73925.02, "rev_act": 89270.46, "op_pred": 8345.64, "op_act": 16451.46}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.8, "op_wape_pct": 34.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "subsidiary_yard_scaled", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 74060.53, "rev_act": 75814.36, "op_pred": 8350.88, "op_act": 10537.75}, {"q": "2025Q4", "rev_pred": 74060.53, "rev_act": 81516.57, "op_pred": 8350.88, "op_act": 10379.19}, {"q": "2026Q1", "rev_pred": 73789.18, "rev_act": 81408.9, "op_pred": 8320.27, "op_act": 13559.7}, {"q": "2026Q2", "rev_pred": 73924.83, "rev_act": 89270.46, "op_pred": 8335.59, "op_act": 16451.46}]}</t>
         </is>
       </c>
     </row>
@@ -8531,36 +8531,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.226446</v>
+        <v>0.226443</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.143398</v>
+        <v>0.143391</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.136671</v>
+        <v>0.136656</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.021065</v>
+        <v>0.034015</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>-0.019505</v>
+        <v>-0.019802</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.033237</v>
+        <v>-0.033529</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.039992</v>
+        <v>-0.04028</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035342</v>
+        <v>-0.047724</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.056145</v>
+        <v>-0.056162</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.07299700000000001</v>
+        <v>-0.073019</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -8832,20 +8832,20 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.143933</v>
+        <v>0.143932</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.143233</v>
+        <v>0.143232</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.143233</v>
+        <v>0.143232</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.140733</v>
+        <v>0.142433</v>
       </c>
       <c r="AH23" s="24" t="n">
         <v>0.140533</v>
@@ -8861,7 +8861,7 @@
         <v>0.140433</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.142632</v>
+        <v>0.142633</v>
       </c>
       <c r="AM23" s="24" t="n">
         <v>0.146333</v>
@@ -8970,7 +8970,7 @@
         <v>-0.140456</v>
       </c>
       <c r="AG24" s="24" t="n">
-        <v>-0.236571</v>
+        <v>-0.227347</v>
       </c>
       <c r="AH24" s="24" t="n">
         <v>-0.023628</v>
@@ -8983,7 +8983,7 @@
         <v>-0.019553</v>
       </c>
       <c r="AL24" s="24" t="n">
-        <v>0.013504</v>
+        <v>0.001404</v>
       </c>
       <c r="AM24" s="24" t="n">
         <v>0.041281</v>
@@ -9122,26 +9122,26 @@
         <v>900.9</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>915.86</v>
+        <v>917.52</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>987.37</v>
+        <v>989.02</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>1058.43</v>
+        <v>1060.07</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>1128.93</v>
+        <v>1130.56</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>1143.58</v>
+        <v>1145.2</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>1215.14</v>
+        <v>1216.74</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -9726,7 +9726,7 @@
         <v/>
       </c>
       <c r="AC29" s="24" t="n">
-        <v>0.760027</v>
+        <v>0.760028</v>
       </c>
       <c r="AD29" s="24" t="n">
         <v>0.760028</v>
@@ -9736,13 +9736,13 @@
         <v/>
       </c>
       <c r="AF29" s="24" t="n">
-        <v>0.760028</v>
+        <v>0.760027</v>
       </c>
       <c r="AG29" s="24" t="n">
         <v>0.760028</v>
       </c>
       <c r="AH29" s="24" t="n">
-        <v>0.760027</v>
+        <v>0.760028</v>
       </c>
       <c r="AI29" s="24" t="n">
         <v>0.760028</v>
@@ -9752,13 +9752,13 @@
         <v/>
       </c>
       <c r="AK29" s="24" t="n">
-        <v>0.760027</v>
+        <v>0.760028</v>
       </c>
       <c r="AL29" s="24" t="n">
         <v>0.760028</v>
       </c>
       <c r="AM29" s="24" t="n">
-        <v>0.760028</v>
+        <v>0.760027</v>
       </c>
       <c r="AN29" s="24" t="n">
         <v>0.760027</v>
@@ -9991,33 +9991,33 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.0061</v>
+        <v>-0.0039</v>
       </c>
       <c r="AD31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>8697.9</v>
+        <v>8697.889999999999</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>8697.9</v>
+        <v>8697.889999999999</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0</v>
@@ -10122,14 +10122,14 @@
         <v>-0.0046</v>
       </c>
       <c r="AD32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>8697.91</v>
+        <v>8697.9</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
@@ -10139,16 +10139,16 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>8697.91</v>
+        <v>8697.9</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -10378,33 +10378,33 @@
         <v>0.093933</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.086113</v>
+        <v>0.08611199999999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.07915800000000001</v>
+        <v>0.07915700000000001</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.014956</v>
+        <v>0.016621</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.070456</v>
+        <v>0.07033</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.065404</v>
+        <v>0.065294</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.060904</v>
+        <v>0.060808</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.011931</v>
+        <v>0.011906</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.057577</v>
+        <v>0.057492</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.053562</v>
+        <v>0.053487</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -10506,33 +10506,33 @@
         <v>0.07446999999999999</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.069507</v>
+        <v>0.069506</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.064885</v>
+        <v>0.064884</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.012423</v>
+        <v>0.013806</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.058673</v>
+        <v>0.058583</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.055072</v>
+        <v>0.054992</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.051785</v>
+        <v>0.051714</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.010233</v>
+        <v>0.010213</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.049463</v>
+        <v>0.049399</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.04637</v>
+        <v>0.046313</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11171,26 +11171,26 @@
         <v>-0.492716</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.208038</v>
+        <v>-0.212766</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.08360099999999999</v>
+        <v>0.07717</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>0.144781</v>
+        <v>0.138047</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>0.160473</v>
+        <v>0.153716</v>
       </c>
       <c r="AL41" s="24" t="n">
+        <v>0.033033</v>
+      </c>
+      <c r="AM41" s="24" t="n">
         <v>0.025373</v>
       </c>
-      <c r="AM41" s="24" t="n">
-        <v>0.019288</v>
-      </c>
       <c r="AN41" s="24" t="n">
-        <v>0.013235</v>
+        <v>0.019231</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -11290,7 +11290,7 @@
         <v>-0.396313</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.329949</v>
+        <v>-0.335025</v>
       </c>
       <c r="AH42" s="24" t="n">
         <v>-0.143836</v>
@@ -11303,10 +11303,10 @@
         <v>-0.122137</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.128788</v>
+        <v>-0.122137</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.112</v>
+        <v>-0.12</v>
       </c>
       <c r="AN42" s="24" t="n">
         <v>-0.116667</v>
@@ -11581,20 +11581,20 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>0.143933</v>
+        <v>0.143932</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.143233</v>
+        <v>0.143232</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.143233</v>
+        <v>0.143232</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.140733</v>
+        <v>0.142433</v>
       </c>
       <c r="AH44" s="24" t="n">
         <v>0.140533</v>
@@ -11610,7 +11610,7 @@
         <v>0.140433</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.142632</v>
+        <v>0.142633</v>
       </c>
       <c r="AM44" s="24" t="n">
         <v>0.146333</v>
@@ -36358,7 +36358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH71"/>
+  <dimension ref="A1:BH72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37178,55 +37178,55 @@
         <v>4.619</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>35.512</v>
+        <v>34.199</v>
       </c>
       <c r="M5" s="26" t="n">
-        <v>61.069</v>
+        <v>58.831</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>67.821</v>
+        <v>65.631</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>68.574</v>
+        <v>66.36</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="S5" s="26" t="n">
-        <v>67.821</v>
+        <v>65.631</v>
       </c>
       <c r="T5" s="26" t="n">
-        <v>68.574</v>
+        <v>66.36</v>
       </c>
       <c r="U5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="V5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="W5" s="26" t="n">
-        <v>68.574</v>
+        <v>66.36</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>68.574</v>
+        <v>66.36</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>69.328</v>
+        <v>67.089</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>37.55</v>
+        <v>65.631</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>19.519</v>
+        <v>23.894</v>
       </c>
       <c r="AC5" s="26" t="n">
         <v>70.495</v>
@@ -37295,19 +37295,19 @@
         <v>18.786</v>
       </c>
       <c r="AY5" s="26" t="n">
-        <v>170.528</v>
+        <v>164.738</v>
       </c>
       <c r="AZ5" s="26" t="n">
-        <v>275.051</v>
+        <v>266.169</v>
       </c>
       <c r="BA5" s="26" t="n">
-        <v>275.051</v>
+        <v>266.169</v>
       </c>
       <c r="BB5" s="26" t="n">
-        <v>275.804</v>
+        <v>266.898</v>
       </c>
       <c r="BC5" s="26" t="n">
-        <v>267.626</v>
+        <v>300.082</v>
       </c>
       <c r="BD5" s="26" t="n">
         <v>1876.968</v>
@@ -37475,67 +37475,70 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>30.842</v>
+        <v>29.528</v>
       </c>
       <c r="M7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>51.403</v>
+        <v>49.213</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="S7" s="26" t="n">
-        <v>51.403</v>
+        <v>49.213</v>
       </c>
       <c r="T7" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="U7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="V7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="W7" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="X7" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="Y7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="Z7" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="AA7" s="26" t="n">
-        <v>21.132</v>
+        <v>49.213</v>
+      </c>
+      <c r="AB7" s="26" t="n">
+        <v>4.375</v>
       </c>
       <c r="AY7" s="26" t="n">
-        <v>135.932</v>
+        <v>130.142</v>
       </c>
       <c r="AZ7" s="26" t="n">
-        <v>208.467</v>
+        <v>199.587</v>
       </c>
       <c r="BA7" s="26" t="n">
-        <v>208.467</v>
+        <v>199.587</v>
       </c>
       <c r="BB7" s="26" t="n">
-        <v>209.038</v>
+        <v>200.134</v>
       </c>
       <c r="BC7" s="26" t="n">
-        <v>21.132</v>
+        <v>53.588</v>
       </c>
     </row>
     <row r="8">
@@ -37997,52 +38000,55 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>30.842</v>
+        <v>29.528</v>
       </c>
       <c r="M13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="O13" s="26" t="n">
-        <v>51.403</v>
+        <v>49.213</v>
       </c>
       <c r="P13" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="Q13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="S13" s="26" t="n">
-        <v>51.403</v>
+        <v>49.213</v>
       </c>
       <c r="T13" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="U13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="V13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="W13" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>51.974</v>
+        <v>49.76</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>52.545</v>
+        <v>50.307</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>21.132</v>
+        <v>49.213</v>
+      </c>
+      <c r="AB13" s="26" t="n">
+        <v>4.375</v>
       </c>
       <c r="AD13" s="26" t="n">
         <v>6.232</v>
@@ -38084,19 +38090,19 @@
         <v>22.702</v>
       </c>
       <c r="AY13" s="26" t="n">
-        <v>135.932</v>
+        <v>130.142</v>
       </c>
       <c r="AZ13" s="26" t="n">
-        <v>208.467</v>
+        <v>199.587</v>
       </c>
       <c r="BA13" s="26" t="n">
-        <v>208.467</v>
+        <v>199.587</v>
       </c>
       <c r="BB13" s="26" t="n">
-        <v>209.038</v>
+        <v>200.134</v>
       </c>
       <c r="BC13" s="26" t="n">
-        <v>27.364</v>
+        <v>59.82</v>
       </c>
       <c r="BD13" s="26" t="n">
         <v>162.476</v>
@@ -38135,70 +38141,61 @@
         <v>372.155</v>
       </c>
       <c r="AG14" s="26" t="n">
-        <v>465.569</v>
+        <v>443.138</v>
       </c>
       <c r="AH14" s="26" t="n">
-        <v>468.001</v>
+        <v>443.138</v>
       </c>
       <c r="AI14" s="26" t="n">
-        <v>457.827</v>
+        <v>433.504</v>
       </c>
       <c r="AJ14" s="26" t="n">
-        <v>462.914</v>
+        <v>438.321</v>
       </c>
       <c r="AK14" s="26" t="n">
-        <v>468.001</v>
+        <v>443.138</v>
       </c>
       <c r="AL14" s="26" t="n">
-        <v>468.001</v>
+        <v>443.138</v>
       </c>
       <c r="AM14" s="26" t="n">
-        <v>462.914</v>
+        <v>438.321</v>
       </c>
       <c r="AN14" s="26" t="n">
-        <v>458.77</v>
+        <v>434.177</v>
       </c>
       <c r="AO14" s="26" t="n">
-        <v>429.886</v>
+        <v>405.023</v>
       </c>
       <c r="AP14" s="26" t="n">
-        <v>408.195</v>
+        <v>383.332</v>
       </c>
       <c r="AQ14" s="26" t="n">
-        <v>315.144</v>
+        <v>290.821</v>
       </c>
       <c r="AR14" s="26" t="n">
-        <v>209.093</v>
+        <v>184.5</v>
       </c>
       <c r="AS14" s="26" t="n">
-        <v>138.818</v>
+        <v>113.955</v>
       </c>
       <c r="AT14" s="26" t="n">
-        <v>86.67100000000001</v>
-      </c>
-      <c r="AU14" s="26" t="n">
-        <v>24.323</v>
-      </c>
-      <c r="AV14" s="26" t="n">
-        <v>16.485</v>
+        <v>61.808</v>
       </c>
       <c r="BC14" s="26" t="n">
         <v>158.284</v>
       </c>
       <c r="BD14" s="26" t="n">
-        <v>1525.708</v>
+        <v>1478.414</v>
       </c>
       <c r="BE14" s="26" t="n">
-        <v>1856.743</v>
+        <v>1758.101</v>
       </c>
       <c r="BF14" s="26" t="n">
-        <v>1759.765</v>
+        <v>1660.853</v>
       </c>
       <c r="BG14" s="26" t="n">
-        <v>749.726</v>
-      </c>
-      <c r="BH14" s="26" t="n">
-        <v>40.808</v>
+        <v>651.0839999999999</v>
       </c>
     </row>
     <row r="15">
@@ -38222,58 +38219,70 @@
         <v>35.138</v>
       </c>
       <c r="AG15" s="26" t="n">
-        <v>35.524</v>
+        <v>57.955</v>
       </c>
       <c r="AH15" s="26" t="n">
-        <v>35.524</v>
+        <v>60.387</v>
       </c>
       <c r="AI15" s="26" t="n">
-        <v>34.752</v>
+        <v>59.074</v>
       </c>
       <c r="AJ15" s="26" t="n">
-        <v>35.138</v>
+        <v>59.731</v>
       </c>
       <c r="AK15" s="26" t="n">
-        <v>35.524</v>
+        <v>60.387</v>
       </c>
       <c r="AL15" s="26" t="n">
-        <v>35.524</v>
+        <v>60.387</v>
       </c>
       <c r="AM15" s="26" t="n">
-        <v>35.138</v>
+        <v>59.731</v>
       </c>
       <c r="AN15" s="26" t="n">
-        <v>35.138</v>
+        <v>59.731</v>
       </c>
       <c r="AO15" s="26" t="n">
-        <v>35.524</v>
+        <v>60.387</v>
       </c>
       <c r="AP15" s="26" t="n">
-        <v>35.524</v>
+        <v>60.387</v>
       </c>
       <c r="AQ15" s="26" t="n">
-        <v>34.752</v>
+        <v>59.074</v>
       </c>
       <c r="AR15" s="26" t="n">
-        <v>35.138</v>
+        <v>59.731</v>
       </c>
       <c r="AS15" s="26" t="n">
-        <v>16.99</v>
+        <v>41.853</v>
+      </c>
+      <c r="AT15" s="26" t="n">
+        <v>24.863</v>
+      </c>
+      <c r="AU15" s="26" t="n">
+        <v>24.323</v>
+      </c>
+      <c r="AV15" s="26" t="n">
+        <v>16.485</v>
       </c>
       <c r="BC15" s="26" t="n">
         <v>16.217</v>
       </c>
       <c r="BD15" s="26" t="n">
-        <v>140.938</v>
+        <v>188.232</v>
       </c>
       <c r="BE15" s="26" t="n">
-        <v>140.938</v>
+        <v>239.579</v>
       </c>
       <c r="BF15" s="26" t="n">
-        <v>141.324</v>
+        <v>240.236</v>
       </c>
       <c r="BG15" s="26" t="n">
-        <v>86.88</v>
+        <v>185.521</v>
+      </c>
+      <c r="BH15" s="26" t="n">
+        <v>40.808</v>
       </c>
     </row>
     <row r="16">
@@ -38453,55 +38462,55 @@
         <v>1193.96</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>1130.94</v>
+        <v>1131.31</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>1129.41</v>
+        <v>1129.71</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="R17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1133.04</v>
+        <v>1133.43</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1142.43</v>
+        <v>1133.43</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1198.12</v>
+        <v>1184.07</v>
       </c>
       <c r="AC17" s="13" t="n">
         <v>1315.33</v>
@@ -38741,55 +38750,55 @@
         <v>1170.27</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1128</v>
+        <v>1128.26</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>1138.56</v>
+        <v>1138.77</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>1148.18</v>
+        <v>1148.45</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>1154.86</v>
+        <v>1155.13</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>1171.76</v>
+        <v>1172.03</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>1195.71</v>
+        <v>1195.98</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>1201.16</v>
+        <v>1201.44</v>
       </c>
       <c r="S19" s="13" t="n">
-        <v>1176.21</v>
+        <v>1176.49</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>1187.84</v>
+        <v>1188.11</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>1187.21</v>
+        <v>1187.49</v>
       </c>
       <c r="V19" s="13" t="n">
-        <v>1189.73</v>
+        <v>1190</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>1192.17</v>
+        <v>1192.44</v>
       </c>
       <c r="X19" s="13" t="n">
-        <v>1204.51</v>
+        <v>1204.78</v>
       </c>
       <c r="Y19" s="13" t="n">
-        <v>1199.99</v>
+        <v>1200.27</v>
       </c>
       <c r="Z19" s="13" t="n">
-        <v>1212.02</v>
+        <v>1212.29</v>
       </c>
       <c r="AA19" s="13" t="n">
-        <v>1235.38</v>
+        <v>1229.08</v>
       </c>
       <c r="AB19" s="13" t="n">
-        <v>1258.24</v>
+        <v>1248.41</v>
       </c>
       <c r="AC19" s="13" t="n">
         <v>1336.82</v>
@@ -38885,55 +38894,55 @@
         <v>5405.8</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>40058</v>
+        <v>38584.8</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>69530.5</v>
+        <v>66994.60000000001</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>79600.60000000001</v>
+        <v>77048.8</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>78323.39999999999</v>
+        <v>75812.5</v>
       </c>
       <c r="P20" s="18" t="n">
-        <v>80352.10000000001</v>
+        <v>77775.89999999999</v>
       </c>
       <c r="Q20" s="18" t="n">
-        <v>82895.60000000001</v>
+        <v>80237.5</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>83274</v>
+        <v>80603.60000000001</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>79771.5</v>
+        <v>77213.8</v>
       </c>
       <c r="T20" s="18" t="n">
-        <v>81454.8</v>
+        <v>78843</v>
       </c>
       <c r="U20" s="18" t="n">
-        <v>82306.8</v>
+        <v>79667.7</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>82481.3</v>
+        <v>79836.60000000001</v>
       </c>
       <c r="W20" s="18" t="n">
-        <v>81752.10000000001</v>
+        <v>79130.60000000001</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>82598.39999999999</v>
+        <v>79949.7</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>83192.8</v>
+        <v>80525.10000000001</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>84026.39999999999</v>
+        <v>81331.8</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>46388.5</v>
+        <v>80665.89999999999</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>24559.7</v>
+        <v>29829</v>
       </c>
       <c r="AC20" s="18" t="n">
         <v>94238.89999999999</v>
@@ -39002,19 +39011,19 @@
         <v>22348.4</v>
       </c>
       <c r="AY20" s="18" t="n">
-        <v>194594.9</v>
+        <v>188034</v>
       </c>
       <c r="AZ20" s="18" t="n">
-        <v>324845.1</v>
+        <v>314429.5</v>
       </c>
       <c r="BA20" s="18" t="n">
-        <v>326014.4</v>
+        <v>315561.1</v>
       </c>
       <c r="BB20" s="18" t="n">
-        <v>331569.7</v>
+        <v>320937.2</v>
       </c>
       <c r="BC20" s="18" t="n">
-        <v>361705.2</v>
+        <v>401251.9</v>
       </c>
       <c r="BD20" s="18" t="n">
         <v>2704846.8</v>
@@ -39092,7 +39101,7 @@
         <v>0</v>
       </c>
       <c r="AB21" s="21" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="AC21" s="21" t="n">
         <v>0.05</v>
@@ -39107,52 +39116,52 @@
         <v>0.0494</v>
       </c>
       <c r="AG21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0516</v>
       </c>
       <c r="AH21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AI21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AJ21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AK21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AL21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AM21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AN21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0518</v>
       </c>
       <c r="AO21" s="21" t="n">
-        <v>0.0495</v>
+        <v>0.0519</v>
       </c>
       <c r="AP21" s="21" t="n">
-        <v>0.0514</v>
+        <v>0.054</v>
       </c>
       <c r="AQ21" s="21" t="n">
-        <v>0.055</v>
+        <v>0.0584</v>
       </c>
       <c r="AR21" s="21" t="n">
-        <v>0.0572</v>
+        <v>0.0622</v>
       </c>
       <c r="AS21" s="21" t="n">
-        <v>0.0555</v>
+        <v>0.0634</v>
       </c>
       <c r="AT21" s="21" t="n">
-        <v>0.05</v>
+        <v>0.0643</v>
       </c>
       <c r="AU21" s="21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="AV21" s="21" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -41030,7 +41039,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -41168,7 +41177,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -41230,42 +41239,89 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
-        </is>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260930800164</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1953900</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1485.076</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1315.69</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 21건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
+          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
+          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 22건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 7%, ③중마진 86%, ④호황 7% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
+          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 7%, ③중마진 80%, ④호황 13% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>⚠ 정기보고서 부문 매출(3개월분)을 만들 수 없어 화해 없음</t>
         </is>
@@ -48401,7 +48457,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>48196.7</v>
+        <v>48471.7</v>
       </c>
     </row>
     <row r="30">
@@ -48421,7 +48477,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.7</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="32">
@@ -48441,7 +48497,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2298</v>
+        <v>0.2311</v>
       </c>
     </row>
     <row r="34">
@@ -48451,7 +48507,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="35">
@@ -48461,7 +48517,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>534800</v>
+        <v>539000</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -22,7 +22,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$101</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$111</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$95</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -656,55 +656,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66113억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 67102억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 65636억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 69348억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 65475억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 73275억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 64648억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 77533억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 63896억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 82494억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 62993억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 87565억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 62351억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 92791억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 61017억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 96850억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 59230억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 99613억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -770,121 +770,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.7% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.7% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.7% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.0% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.1% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.7% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.7% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.7% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.6% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.4% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.4% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.4% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 12.6% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 13.0% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-자회사 OPM 13.1% + 실측 차이 +1.7%p</t>
+자회사 OPM 14.0% + 실측 차이 +1.7%p</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -896,55 +896,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 162554억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 163467억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 173853억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 175911억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 185133억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 188817억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 187689억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 193785억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 198684억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 208227억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 209611억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 223620억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 220450억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 239987억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 222702억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 248664억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 233703억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 266800억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1883,55 +1883,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66113억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 67102억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 65636억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 69348억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 65475억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 73275억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 64648억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 77533억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 63896억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 82494억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 62993억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 87565억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 62351억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 92791억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 61017억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 96850억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 59230억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 99613억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2117,61 +2117,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.7% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.7% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.7% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.4% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 12.6% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.0% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.1% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.0% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
@@ -2272,61 +2272,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.7% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.7% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.7% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.6% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.4% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 12.6% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.0% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.1% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.0% + 실측 차이 +1.7%p
 [yoy]</t>
       </text>
     </comment>
@@ -2338,55 +2338,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 162554억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 163467억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 173853억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 175911억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 185133억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 188817억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 187689억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 193785억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 198684억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 208227억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 209611억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 223620억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 220450억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 239987억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 222702억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 248664억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 233703억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 266800억 × 2.60% − 총차입금 29860억 × 4.06% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4502,7 +4502,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.8, "op_wape_pct": 34.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "subsidiary_yard_scaled", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 74060.53, "rev_act": 75814.36, "op_pred": 8350.88, "op_act": 10537.75}, {"q": "2025Q4", "rev_pred": 74060.53, "rev_act": 81516.57, "op_pred": 8350.88, "op_act": 10379.19}, {"q": "2026Q1", "rev_pred": 73789.18, "rev_act": 81408.9, "op_pred": 8320.27, "op_act": 13559.7}, {"q": "2026Q2", "rev_pred": 73924.83, "rev_act": 89270.46, "op_pred": 8335.59, "op_act": 16451.46}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.8, "op_wape_pct": 40.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "subsidiary_yard_scaled", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 74060.53, "rev_act": 75814.36, "op_pred": 7553.95, "op_act": 10537.75}, {"q": "2025Q4", "rev_pred": 74060.53, "rev_act": 81516.57, "op_pred": 7553.95, "op_act": 10379.19}, {"q": "2026Q1", "rev_pred": 73789.18, "rev_act": 81408.9, "op_pred": 7526.28, "op_act": 13559.7}, {"q": "2026Q2", "rev_pred": 73924.83, "rev_act": 89270.46, "op_pred": 7540.11, "op_act": 16451.46}]}</t>
         </is>
       </c>
     </row>
@@ -8534,33 +8534,33 @@
         <v>0.226443</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.143391</v>
+        <v>0.160501</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.136656</v>
+        <v>0.200936</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.034015</v>
+        <v>0.157188</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>-0.019802</v>
+        <v>0.175551</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.033529</v>
+        <v>0.229384</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.04028</v>
+        <v>0.262692</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.047724</v>
+        <v>0.266343</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.056162</v>
+        <v>0.249159</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.073019</v>
+        <v>0.207512</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -8832,42 +8832,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.143932</v>
+        <v>0.156182</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.143232</v>
+        <v>0.156183</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.143232</v>
+        <v>0.156183</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.142433</v>
+        <v>0.156183</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.140533</v>
+        <v>0.156183</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.140433</v>
+        <v>0.156183</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.140433</v>
+        <v>0.156182</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.142633</v>
+        <v>0.156183</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.146333</v>
+        <v>0.156183</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.147233</v>
+        <v>0.156183</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8960,36 +8960,36 @@
         <v/>
       </c>
       <c r="AC24" s="24" t="n">
-        <v>0.035252</v>
+        <v>0.123741</v>
       </c>
       <c r="AD24" s="24" t="n">
-        <v>0.124902</v>
+        <v>0.227023</v>
       </c>
       <c r="AE24" s="25" t="n"/>
       <c r="AF24" s="24" t="n">
-        <v>-0.140456</v>
+        <v>-0.062425</v>
       </c>
       <c r="AG24" s="24" t="n">
-        <v>-0.227347</v>
+        <v>-0.152469</v>
       </c>
       <c r="AH24" s="24" t="n">
-        <v>-0.023628</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="24" t="n">
-        <v>-0.019553</v>
+        <v>0</v>
       </c>
       <c r="AJ24" s="25" t="n"/>
       <c r="AK24" s="24" t="n">
-        <v>-0.019553</v>
+        <v>0</v>
       </c>
       <c r="AL24" s="24" t="n">
-        <v>0.001404</v>
+        <v>0</v>
       </c>
       <c r="AM24" s="24" t="n">
-        <v>0.041281</v>
+        <v>0</v>
       </c>
       <c r="AN24" s="24" t="n">
-        <v>0.048433</v>
+        <v>0</v>
       </c>
       <c r="AO24" s="25" t="n"/>
     </row>
@@ -9109,39 +9109,39 @@
         <v>680.8200000000001</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>754.08</v>
+        <v>760.01</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>827.55</v>
+        <v>840.9400000000001</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>900.9</v>
+        <v>924.86</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>917.52</v>
+        <v>957.16</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>989.02</v>
+        <v>1051.08</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>1060.07</v>
+        <v>1151.17</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>1130.56</v>
+        <v>1257.6</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>1145.2</v>
+        <v>1314.02</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>1216.74</v>
+        <v>1431.95</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -9739,7 +9739,7 @@
         <v>0.760027</v>
       </c>
       <c r="AG29" s="24" t="n">
-        <v>0.760028</v>
+        <v>0.760027</v>
       </c>
       <c r="AH29" s="24" t="n">
         <v>0.760028</v>
@@ -9761,7 +9761,7 @@
         <v>0.760027</v>
       </c>
       <c r="AN29" s="24" t="n">
-        <v>0.760027</v>
+        <v>0.760028</v>
       </c>
       <c r="AO29" s="25">
         <f>IFERROR(subQ!AO17/subQ!AO16,"")</f>
@@ -9998,26 +9998,26 @@
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="29" t="n">
+        <v>8697.9</v>
+      </c>
+      <c r="AH31" s="29" t="n">
         <v>-0</v>
-      </c>
-      <c r="AG31" s="29" t="n">
-        <v>8697.889999999999</v>
-      </c>
-      <c r="AH31" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>8697.889999999999</v>
+        <v>8697.9</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0</v>
@@ -10119,7 +10119,7 @@
         <v/>
       </c>
       <c r="AC32" s="29" t="n">
-        <v>-0.0046</v>
+        <v>0.0054</v>
       </c>
       <c r="AD32" s="29" t="n">
         <v>0</v>
@@ -10129,13 +10129,13 @@
         <v>0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>8697.9</v>
+        <v>8697.889999999999</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
@@ -10375,36 +10375,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.093933</v>
+        <v>0.10154</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.08611199999999999</v>
+        <v>0.094193</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.07915700000000001</v>
+        <v>0.08927300000000001</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.016621</v>
+        <v>0.031547</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.07033</v>
+        <v>0.088911</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.065294</v>
+        <v>0.087024</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.060808</v>
+        <v>0.08512699999999999</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.011906</v>
+        <v>0.041586</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.057492</v>
+        <v>0.083453</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.053487</v>
+        <v>0.079495</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -10503,36 +10503,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.07446999999999999</v>
+        <v>0.080501</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.069506</v>
+        <v>0.07613</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.064884</v>
+        <v>0.073365</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.013806</v>
+        <v>0.026309</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.058583</v>
+        <v>0.074528</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.054992</v>
+        <v>0.073923</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.051714</v>
+        <v>0.07319299999999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.010213</v>
+        <v>0.036154</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.049399</v>
+        <v>0.072932</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.046313</v>
+        <v>0.070155</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11161,36 +11161,36 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.519691</v>
+        <v>-0.528185</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.577525</v>
+        <v>-0.593883</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.492716</v>
+        <v>-0.526992</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.212766</v>
+        <v>-0.306147</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.07717</v>
+        <v>-0.080196</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>0.138047</v>
+        <v>-0.06655</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>0.153716</v>
+        <v>-0.09057999999999999</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>0.033033</v>
+        <v>-0.194208</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>0.025373</v>
+        <v>-0.204626</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>0.019231</v>
+        <v>-0.20075</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -11280,36 +11280,36 @@
         <v/>
       </c>
       <c r="AC42" s="24" t="n">
-        <v>-0.308057</v>
+        <v>-0.312796</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.39738</v>
+        <v>-0.401747</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.396313</v>
+        <v>-0.40553</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.335025</v>
+        <v>-0.350254</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.143836</v>
+        <v>-0.165517</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.130435</v>
+        <v>-0.167883</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.122137</v>
+        <v>-0.170543</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.122137</v>
+        <v>-0.179688</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.12</v>
+        <v>-0.190083</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.116667</v>
+        <v>-0.184211</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -11581,42 +11581,42 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>0.143932</v>
+        <v>0.156182</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.143232</v>
+        <v>0.156183</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.143232</v>
+        <v>0.156183</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.142433</v>
+        <v>0.156183</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.140533</v>
+        <v>0.156183</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.140433</v>
+        <v>0.156183</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.140433</v>
+        <v>0.156182</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.142633</v>
+        <v>0.156183</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.146333</v>
+        <v>0.156183</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.147233</v>
+        <v>0.156183</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -12111,7 +12111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO101"/>
+  <dimension ref="A1:AO111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20358,78 +20358,47 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>-441452.68</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>19429.74</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>208403.68</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>191575.98</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>42836.37</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>462245.77</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>762750.9300000001</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>542991.39</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>944715.27</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>-168866.66</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>2081590.93</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
       <c r="Q87" s="18" t="n">
-        <v>755596.45</v>
+        <v>53146</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1526057.79</v>
+        <v>51184</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>119321.75</v>
+        <v>49722</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>1887684.19</v>
+        <v>59022</v>
       </c>
       <c r="U87" s="34" t="n">
-        <v>4288660.18</v>
+        <v>213074</v>
       </c>
       <c r="V87" s="18" t="n">
-        <v>2184544.04</v>
+        <v>57847</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>1082950.18</v>
+        <v>66767</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>1702441.67</v>
+        <v>66049</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>-547885.25</v>
+        <v>64327</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>4422050.64</v>
+        <v>254990</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>1775559.42</v>
+        <v>66391</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>2603951.37</v>
+        <v>85010</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -20451,78 +20420,47 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>16996.82</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="G88" s="18" t="n">
-        <v>18414.8</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>22974.54</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>31343.76</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>51703.69</v>
-      </c>
-      <c r="K88" s="34" t="n">
-        <v>124436.79</v>
-      </c>
-      <c r="L88" s="18" t="n">
-        <v>47765.21</v>
-      </c>
-      <c r="M88" s="18" t="n">
-        <v>41450.99</v>
-      </c>
-      <c r="N88" s="18" t="n">
-        <v>37646.93</v>
-      </c>
-      <c r="O88" s="18" t="n">
-        <v>61566.25</v>
-      </c>
-      <c r="P88" s="34" t="n">
-        <v>188429.38</v>
-      </c>
+      <c r="K88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
       <c r="Q88" s="18" t="n">
-        <v>65644.19</v>
+        <v>3591</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>50606.21</v>
+        <v>26</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>48306.57</v>
+        <v>12</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>51513.17</v>
+        <v>3</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>216070.14</v>
+        <v>3632</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>48068.96</v>
+        <v>170</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>69575.62</v>
+        <v>3</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>61388.33</v>
+        <v>65</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>46506.68</v>
+        <v>7</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>225539.59</v>
+        <v>245</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>62709.95</v>
+        <v>268</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>89592.67999999999</v>
+        <v>6</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -20544,78 +20482,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>-33999.42</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>-29831.84</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>-31392.63</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>-34973.1</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>-32004.07</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>-128201.64</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>-46093.64</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>-37699.81</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>-41720.64</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>-52044.08</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>-177558.17</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
       <c r="Q89" s="18" t="n">
-        <v>-62119.68</v>
+        <v>60072</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>-30188.56</v>
+        <v>53985</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>-41195.57</v>
+        <v>44262</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>-18127.61</v>
+        <v>48003</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>-151631.42</v>
+        <v>206322</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>-24354.76</v>
+        <v>39703</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>-9728.43</v>
+        <v>44880</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>-18560.29</v>
+        <v>44101</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>-27062.5</v>
+        <v>30078</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>-79705.98</v>
+        <v>158762</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>-15370.69</v>
+        <v>38616</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>-2490.84</v>
+        <v>92377</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -20637,78 +20544,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>40737.12</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>172.75</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>6258.74</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>6449.4</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>170.25</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>6771.23</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>6958.29</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
       <c r="Q90" s="18" t="n">
-        <v>54.78</v>
+        <v>203433</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>3706.77</v>
+        <v>302238</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>12.41</v>
+        <v>155388</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>27838.71</v>
+        <v>285849</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>31612.67</v>
+        <v>946908</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>37.05</v>
+        <v>162258</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>1020.28</v>
+        <v>241900</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>64.84</v>
+        <v>176052</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>6.42</v>
+        <v>233393</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>1128.59</v>
+        <v>813603</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>76.19</v>
+        <v>364975</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>1304.09</v>
+        <v>448403</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -20730,62 +20606,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>655.01</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>-3175.4</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>4117.76</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>-10400.97</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>-9209.02</v>
-      </c>
-      <c r="K91" s="34" t="n">
-        <v>-18667.63</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>-8706.120000000001</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>-1843.93</v>
-      </c>
-      <c r="N91" s="18" t="n">
-        <v>-6611.94</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>-7857</v>
-      </c>
-      <c r="P91" s="34" t="n">
-        <v>-25018.99</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
       <c r="Q91" s="18" t="n">
-        <v>-7286.07</v>
+        <v>98554</v>
+      </c>
+      <c r="R91" s="18" t="n">
+        <v>121808</v>
+      </c>
+      <c r="S91" s="18" t="n">
+        <v>143996</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>-8961.690000000001</v>
-      </c>
-      <c r="U91" s="9" t="n"/>
+        <v>116315</v>
+      </c>
+      <c r="U91" s="34" t="n">
+        <v>480673</v>
+      </c>
       <c r="V91" s="18" t="n">
-        <v>-12467.11</v>
+        <v>236630</v>
+      </c>
+      <c r="W91" s="18" t="n">
+        <v>472913</v>
+      </c>
+      <c r="X91" s="18" t="n">
+        <v>282773</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>-8551.040000000001</v>
-      </c>
-      <c r="Z91" s="9" t="n"/>
+        <v>162019</v>
+      </c>
+      <c r="Z91" s="34" t="n">
+        <v>1154335</v>
+      </c>
       <c r="AA91" s="18" t="n">
-        <v>-23026.9</v>
+        <v>217365</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>-63819.1</v>
+        <v>254597</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -20807,78 +20668,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>167889.63</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>-199318.38</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>-19669.57</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>-1039801.34</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>-80681.37</v>
-      </c>
-      <c r="K92" s="34" t="n">
-        <v>-1339470.66</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>-21313.82</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>586275.47</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>-994862.9399999999</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>-836988.26</v>
-      </c>
-      <c r="P92" s="34" t="n">
-        <v>-1266889.55</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
       <c r="Q92" s="18" t="n">
-        <v>510535.87</v>
+        <v>241717</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>-1093407.1</v>
+        <v>45241</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>-261909.31</v>
+        <v>0</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>-388020.87</v>
+        <v>530784</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>-1232801.41</v>
+        <v>817742</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>-753976.5600000001</v>
+        <v>52531</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>-464113.62</v>
+        <v>52397</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>-2107226.95</v>
+        <v>334500</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>-278523.19</v>
+        <v>51326</v>
       </c>
       <c r="Z92" s="34" t="n">
-        <v>-3603840.32</v>
+        <v>490754</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>975569.45</v>
+        <v>381838</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>446610.35</v>
+        <v>135499</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -20900,78 +20730,47 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>7674.54</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>2878.08</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>7116.78</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>10419.17</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>3217.02</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>23631.05</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>2904.18</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>4930.15</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>3602.49</v>
-      </c>
-      <c r="O93" s="18" t="n">
-        <v>12225.01</v>
-      </c>
-      <c r="P93" s="34" t="n">
-        <v>23661.83</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
+      <c r="P93" s="9" t="n"/>
       <c r="Q93" s="18" t="n">
-        <v>8761.559999999999</v>
+        <v>74042</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>8415.43</v>
+        <v>26859</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>5498.76</v>
+        <v>345213</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>1820.38</v>
+        <v>-20614</v>
       </c>
       <c r="U93" s="34" t="n">
-        <v>24496.13</v>
+        <v>425500</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>4219.63</v>
+        <v>27360</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>15773.93</v>
+        <v>410728</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>2713.72</v>
+        <v>0</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>9218.65</v>
+        <v>-10246</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>31925.93</v>
+        <v>427842</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>1952.13</v>
+        <v>91407</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>9804.360000000001</v>
+        <v>142777</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -20993,45 +20792,47 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>300</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="I94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="K94" s="9" t="n"/>
       <c r="P94" s="9" t="n"/>
+      <c r="Q94" s="18" t="n">
+        <v>59757</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>10889</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>1230188</v>
+      </c>
       <c r="T94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n"/>
+        <v>-91936</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>1208898</v>
+      </c>
       <c r="V94" s="18" t="n">
-        <v>11.21</v>
+        <v>48443</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>0</v>
+        <v>2232287</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>985.91</v>
+        <v>154810</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>3282.05</v>
+        <v>-488050</v>
       </c>
       <c r="Z94" s="34" t="n">
-        <v>4279.17</v>
+        <v>1947490</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>0</v>
+        <v>35563</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>0</v>
+        <v>24996</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -21053,78 +20854,47 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>111586.14</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="G95" s="18" t="n">
-        <v>92408.14999999999</v>
-      </c>
-      <c r="H95" s="18" t="n">
-        <v>154627.4</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>211326.34</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>208529.12</v>
-      </c>
-      <c r="K95" s="34" t="n">
-        <v>666891.01</v>
-      </c>
-      <c r="L95" s="18" t="n">
-        <v>146046.52</v>
-      </c>
-      <c r="M95" s="18" t="n">
-        <v>222061.34</v>
-      </c>
-      <c r="N95" s="18" t="n">
-        <v>227623.87</v>
-      </c>
-      <c r="O95" s="18" t="n">
-        <v>226221.37</v>
-      </c>
-      <c r="P95" s="34" t="n">
-        <v>821953.1</v>
-      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="P95" s="9" t="n"/>
       <c r="Q95" s="18" t="n">
-        <v>184798.26</v>
+        <v>1233915</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>237755</v>
+        <v>965463</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>242961.79</v>
+        <v>182105</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>225473.99</v>
+        <v>3000352</v>
       </c>
       <c r="U95" s="34" t="n">
-        <v>890989.04</v>
+        <v>5381835</v>
       </c>
       <c r="V95" s="18" t="n">
-        <v>305401.7</v>
+        <v>243285</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>192975.17</v>
+        <v>10711</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>223086.15</v>
+        <v>1392245</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>225371.71</v>
+        <v>462356</v>
       </c>
       <c r="Z95" s="34" t="n">
-        <v>946834.73</v>
+        <v>2108597</v>
       </c>
       <c r="AA95" s="18" t="n">
-        <v>184515.63</v>
+        <v>1881727</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>195858.74</v>
+        <v>799209</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -21146,78 +20916,47 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>128443.33</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="G96" s="18" t="n">
-        <v>97553.85000000001</v>
-      </c>
-      <c r="H96" s="18" t="n">
-        <v>161857.65</v>
-      </c>
-      <c r="I96" s="18" t="n">
-        <v>223384.89</v>
-      </c>
-      <c r="J96" s="18" t="n">
-        <v>224603.23</v>
-      </c>
-      <c r="K96" s="34" t="n">
-        <v>707399.62</v>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>156070.01</v>
-      </c>
-      <c r="M96" s="18" t="n">
-        <v>233127.78</v>
-      </c>
-      <c r="N96" s="18" t="n">
-        <v>243738.95</v>
-      </c>
-      <c r="O96" s="18" t="n">
-        <v>249103.02</v>
-      </c>
-      <c r="P96" s="34" t="n">
-        <v>882039.76</v>
-      </c>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
       <c r="Q96" s="18" t="n">
-        <v>195556.18</v>
+        <v>-6926</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>248185.1</v>
+        <v>-2801</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>253555.15</v>
+        <v>5460</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>251745.24</v>
+        <v>11019</v>
       </c>
       <c r="U96" s="34" t="n">
-        <v>949041.67</v>
+        <v>6752</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>312531.22</v>
+        <v>18144</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>206038.33</v>
+        <v>21887</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>233867.76</v>
+        <v>21948</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>251263.64</v>
+        <v>34249</v>
       </c>
       <c r="Z96" s="34" t="n">
-        <v>1003700.95</v>
+        <v>96228</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>193606.13</v>
+        <v>27775</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>209826.55</v>
+        <v>-7367</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -21239,78 +20978,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
-        <v>16857.19</v>
+        <v>-441452.68</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>5145.7</v>
+        <v>19429.74</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>7230.25</v>
+        <v>208403.68</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>12058.55</v>
+        <v>191575.98</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>16074.11</v>
+        <v>42836.37</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>40508.61</v>
+        <v>462245.77</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>10023.49</v>
+        <v>762750.9300000001</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>11066.44</v>
+        <v>542991.39</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>16115.08</v>
+        <v>944715.27</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>22881.65</v>
+        <v>-168866.66</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>60086.66</v>
+        <v>2081590.93</v>
       </c>
       <c r="Q97" s="18" t="n">
-        <v>10757.92</v>
+        <v>755596.45</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>10430.1</v>
+        <v>1526057.79</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>10593.36</v>
+        <v>119321.75</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>26271.25</v>
+        <v>1887684.19</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>58052.63</v>
+        <v>4288660.18</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>7129.52</v>
+        <v>2184544.04</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>13063.16</v>
+        <v>1082950.18</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>10781.61</v>
+        <v>1702441.67</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>25891.93</v>
+        <v>-547885.25</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>56866.22</v>
+        <v>4422050.64</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>9090.5</v>
+        <v>1775559.42</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>13967.81</v>
+        <v>2603951.37</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -21332,78 +21071,78 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E98" s="18" t="n">
-        <v>-717845.88</v>
+        <v>16996.82</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
-        <v>144143.98</v>
+        <v>18414.8</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>27273.1</v>
+        <v>22974.54</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>-273298.21</v>
+        <v>31343.76</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>-875389.25</v>
+        <v>51703.69</v>
       </c>
       <c r="K98" s="34" t="n">
-        <v>-977270.38</v>
+        <v>124436.79</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>-591077.39</v>
+        <v>47765.21</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>292019.11</v>
+        <v>41450.99</v>
       </c>
       <c r="N98" s="18" t="n">
-        <v>-184404.76</v>
+        <v>37646.93</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>-1745.74</v>
+        <v>61566.25</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>-485208.78</v>
+        <v>188429.38</v>
       </c>
       <c r="Q98" s="18" t="n">
-        <v>-611991.71</v>
+        <v>65644.19</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>-709438.28</v>
+        <v>50606.21</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>-708473.34</v>
+        <v>48306.57</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>-329064.71</v>
+        <v>51513.17</v>
       </c>
       <c r="U98" s="34" t="n">
-        <v>-2358968.04</v>
+        <v>216070.14</v>
       </c>
       <c r="V98" s="18" t="n">
-        <v>451391.26</v>
+        <v>48068.96</v>
       </c>
       <c r="W98" s="18" t="n">
-        <v>-699760.55</v>
+        <v>69575.62</v>
       </c>
       <c r="X98" s="18" t="n">
-        <v>-391971.29</v>
+        <v>61388.33</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>-151935.43</v>
+        <v>46506.68</v>
       </c>
       <c r="Z98" s="34" t="n">
-        <v>-792276.01</v>
+        <v>225539.59</v>
       </c>
       <c r="AA98" s="18" t="n">
-        <v>-46384.23</v>
+        <v>62709.95</v>
       </c>
       <c r="AB98" s="19" t="n">
-        <v>1392171.21</v>
+        <v>89592.67999999999</v>
       </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -21425,78 +21164,78 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E99" s="18" t="n">
-        <v>5109.03</v>
+        <v>-33999.42</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="18" t="n">
-        <v>4285.59</v>
+        <v>-29831.84</v>
       </c>
       <c r="H99" s="18" t="n">
-        <v>5277.07</v>
+        <v>-31392.63</v>
       </c>
       <c r="I99" s="18" t="n">
-        <v>4540.93</v>
+        <v>-34973.1</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>6517.29</v>
+        <v>-32004.07</v>
       </c>
       <c r="K99" s="34" t="n">
-        <v>20620.88</v>
+        <v>-128201.64</v>
       </c>
       <c r="L99" s="18" t="n">
-        <v>7182.17</v>
+        <v>-46093.64</v>
       </c>
       <c r="M99" s="18" t="n">
-        <v>9107.540000000001</v>
+        <v>-37699.81</v>
       </c>
       <c r="N99" s="18" t="n">
-        <v>8584.690000000001</v>
+        <v>-41720.64</v>
       </c>
       <c r="O99" s="18" t="n">
-        <v>8135.68</v>
+        <v>-52044.08</v>
       </c>
       <c r="P99" s="34" t="n">
-        <v>33010.08</v>
+        <v>-177558.17</v>
       </c>
       <c r="Q99" s="18" t="n">
-        <v>8944.6</v>
+        <v>-62119.68</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>9994.799999999999</v>
+        <v>-30188.56</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>9147.51</v>
+        <v>-41195.57</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>7139.79</v>
+        <v>-18127.61</v>
       </c>
       <c r="U99" s="34" t="n">
-        <v>35226.7</v>
+        <v>-151631.42</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>8127.99</v>
+        <v>-24354.76</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>9213.49</v>
+        <v>-9728.43</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>9317.610000000001</v>
+        <v>-18560.29</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>10689.65</v>
+        <v>-27062.5</v>
       </c>
       <c r="Z99" s="34" t="n">
-        <v>37348.74</v>
+        <v>-79705.98</v>
       </c>
       <c r="AA99" s="18" t="n">
-        <v>9043.379999999999</v>
+        <v>-15370.69</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>9937.709999999999</v>
+        <v>-2490.84</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -21518,78 +21257,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E100" s="18" t="n">
-        <v>-991955.35</v>
+        <v>40737.12</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="18" t="n">
-        <v>-35166.64</v>
+        <v>172.75</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>220659.62</v>
+        <v>6258.74</v>
       </c>
       <c r="I100" s="18" t="n">
-        <v>-1118488.92</v>
+        <v>13.91</v>
       </c>
       <c r="J100" s="18" t="n">
-        <v>-937249.29</v>
+        <v>4</v>
       </c>
       <c r="K100" s="34" t="n">
-        <v>-1870245.23</v>
+        <v>6449.4</v>
       </c>
       <c r="L100" s="18" t="n">
-        <v>155349.75</v>
+        <v>170.25</v>
       </c>
       <c r="M100" s="18" t="n">
-        <v>1417737.12</v>
+        <v>6771.23</v>
       </c>
       <c r="N100" s="18" t="n">
-        <v>-234807.94</v>
+        <v>12.81</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>-1017110.83</v>
+        <v>4</v>
       </c>
       <c r="P100" s="34" t="n">
-        <v>321168.1</v>
+        <v>6958.29</v>
       </c>
       <c r="Q100" s="18" t="n">
-        <v>651212.95</v>
+        <v>54.78</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>-271753.66</v>
+        <v>3706.77</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>-854473.53</v>
+        <v>12.41</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>1173942.23</v>
+        <v>27838.71</v>
       </c>
       <c r="U100" s="34" t="n">
-        <v>698927.99</v>
+        <v>31612.67</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>1883124.15</v>
+        <v>37.05</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>-86609.06</v>
+        <v>1020.28</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>187588.87</v>
+        <v>64.84</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>-1959407.37</v>
+        <v>6.42</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>24696.59</v>
+        <v>1128.59</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>2726657.22</v>
+        <v>76.19</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>4527302.7</v>
+        <v>1304.09</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -21611,78 +21350,62 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E101" s="18" t="n">
-        <v>-991955.35</v>
+        <v>655.01</v>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="18" t="n">
-        <v>4532301.46</v>
+        <v>-3175.4</v>
       </c>
       <c r="H101" s="18" t="n">
-        <v>220659.62</v>
+        <v>4117.76</v>
       </c>
       <c r="I101" s="18" t="n">
-        <v>-1118488.92</v>
+        <v>-10400.97</v>
       </c>
       <c r="J101" s="18" t="n">
-        <v>-937249.29</v>
+        <v>-9209.02</v>
       </c>
       <c r="K101" s="34" t="n">
-        <v>2697222.87</v>
+        <v>-18667.63</v>
       </c>
       <c r="L101" s="18" t="n">
-        <v>2852572.62</v>
+        <v>-8706.120000000001</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>1417737.12</v>
+        <v>-1843.93</v>
       </c>
       <c r="N101" s="18" t="n">
-        <v>-234807.95</v>
+        <v>-6611.94</v>
       </c>
       <c r="O101" s="18" t="n">
-        <v>-1017110.83</v>
+        <v>-7857</v>
       </c>
       <c r="P101" s="34" t="n">
-        <v>3018390.96</v>
+        <v>-25018.99</v>
       </c>
       <c r="Q101" s="18" t="n">
-        <v>3669603.92</v>
-      </c>
-      <c r="R101" s="18" t="n">
-        <v>-271753.66</v>
-      </c>
-      <c r="S101" s="18" t="n">
-        <v>-854473.54</v>
+        <v>-7286.07</v>
       </c>
       <c r="T101" s="18" t="n">
-        <v>1173942.24</v>
-      </c>
-      <c r="U101" s="34" t="n">
-        <v>3717318.96</v>
-      </c>
+        <v>-8961.690000000001</v>
+      </c>
+      <c r="U101" s="9" t="n"/>
       <c r="V101" s="18" t="n">
-        <v>5600443.11</v>
-      </c>
-      <c r="W101" s="18" t="n">
-        <v>-86609.06</v>
-      </c>
-      <c r="X101" s="18" t="n">
-        <v>3904907.83</v>
+        <v>-12467.11</v>
       </c>
       <c r="Y101" s="18" t="n">
-        <v>-5676726.33</v>
-      </c>
-      <c r="Z101" s="34" t="n">
-        <v>3742015.55</v>
-      </c>
+        <v>-8551.040000000001</v>
+      </c>
+      <c r="Z101" s="9" t="n"/>
       <c r="AA101" s="18" t="n">
-        <v>6468672.77</v>
+        <v>-23026.9</v>
       </c>
       <c r="AB101" s="19" t="n">
-        <v>4527302.69</v>
+        <v>-63819.1</v>
       </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
@@ -21697,6 +21420,903 @@
       <c r="AM101" s="10" t="n"/>
       <c r="AN101" s="10" t="n"/>
       <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>투자활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>167889.63</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>-199318.38</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>-19669.57</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>-1039801.34</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>-80681.37</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>-1339470.66</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>-21313.82</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>586275.47</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>-994862.9399999999</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>-836988.26</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>-1266889.55</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>510535.87</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>-1093407.1</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>-261909.31</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>-388020.87</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>-1232801.41</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>-753976.5600000001</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>-464113.62</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>-2107226.95</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>-278523.19</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>-3603840.32</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>975569.45</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>446610.35</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>7674.54</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>2878.08</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>7116.78</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>10419.17</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>3217.02</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>23631.05</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>2904.18</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>4930.15</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>3602.49</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>12225.01</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>23661.83</v>
+      </c>
+      <c r="Q103" s="18" t="n">
+        <v>8761.559999999999</v>
+      </c>
+      <c r="R103" s="18" t="n">
+        <v>8415.43</v>
+      </c>
+      <c r="S103" s="18" t="n">
+        <v>5498.76</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>1820.38</v>
+      </c>
+      <c r="U103" s="34" t="n">
+        <v>24496.13</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>4219.63</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>15773.93</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>2713.72</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>9218.65</v>
+      </c>
+      <c r="Z103" s="34" t="n">
+        <v>31925.93</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>1952.13</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>9804.360000000001</v>
+      </c>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="I104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="9" t="n"/>
+      <c r="P104" s="9" t="n"/>
+      <c r="T104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n"/>
+      <c r="V104" s="18" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="W104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="18" t="n">
+        <v>985.91</v>
+      </c>
+      <c r="Y104" s="18" t="n">
+        <v>3282.05</v>
+      </c>
+      <c r="Z104" s="34" t="n">
+        <v>4279.17</v>
+      </c>
+      <c r="AA104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>111586.14</v>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="18" t="n">
+        <v>92408.14999999999</v>
+      </c>
+      <c r="H105" s="18" t="n">
+        <v>154627.4</v>
+      </c>
+      <c r="I105" s="18" t="n">
+        <v>211326.34</v>
+      </c>
+      <c r="J105" s="18" t="n">
+        <v>208529.12</v>
+      </c>
+      <c r="K105" s="34" t="n">
+        <v>666891.01</v>
+      </c>
+      <c r="L105" s="18" t="n">
+        <v>146046.52</v>
+      </c>
+      <c r="M105" s="18" t="n">
+        <v>222061.34</v>
+      </c>
+      <c r="N105" s="18" t="n">
+        <v>227623.87</v>
+      </c>
+      <c r="O105" s="18" t="n">
+        <v>226221.37</v>
+      </c>
+      <c r="P105" s="34" t="n">
+        <v>821953.1</v>
+      </c>
+      <c r="Q105" s="18" t="n">
+        <v>184798.26</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>237755</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>242961.79</v>
+      </c>
+      <c r="T105" s="18" t="n">
+        <v>225473.99</v>
+      </c>
+      <c r="U105" s="34" t="n">
+        <v>890989.04</v>
+      </c>
+      <c r="V105" s="18" t="n">
+        <v>305401.7</v>
+      </c>
+      <c r="W105" s="18" t="n">
+        <v>192975.17</v>
+      </c>
+      <c r="X105" s="18" t="n">
+        <v>223086.15</v>
+      </c>
+      <c r="Y105" s="18" t="n">
+        <v>225371.71</v>
+      </c>
+      <c r="Z105" s="34" t="n">
+        <v>946834.73</v>
+      </c>
+      <c r="AA105" s="18" t="n">
+        <v>184515.63</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>195858.74</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>128443.33</v>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="18" t="n">
+        <v>97553.85000000001</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>161857.65</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>223384.89</v>
+      </c>
+      <c r="J106" s="18" t="n">
+        <v>224603.23</v>
+      </c>
+      <c r="K106" s="34" t="n">
+        <v>707399.62</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>156070.01</v>
+      </c>
+      <c r="M106" s="18" t="n">
+        <v>233127.78</v>
+      </c>
+      <c r="N106" s="18" t="n">
+        <v>243738.95</v>
+      </c>
+      <c r="O106" s="18" t="n">
+        <v>249103.02</v>
+      </c>
+      <c r="P106" s="34" t="n">
+        <v>882039.76</v>
+      </c>
+      <c r="Q106" s="18" t="n">
+        <v>195556.18</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>248185.1</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>253555.15</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>251745.24</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>949041.67</v>
+      </c>
+      <c r="V106" s="18" t="n">
+        <v>312531.22</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>206038.33</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>233867.76</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>251263.64</v>
+      </c>
+      <c r="Z106" s="34" t="n">
+        <v>1003700.95</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>193606.13</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>209826.55</v>
+      </c>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>16857.19</v>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="18" t="n">
+        <v>5145.7</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>7230.25</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>12058.55</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>16074.11</v>
+      </c>
+      <c r="K107" s="34" t="n">
+        <v>40508.61</v>
+      </c>
+      <c r="L107" s="18" t="n">
+        <v>10023.49</v>
+      </c>
+      <c r="M107" s="18" t="n">
+        <v>11066.44</v>
+      </c>
+      <c r="N107" s="18" t="n">
+        <v>16115.08</v>
+      </c>
+      <c r="O107" s="18" t="n">
+        <v>22881.65</v>
+      </c>
+      <c r="P107" s="34" t="n">
+        <v>60086.66</v>
+      </c>
+      <c r="Q107" s="18" t="n">
+        <v>10757.92</v>
+      </c>
+      <c r="R107" s="18" t="n">
+        <v>10430.1</v>
+      </c>
+      <c r="S107" s="18" t="n">
+        <v>10593.36</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>26271.25</v>
+      </c>
+      <c r="U107" s="34" t="n">
+        <v>58052.63</v>
+      </c>
+      <c r="V107" s="18" t="n">
+        <v>7129.52</v>
+      </c>
+      <c r="W107" s="18" t="n">
+        <v>13063.16</v>
+      </c>
+      <c r="X107" s="18" t="n">
+        <v>10781.61</v>
+      </c>
+      <c r="Y107" s="18" t="n">
+        <v>25891.93</v>
+      </c>
+      <c r="Z107" s="34" t="n">
+        <v>56866.22</v>
+      </c>
+      <c r="AA107" s="18" t="n">
+        <v>9090.5</v>
+      </c>
+      <c r="AB107" s="19" t="n">
+        <v>13967.81</v>
+      </c>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="11" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>-717845.88</v>
+      </c>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>144143.98</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>27273.1</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>-273298.21</v>
+      </c>
+      <c r="J108" s="18" t="n">
+        <v>-875389.25</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>-977270.38</v>
+      </c>
+      <c r="L108" s="18" t="n">
+        <v>-591077.39</v>
+      </c>
+      <c r="M108" s="18" t="n">
+        <v>292019.11</v>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>-184404.76</v>
+      </c>
+      <c r="O108" s="18" t="n">
+        <v>-1745.74</v>
+      </c>
+      <c r="P108" s="34" t="n">
+        <v>-485208.78</v>
+      </c>
+      <c r="Q108" s="18" t="n">
+        <v>-611991.71</v>
+      </c>
+      <c r="R108" s="18" t="n">
+        <v>-709438.28</v>
+      </c>
+      <c r="S108" s="18" t="n">
+        <v>-708473.34</v>
+      </c>
+      <c r="T108" s="18" t="n">
+        <v>-329064.71</v>
+      </c>
+      <c r="U108" s="34" t="n">
+        <v>-2358968.04</v>
+      </c>
+      <c r="V108" s="18" t="n">
+        <v>451391.26</v>
+      </c>
+      <c r="W108" s="18" t="n">
+        <v>-699760.55</v>
+      </c>
+      <c r="X108" s="18" t="n">
+        <v>-391971.29</v>
+      </c>
+      <c r="Y108" s="18" t="n">
+        <v>-151935.43</v>
+      </c>
+      <c r="Z108" s="34" t="n">
+        <v>-792276.01</v>
+      </c>
+      <c r="AA108" s="18" t="n">
+        <v>-46384.23</v>
+      </c>
+      <c r="AB108" s="19" t="n">
+        <v>1392171.21</v>
+      </c>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="10" t="n"/>
+      <c r="AL108" s="10" t="n"/>
+      <c r="AM108" s="10" t="n"/>
+      <c r="AN108" s="10" t="n"/>
+      <c r="AO108" s="11" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>5109.03</v>
+      </c>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="18" t="n">
+        <v>4285.59</v>
+      </c>
+      <c r="H109" s="18" t="n">
+        <v>5277.07</v>
+      </c>
+      <c r="I109" s="18" t="n">
+        <v>4540.93</v>
+      </c>
+      <c r="J109" s="18" t="n">
+        <v>6517.29</v>
+      </c>
+      <c r="K109" s="34" t="n">
+        <v>20620.88</v>
+      </c>
+      <c r="L109" s="18" t="n">
+        <v>7182.17</v>
+      </c>
+      <c r="M109" s="18" t="n">
+        <v>9107.540000000001</v>
+      </c>
+      <c r="N109" s="18" t="n">
+        <v>8584.690000000001</v>
+      </c>
+      <c r="O109" s="18" t="n">
+        <v>8135.68</v>
+      </c>
+      <c r="P109" s="34" t="n">
+        <v>33010.08</v>
+      </c>
+      <c r="Q109" s="18" t="n">
+        <v>8944.6</v>
+      </c>
+      <c r="R109" s="18" t="n">
+        <v>9994.799999999999</v>
+      </c>
+      <c r="S109" s="18" t="n">
+        <v>9147.51</v>
+      </c>
+      <c r="T109" s="18" t="n">
+        <v>7139.79</v>
+      </c>
+      <c r="U109" s="34" t="n">
+        <v>35226.7</v>
+      </c>
+      <c r="V109" s="18" t="n">
+        <v>8127.99</v>
+      </c>
+      <c r="W109" s="18" t="n">
+        <v>9213.49</v>
+      </c>
+      <c r="X109" s="18" t="n">
+        <v>9317.610000000001</v>
+      </c>
+      <c r="Y109" s="18" t="n">
+        <v>10689.65</v>
+      </c>
+      <c r="Z109" s="34" t="n">
+        <v>37348.74</v>
+      </c>
+      <c r="AA109" s="18" t="n">
+        <v>9043.379999999999</v>
+      </c>
+      <c r="AB109" s="19" t="n">
+        <v>9937.709999999999</v>
+      </c>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>-991955.35</v>
+      </c>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="18" t="n">
+        <v>-35166.64</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>220659.62</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>-1118488.92</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>-937249.29</v>
+      </c>
+      <c r="K110" s="34" t="n">
+        <v>-1870245.23</v>
+      </c>
+      <c r="L110" s="18" t="n">
+        <v>155349.75</v>
+      </c>
+      <c r="M110" s="18" t="n">
+        <v>1417737.12</v>
+      </c>
+      <c r="N110" s="18" t="n">
+        <v>-234807.94</v>
+      </c>
+      <c r="O110" s="18" t="n">
+        <v>-1017110.83</v>
+      </c>
+      <c r="P110" s="34" t="n">
+        <v>321168.1</v>
+      </c>
+      <c r="Q110" s="18" t="n">
+        <v>651212.95</v>
+      </c>
+      <c r="R110" s="18" t="n">
+        <v>-271753.66</v>
+      </c>
+      <c r="S110" s="18" t="n">
+        <v>-854473.53</v>
+      </c>
+      <c r="T110" s="18" t="n">
+        <v>1173942.23</v>
+      </c>
+      <c r="U110" s="34" t="n">
+        <v>698927.99</v>
+      </c>
+      <c r="V110" s="18" t="n">
+        <v>1883124.15</v>
+      </c>
+      <c r="W110" s="18" t="n">
+        <v>-86609.06</v>
+      </c>
+      <c r="X110" s="18" t="n">
+        <v>187588.87</v>
+      </c>
+      <c r="Y110" s="18" t="n">
+        <v>-1959407.37</v>
+      </c>
+      <c r="Z110" s="34" t="n">
+        <v>24696.59</v>
+      </c>
+      <c r="AA110" s="18" t="n">
+        <v>2726657.22</v>
+      </c>
+      <c r="AB110" s="19" t="n">
+        <v>4527302.7</v>
+      </c>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="10" t="n"/>
+      <c r="AL110" s="10" t="n"/>
+      <c r="AM110" s="10" t="n"/>
+      <c r="AN110" s="10" t="n"/>
+      <c r="AO110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>-991955.35</v>
+      </c>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="18" t="n">
+        <v>4532301.46</v>
+      </c>
+      <c r="H111" s="18" t="n">
+        <v>220659.62</v>
+      </c>
+      <c r="I111" s="18" t="n">
+        <v>-1118488.92</v>
+      </c>
+      <c r="J111" s="18" t="n">
+        <v>-937249.29</v>
+      </c>
+      <c r="K111" s="34" t="n">
+        <v>2697222.87</v>
+      </c>
+      <c r="L111" s="18" t="n">
+        <v>2852572.62</v>
+      </c>
+      <c r="M111" s="18" t="n">
+        <v>1417737.12</v>
+      </c>
+      <c r="N111" s="18" t="n">
+        <v>-234807.95</v>
+      </c>
+      <c r="O111" s="18" t="n">
+        <v>-1017110.83</v>
+      </c>
+      <c r="P111" s="34" t="n">
+        <v>3018390.96</v>
+      </c>
+      <c r="Q111" s="18" t="n">
+        <v>3669603.92</v>
+      </c>
+      <c r="R111" s="18" t="n">
+        <v>-271753.66</v>
+      </c>
+      <c r="S111" s="18" t="n">
+        <v>-854473.54</v>
+      </c>
+      <c r="T111" s="18" t="n">
+        <v>1173942.24</v>
+      </c>
+      <c r="U111" s="34" t="n">
+        <v>3717318.96</v>
+      </c>
+      <c r="V111" s="18" t="n">
+        <v>5600443.11</v>
+      </c>
+      <c r="W111" s="18" t="n">
+        <v>-86609.06</v>
+      </c>
+      <c r="X111" s="18" t="n">
+        <v>3904907.83</v>
+      </c>
+      <c r="Y111" s="18" t="n">
+        <v>-5676726.33</v>
+      </c>
+      <c r="Z111" s="34" t="n">
+        <v>3742015.55</v>
+      </c>
+      <c r="AA111" s="18" t="n">
+        <v>6468672.77</v>
+      </c>
+      <c r="AB111" s="19" t="n">
+        <v>4527302.69</v>
+      </c>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21957,7 +22577,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36358,7 +36978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH72"/>
+  <dimension ref="A1:BH71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -37991,12 +38611,12 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>cohort:②BEP</t>
+          <t>cohort:④호황</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>코호트 ②BEP</t>
+          <t>코호트 ④호황</t>
         </is>
       </c>
       <c r="L13" s="26" t="n">
@@ -38050,45 +38670,6 @@
       <c r="AB13" s="26" t="n">
         <v>4.375</v>
       </c>
-      <c r="AD13" s="26" t="n">
-        <v>6.232</v>
-      </c>
-      <c r="AE13" s="26" t="n">
-        <v>40.062</v>
-      </c>
-      <c r="AF13" s="26" t="n">
-        <v>40.508</v>
-      </c>
-      <c r="AG13" s="26" t="n">
-        <v>40.953</v>
-      </c>
-      <c r="AH13" s="26" t="n">
-        <v>40.953</v>
-      </c>
-      <c r="AI13" s="26" t="n">
-        <v>40.062</v>
-      </c>
-      <c r="AJ13" s="26" t="n">
-        <v>40.508</v>
-      </c>
-      <c r="AK13" s="26" t="n">
-        <v>40.953</v>
-      </c>
-      <c r="AL13" s="26" t="n">
-        <v>40.953</v>
-      </c>
-      <c r="AM13" s="26" t="n">
-        <v>40.508</v>
-      </c>
-      <c r="AN13" s="26" t="n">
-        <v>40.508</v>
-      </c>
-      <c r="AO13" s="26" t="n">
-        <v>40.953</v>
-      </c>
-      <c r="AP13" s="26" t="n">
-        <v>22.702</v>
-      </c>
       <c r="AY13" s="26" t="n">
         <v>130.142</v>
       </c>
@@ -38102,27 +38683,18 @@
         <v>200.134</v>
       </c>
       <c r="BC13" s="26" t="n">
-        <v>59.82</v>
-      </c>
-      <c r="BD13" s="26" t="n">
-        <v>162.476</v>
-      </c>
-      <c r="BE13" s="26" t="n">
-        <v>162.476</v>
-      </c>
-      <c r="BF13" s="26" t="n">
-        <v>144.671</v>
+        <v>53.588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>cohort:③중마진</t>
+          <t>cohort:⑤초호황</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>코호트 ③중마진</t>
+          <t>코호트 ⑤초호황</t>
         </is>
       </c>
       <c r="AB14" s="26" t="n">
@@ -38132,1148 +38704,1122 @@
         <v>53.713</v>
       </c>
       <c r="AD14" s="26" t="n">
-        <v>101.652</v>
+        <v>124.101</v>
       </c>
       <c r="AE14" s="26" t="n">
-        <v>219.983</v>
+        <v>294.797</v>
       </c>
       <c r="AF14" s="26" t="n">
-        <v>372.155</v>
+        <v>447.8</v>
       </c>
       <c r="AG14" s="26" t="n">
-        <v>443.138</v>
+        <v>542.045</v>
       </c>
       <c r="AH14" s="26" t="n">
-        <v>443.138</v>
+        <v>544.477</v>
       </c>
       <c r="AI14" s="26" t="n">
-        <v>433.504</v>
+        <v>532.641</v>
       </c>
       <c r="AJ14" s="26" t="n">
-        <v>438.321</v>
+        <v>538.559</v>
       </c>
       <c r="AK14" s="26" t="n">
-        <v>443.138</v>
+        <v>544.477</v>
       </c>
       <c r="AL14" s="26" t="n">
-        <v>443.138</v>
+        <v>544.477</v>
       </c>
       <c r="AM14" s="26" t="n">
-        <v>438.321</v>
+        <v>538.559</v>
       </c>
       <c r="AN14" s="26" t="n">
-        <v>434.177</v>
+        <v>534.415</v>
       </c>
       <c r="AO14" s="26" t="n">
-        <v>405.023</v>
+        <v>506.362</v>
       </c>
       <c r="AP14" s="26" t="n">
-        <v>383.332</v>
+        <v>466.421</v>
       </c>
       <c r="AQ14" s="26" t="n">
-        <v>290.821</v>
+        <v>349.895</v>
       </c>
       <c r="AR14" s="26" t="n">
-        <v>184.5</v>
+        <v>244.231</v>
       </c>
       <c r="AS14" s="26" t="n">
-        <v>113.955</v>
+        <v>155.808</v>
       </c>
       <c r="AT14" s="26" t="n">
-        <v>61.808</v>
+        <v>86.67100000000001</v>
+      </c>
+      <c r="AU14" s="26" t="n">
+        <v>24.323</v>
+      </c>
+      <c r="AV14" s="26" t="n">
+        <v>16.485</v>
       </c>
       <c r="BC14" s="26" t="n">
-        <v>158.284</v>
+        <v>180.733</v>
       </c>
       <c r="BD14" s="26" t="n">
-        <v>1478.414</v>
+        <v>1829.119</v>
       </c>
       <c r="BE14" s="26" t="n">
-        <v>1758.101</v>
+        <v>2160.154</v>
       </c>
       <c r="BF14" s="26" t="n">
-        <v>1660.853</v>
+        <v>2045.757</v>
       </c>
       <c r="BG14" s="26" t="n">
-        <v>651.0839999999999</v>
+        <v>836.605</v>
+      </c>
+      <c r="BH14" s="26" t="n">
+        <v>40.808</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>cohort:④호황</t>
+          <t>hedge_ratio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>코호트 ④호황</t>
-        </is>
-      </c>
-      <c r="AD15" s="26" t="n">
-        <v>16.217</v>
-      </c>
-      <c r="AE15" s="26" t="n">
-        <v>34.752</v>
-      </c>
-      <c r="AF15" s="26" t="n">
-        <v>35.138</v>
-      </c>
-      <c r="AG15" s="26" t="n">
-        <v>57.955</v>
-      </c>
-      <c r="AH15" s="26" t="n">
-        <v>60.387</v>
-      </c>
-      <c r="AI15" s="26" t="n">
-        <v>59.074</v>
-      </c>
-      <c r="AJ15" s="26" t="n">
-        <v>59.731</v>
-      </c>
-      <c r="AK15" s="26" t="n">
-        <v>60.387</v>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>60.387</v>
-      </c>
-      <c r="AM15" s="26" t="n">
-        <v>59.731</v>
-      </c>
-      <c r="AN15" s="26" t="n">
-        <v>59.731</v>
-      </c>
-      <c r="AO15" s="26" t="n">
-        <v>60.387</v>
-      </c>
-      <c r="AP15" s="26" t="n">
-        <v>60.387</v>
-      </c>
-      <c r="AQ15" s="26" t="n">
-        <v>59.074</v>
-      </c>
-      <c r="AR15" s="26" t="n">
-        <v>59.731</v>
-      </c>
-      <c r="AS15" s="26" t="n">
-        <v>41.853</v>
-      </c>
-      <c r="AT15" s="26" t="n">
-        <v>24.863</v>
-      </c>
-      <c r="AU15" s="26" t="n">
-        <v>24.323</v>
-      </c>
-      <c r="AV15" s="26" t="n">
-        <v>16.485</v>
-      </c>
-      <c r="BC15" s="26" t="n">
-        <v>16.217</v>
-      </c>
-      <c r="BD15" s="26" t="n">
-        <v>188.232</v>
-      </c>
-      <c r="BE15" s="26" t="n">
-        <v>239.579</v>
-      </c>
-      <c r="BF15" s="26" t="n">
-        <v>240.236</v>
-      </c>
-      <c r="BG15" s="26" t="n">
-        <v>185.521</v>
-      </c>
-      <c r="BH15" s="26" t="n">
-        <v>40.808</v>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="W15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AA15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AF15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AG15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AK15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AM15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AO15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AS15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AU15" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AV15" s="21" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>hedge_ratio</t>
+          <t>hedge_rate</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="W16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="X16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Z16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AA16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AB16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AD16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AE16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AF16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AG16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AH16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AI16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AJ16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AK16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AL16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AM16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AN16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AO16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AQ16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AS16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AT16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AU16" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AV16" s="21" t="n">
-        <v>0.7</v>
+          <t>헤지환율</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>1193.96</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>1131.31</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>1129.71</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="S16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="T16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="U16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="W16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="X16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="Z16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="AA16" s="13" t="n">
+        <v>1133.43</v>
+      </c>
+      <c r="AB16" s="13" t="n">
+        <v>1184.07</v>
+      </c>
+      <c r="AC16" s="13" t="n">
+        <v>1315.33</v>
+      </c>
+      <c r="AD16" s="13" t="n">
+        <v>1383.31</v>
+      </c>
+      <c r="AE16" s="13" t="n">
+        <v>1424.95</v>
+      </c>
+      <c r="AF16" s="13" t="n">
+        <v>1447.25</v>
+      </c>
+      <c r="AG16" s="13" t="n">
+        <v>1452.71</v>
+      </c>
+      <c r="AH16" s="13" t="n">
+        <v>1452.57</v>
+      </c>
+      <c r="AI16" s="13" t="n">
+        <v>1452.57</v>
+      </c>
+      <c r="AJ16" s="13" t="n">
+        <v>1452.57</v>
+      </c>
+      <c r="AK16" s="13" t="n">
+        <v>1454.65</v>
+      </c>
+      <c r="AL16" s="13" t="n">
+        <v>1459.05</v>
+      </c>
+      <c r="AM16" s="13" t="n">
+        <v>1459.05</v>
+      </c>
+      <c r="AN16" s="13" t="n">
+        <v>1459</v>
+      </c>
+      <c r="AO16" s="13" t="n">
+        <v>1458.52</v>
+      </c>
+      <c r="AP16" s="13" t="n">
+        <v>1459.3</v>
+      </c>
+      <c r="AQ16" s="13" t="n">
+        <v>1469.78</v>
+      </c>
+      <c r="AR16" s="13" t="n">
+        <v>1478.89</v>
+      </c>
+      <c r="AS16" s="13" t="n">
+        <v>1482.93</v>
+      </c>
+      <c r="AT16" s="13" t="n">
+        <v>1478.22</v>
+      </c>
+      <c r="AU16" s="13" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="AV16" s="13" t="n">
+        <v>1419.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>hedge_rate</t>
+          <t>spot_assumed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>헤지환율</t>
+          <t>건조시점 환율(가정)</t>
         </is>
       </c>
       <c r="E17" s="13" t="n">
         <v>1193.96</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1193.96</v>
+        <v>1176.23</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1193.96</v>
+        <v>1193.92</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>1193.96</v>
+        <v>1219.69</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>1193.96</v>
+        <v>1187.81</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>1193.96</v>
+        <v>1117.97</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>1193.96</v>
+        <v>1114.99</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>1131.31</v>
+        <v>1121.13</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>1129.71</v>
+        <v>1159.91</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1183.5</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1205.78</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1262.09</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1341.93</v>
       </c>
       <c r="R17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1360.12</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1276.95</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1315.69</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1313.62</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1322.01</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1330.14</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1371.28</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1356.22</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1396.3</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1452.28</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1184.07</v>
+        <v>1398.52</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1315.33</v>
+        <v>1386.95</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1383.31</v>
+        <v>1449.19</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1424.95</v>
+        <v>1466.12</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1447.25</v>
+        <v>1501.75</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1452.71</v>
+        <v>1419.72</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1452.57</v>
+        <v>1353.36</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1452.57</v>
+        <v>1353.36</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1452.57</v>
+        <v>1353.36</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1454.65</v>
+        <v>1353.36</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1459.05</v>
+        <v>1353.36</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1459.05</v>
+        <v>1353.36</v>
       </c>
       <c r="AN17" s="13" t="n">
-        <v>1459</v>
+        <v>1353.36</v>
       </c>
       <c r="AO17" s="13" t="n">
-        <v>1458.52</v>
+        <v>1353.36</v>
       </c>
       <c r="AP17" s="13" t="n">
-        <v>1459.3</v>
+        <v>1353.36</v>
       </c>
       <c r="AQ17" s="13" t="n">
-        <v>1469.78</v>
+        <v>1353.36</v>
       </c>
       <c r="AR17" s="13" t="n">
-        <v>1478.89</v>
+        <v>1353.36</v>
       </c>
       <c r="AS17" s="13" t="n">
-        <v>1482.93</v>
+        <v>1353.36</v>
       </c>
       <c r="AT17" s="13" t="n">
-        <v>1478.22</v>
+        <v>1353.36</v>
       </c>
       <c r="AU17" s="13" t="n">
-        <v>1419.72</v>
+        <v>1353.36</v>
       </c>
       <c r="AV17" s="13" t="n">
-        <v>1419.72</v>
+        <v>1353.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>spot_assumed</t>
+          <t>applied_rate</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>건조시점 환율(가정)</t>
+          <t>적용환율</t>
         </is>
       </c>
       <c r="E18" s="13" t="n">
         <v>1193.96</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1176.23</v>
+        <v>1188.64</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1193.92</v>
+        <v>1193.95</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>1219.69</v>
+        <v>1201.68</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>1187.81</v>
+        <v>1192.12</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>1117.97</v>
+        <v>1171.16</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>1114.99</v>
+        <v>1170.27</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>1121.13</v>
+        <v>1128.26</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>1159.91</v>
+        <v>1138.77</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>1183.5</v>
+        <v>1148.45</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>1205.78</v>
+        <v>1155.13</v>
       </c>
       <c r="P18" s="13" t="n">
-        <v>1262.09</v>
+        <v>1172.03</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>1341.93</v>
+        <v>1195.98</v>
       </c>
       <c r="R18" s="13" t="n">
-        <v>1360.12</v>
+        <v>1201.44</v>
       </c>
       <c r="S18" s="13" t="n">
-        <v>1276.95</v>
+        <v>1176.49</v>
       </c>
       <c r="T18" s="13" t="n">
-        <v>1315.69</v>
+        <v>1188.11</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>1313.62</v>
+        <v>1187.49</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>1322.01</v>
+        <v>1190</v>
       </c>
       <c r="W18" s="13" t="n">
-        <v>1330.14</v>
+        <v>1192.44</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1371.28</v>
+        <v>1204.78</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1356.22</v>
+        <v>1200.27</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1396.3</v>
+        <v>1212.29</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1452.28</v>
+        <v>1229.08</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1398.52</v>
+        <v>1248.41</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1386.95</v>
+        <v>1336.82</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1449.19</v>
+        <v>1403.08</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1466.12</v>
+        <v>1437.3</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1501.75</v>
+        <v>1463.6</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1419.72</v>
+        <v>1442.82</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.81</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.81</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.81</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1424.26</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1427.34</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1427.34</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1427.31</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1426.97</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1427.52</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1434.85</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1441.23</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1444.06</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1440.76</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1399.81</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1353.36</v>
+        <v>1399.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>applied_rate</t>
+          <t>hedged_krw_m</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>적용환율</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>1193.96</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>1188.64</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>1193.95</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>1201.68</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>1192.12</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>1171.16</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>1170.27</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>1128.26</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>1138.77</v>
-      </c>
-      <c r="N19" s="13" t="n">
-        <v>1148.45</v>
-      </c>
-      <c r="O19" s="13" t="n">
-        <v>1155.13</v>
-      </c>
-      <c r="P19" s="13" t="n">
-        <v>1172.03</v>
-      </c>
-      <c r="Q19" s="13" t="n">
-        <v>1195.98</v>
-      </c>
-      <c r="R19" s="13" t="n">
-        <v>1201.44</v>
-      </c>
-      <c r="S19" s="13" t="n">
-        <v>1176.49</v>
-      </c>
-      <c r="T19" s="13" t="n">
-        <v>1188.11</v>
-      </c>
-      <c r="U19" s="13" t="n">
-        <v>1187.49</v>
-      </c>
-      <c r="V19" s="13" t="n">
-        <v>1190</v>
-      </c>
-      <c r="W19" s="13" t="n">
-        <v>1192.44</v>
-      </c>
-      <c r="X19" s="13" t="n">
-        <v>1204.78</v>
-      </c>
-      <c r="Y19" s="13" t="n">
-        <v>1200.27</v>
-      </c>
-      <c r="Z19" s="13" t="n">
-        <v>1212.29</v>
-      </c>
-      <c r="AA19" s="13" t="n">
-        <v>1229.08</v>
-      </c>
-      <c r="AB19" s="13" t="n">
-        <v>1248.41</v>
-      </c>
-      <c r="AC19" s="13" t="n">
-        <v>1336.82</v>
-      </c>
-      <c r="AD19" s="13" t="n">
-        <v>1403.08</v>
-      </c>
-      <c r="AE19" s="13" t="n">
-        <v>1437.3</v>
-      </c>
-      <c r="AF19" s="13" t="n">
-        <v>1463.6</v>
-      </c>
-      <c r="AG19" s="13" t="n">
-        <v>1442.82</v>
-      </c>
-      <c r="AH19" s="13" t="n">
-        <v>1422.81</v>
-      </c>
-      <c r="AI19" s="13" t="n">
-        <v>1422.81</v>
-      </c>
-      <c r="AJ19" s="13" t="n">
-        <v>1422.81</v>
-      </c>
-      <c r="AK19" s="13" t="n">
-        <v>1424.26</v>
-      </c>
-      <c r="AL19" s="13" t="n">
-        <v>1427.34</v>
-      </c>
-      <c r="AM19" s="13" t="n">
-        <v>1427.34</v>
-      </c>
-      <c r="AN19" s="13" t="n">
-        <v>1427.31</v>
-      </c>
-      <c r="AO19" s="13" t="n">
-        <v>1426.97</v>
-      </c>
-      <c r="AP19" s="13" t="n">
-        <v>1427.52</v>
-      </c>
-      <c r="AQ19" s="13" t="n">
-        <v>1434.85</v>
-      </c>
-      <c r="AR19" s="13" t="n">
-        <v>1441.23</v>
-      </c>
-      <c r="AS19" s="13" t="n">
-        <v>1444.06</v>
-      </c>
-      <c r="AT19" s="13" t="n">
-        <v>1440.76</v>
-      </c>
-      <c r="AU19" s="13" t="n">
-        <v>1399.81</v>
-      </c>
-      <c r="AV19" s="13" t="n">
-        <v>1399.81</v>
+          <t>헤지적용 원화매출(백만원)</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>1715.9</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>5612.7</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>5576.5</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>5612.6</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>5629.1</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>5530.2</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>5405.8</v>
+      </c>
+      <c r="L19" s="18" t="n">
+        <v>38584.8</v>
+      </c>
+      <c r="M19" s="18" t="n">
+        <v>66994.60000000001</v>
+      </c>
+      <c r="N19" s="18" t="n">
+        <v>77048.8</v>
+      </c>
+      <c r="O19" s="18" t="n">
+        <v>75812.5</v>
+      </c>
+      <c r="P19" s="18" t="n">
+        <v>77775.89999999999</v>
+      </c>
+      <c r="Q19" s="18" t="n">
+        <v>80237.5</v>
+      </c>
+      <c r="R19" s="18" t="n">
+        <v>80603.60000000001</v>
+      </c>
+      <c r="S19" s="18" t="n">
+        <v>77213.8</v>
+      </c>
+      <c r="T19" s="18" t="n">
+        <v>78843</v>
+      </c>
+      <c r="U19" s="18" t="n">
+        <v>79667.7</v>
+      </c>
+      <c r="V19" s="18" t="n">
+        <v>79836.60000000001</v>
+      </c>
+      <c r="W19" s="18" t="n">
+        <v>79130.60000000001</v>
+      </c>
+      <c r="X19" s="18" t="n">
+        <v>79949.7</v>
+      </c>
+      <c r="Y19" s="18" t="n">
+        <v>80525.10000000001</v>
+      </c>
+      <c r="Z19" s="18" t="n">
+        <v>81331.8</v>
+      </c>
+      <c r="AA19" s="18" t="n">
+        <v>80665.89999999999</v>
+      </c>
+      <c r="AB19" s="18" t="n">
+        <v>29829</v>
+      </c>
+      <c r="AC19" s="18" t="n">
+        <v>94238.89999999999</v>
+      </c>
+      <c r="AD19" s="18" t="n">
+        <v>196518.1</v>
+      </c>
+      <c r="AE19" s="18" t="n">
+        <v>440669.5</v>
+      </c>
+      <c r="AF19" s="18" t="n">
+        <v>672859.3</v>
+      </c>
+      <c r="AG19" s="18" t="n">
+        <v>799472.2</v>
+      </c>
+      <c r="AH19" s="18" t="n">
+        <v>791845.8</v>
+      </c>
+      <c r="AI19" s="18" t="n">
+        <v>774631.7</v>
+      </c>
+      <c r="AJ19" s="18" t="n">
+        <v>783238.7</v>
+      </c>
+      <c r="AK19" s="18" t="n">
+        <v>787055.9</v>
+      </c>
+      <c r="AL19" s="18" t="n">
+        <v>777156.8</v>
+      </c>
+      <c r="AM19" s="18" t="n">
+        <v>768709.5</v>
+      </c>
+      <c r="AN19" s="18" t="n">
+        <v>762773.6</v>
+      </c>
+      <c r="AO19" s="18" t="n">
+        <v>722565</v>
+      </c>
+      <c r="AP19" s="18" t="n">
+        <v>665825.3</v>
+      </c>
+      <c r="AQ19" s="18" t="n">
+        <v>502048.9</v>
+      </c>
+      <c r="AR19" s="18" t="n">
+        <v>351994.4</v>
+      </c>
+      <c r="AS19" s="18" t="n">
+        <v>224995.8</v>
+      </c>
+      <c r="AT19" s="18" t="n">
+        <v>124872.9</v>
+      </c>
+      <c r="AU19" s="18" t="n">
+        <v>34047.4</v>
+      </c>
+      <c r="AV19" s="18" t="n">
+        <v>23076.6</v>
+      </c>
+      <c r="AW19" s="18" t="n">
+        <v>7328.6</v>
+      </c>
+      <c r="AX19" s="18" t="n">
+        <v>22348.4</v>
+      </c>
+      <c r="AY19" s="18" t="n">
+        <v>188034</v>
+      </c>
+      <c r="AZ19" s="18" t="n">
+        <v>314429.5</v>
+      </c>
+      <c r="BA19" s="18" t="n">
+        <v>315561.1</v>
+      </c>
+      <c r="BB19" s="18" t="n">
+        <v>320937.2</v>
+      </c>
+      <c r="BC19" s="18" t="n">
+        <v>401251.9</v>
+      </c>
+      <c r="BD19" s="18" t="n">
+        <v>2704846.8</v>
+      </c>
+      <c r="BE19" s="18" t="n">
+        <v>3122083.1</v>
+      </c>
+      <c r="BF19" s="18" t="n">
+        <v>2919873.4</v>
+      </c>
+      <c r="BG19" s="18" t="n">
+        <v>1203912</v>
+      </c>
+      <c r="BH19" s="18" t="n">
+        <v>57124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>hedged_krw_m</t>
+          <t>target_opm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>헤지적용 원화매출(백만원)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>1715.9</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>5612.7</v>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>5576.5</v>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>5612.6</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>5629.1</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>5530.2</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>5405.8</v>
-      </c>
-      <c r="L20" s="18" t="n">
-        <v>38584.8</v>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>66994.60000000001</v>
-      </c>
-      <c r="N20" s="18" t="n">
-        <v>77048.8</v>
-      </c>
-      <c r="O20" s="18" t="n">
-        <v>75812.5</v>
-      </c>
-      <c r="P20" s="18" t="n">
-        <v>77775.89999999999</v>
-      </c>
-      <c r="Q20" s="18" t="n">
-        <v>80237.5</v>
-      </c>
-      <c r="R20" s="18" t="n">
-        <v>80603.60000000001</v>
-      </c>
-      <c r="S20" s="18" t="n">
-        <v>77213.8</v>
-      </c>
-      <c r="T20" s="18" t="n">
-        <v>78843</v>
-      </c>
-      <c r="U20" s="18" t="n">
-        <v>79667.7</v>
-      </c>
-      <c r="V20" s="18" t="n">
-        <v>79836.60000000001</v>
-      </c>
-      <c r="W20" s="18" t="n">
-        <v>79130.60000000001</v>
-      </c>
-      <c r="X20" s="18" t="n">
-        <v>79949.7</v>
-      </c>
-      <c r="Y20" s="18" t="n">
-        <v>80525.10000000001</v>
-      </c>
-      <c r="Z20" s="18" t="n">
-        <v>81331.8</v>
-      </c>
-      <c r="AA20" s="18" t="n">
-        <v>80665.89999999999</v>
-      </c>
-      <c r="AB20" s="18" t="n">
-        <v>29829</v>
-      </c>
-      <c r="AC20" s="18" t="n">
-        <v>94238.89999999999</v>
-      </c>
-      <c r="AD20" s="18" t="n">
-        <v>196518.1</v>
-      </c>
-      <c r="AE20" s="18" t="n">
-        <v>440669.5</v>
-      </c>
-      <c r="AF20" s="18" t="n">
-        <v>672859.3</v>
-      </c>
-      <c r="AG20" s="18" t="n">
-        <v>799472.2</v>
-      </c>
-      <c r="AH20" s="18" t="n">
-        <v>791845.8</v>
-      </c>
-      <c r="AI20" s="18" t="n">
-        <v>774631.7</v>
-      </c>
-      <c r="AJ20" s="18" t="n">
-        <v>783238.7</v>
-      </c>
-      <c r="AK20" s="18" t="n">
-        <v>787055.9</v>
-      </c>
-      <c r="AL20" s="18" t="n">
-        <v>777156.8</v>
-      </c>
-      <c r="AM20" s="18" t="n">
-        <v>768709.5</v>
-      </c>
-      <c r="AN20" s="18" t="n">
-        <v>762773.6</v>
-      </c>
-      <c r="AO20" s="18" t="n">
-        <v>722565</v>
-      </c>
-      <c r="AP20" s="18" t="n">
-        <v>665825.3</v>
-      </c>
-      <c r="AQ20" s="18" t="n">
-        <v>502048.9</v>
-      </c>
-      <c r="AR20" s="18" t="n">
-        <v>351994.4</v>
-      </c>
-      <c r="AS20" s="18" t="n">
-        <v>224995.8</v>
-      </c>
-      <c r="AT20" s="18" t="n">
-        <v>124872.9</v>
-      </c>
-      <c r="AU20" s="18" t="n">
-        <v>34047.4</v>
-      </c>
-      <c r="AV20" s="18" t="n">
-        <v>23076.6</v>
-      </c>
-      <c r="AW20" s="18" t="n">
-        <v>7328.6</v>
-      </c>
-      <c r="AX20" s="18" t="n">
-        <v>22348.4</v>
-      </c>
-      <c r="AY20" s="18" t="n">
-        <v>188034</v>
-      </c>
-      <c r="AZ20" s="18" t="n">
-        <v>314429.5</v>
-      </c>
-      <c r="BA20" s="18" t="n">
-        <v>315561.1</v>
-      </c>
-      <c r="BB20" s="18" t="n">
-        <v>320937.2</v>
-      </c>
-      <c r="BC20" s="18" t="n">
-        <v>401251.9</v>
-      </c>
-      <c r="BD20" s="18" t="n">
-        <v>2704846.8</v>
-      </c>
-      <c r="BE20" s="18" t="n">
-        <v>3122083.1</v>
-      </c>
-      <c r="BF20" s="18" t="n">
-        <v>2919873.4</v>
-      </c>
-      <c r="BG20" s="18" t="n">
-        <v>1203912</v>
-      </c>
-      <c r="BH20" s="18" t="n">
-        <v>57124</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>target_opm</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
           <t>타겟 OPM(코호트)</t>
         </is>
       </c>
-      <c r="L21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AC21" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AD21" s="21" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="AE21" s="21" t="n">
-        <v>0.0491</v>
-      </c>
-      <c r="AF21" s="21" t="n">
-        <v>0.0494</v>
-      </c>
-      <c r="AG21" s="21" t="n">
-        <v>0.0516</v>
-      </c>
-      <c r="AH21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AI21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AJ21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AK21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AL21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AM21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AN21" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="AO21" s="21" t="n">
-        <v>0.0519</v>
-      </c>
-      <c r="AP21" s="21" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="AQ21" s="21" t="n">
-        <v>0.0584</v>
-      </c>
-      <c r="AR21" s="21" t="n">
-        <v>0.0622</v>
-      </c>
-      <c r="AS21" s="21" t="n">
-        <v>0.0634</v>
-      </c>
-      <c r="AT21" s="21" t="n">
-        <v>0.0643</v>
-      </c>
-      <c r="AU21" s="21" t="n">
+      <c r="L20" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="AV21" s="21" t="n">
+      <c r="M20" s="21" t="n">
         <v>0.1</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AA20" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB20" s="21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AD20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AE20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AG20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AH20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AK20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AL20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AM20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AN20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AP20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AQ20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AS20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AT20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AU20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AV20" s="21" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>계약 원장(contracts.json 기반)</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>계약 원장(contracts.json 기반)</t>
+          <t>rcp</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>ships</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>amt_krw_m</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>amt_usd_m</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>fx_at_sign</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>signed</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>curve</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>estimated_series</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>rcp</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>ships</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>amt_krw_m</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>amt_usd_m</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>fx_at_sign</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>signed</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>curve</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>estimated_series</t>
-        </is>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20251121800424</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VLCC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>762700</v>
+      </c>
+      <c r="E24" t="n">
+        <v>526.294</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1449.19</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2029-08-13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20251121800424</t>
+          <t>20251124800131</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>762700</v>
+        <v>1603700</v>
       </c>
       <c r="E25" t="n">
-        <v>526.294</v>
+        <v>1106.618</v>
       </c>
       <c r="F25" t="n">
         <v>1449.19</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2029-08-13</t>
+          <t>2029-04-30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -39288,7 +39834,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20251124800131</t>
+          <t>20251124800132</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -39297,13 +39843,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1603700</v>
+        <v>534600</v>
       </c>
       <c r="E26" t="n">
-        <v>1106.618</v>
+        <v>368.896</v>
       </c>
       <c r="F26" t="n">
         <v>1449.19</v>
@@ -39320,12 +39866,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-07-14</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -39340,39 +39881,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20251124800132</t>
+          <t>20251202800104</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>534600</v>
+        <v>367200</v>
       </c>
       <c r="E27" t="n">
-        <v>368.896</v>
+        <v>253.383</v>
       </c>
       <c r="F27" t="n">
         <v>1449.19</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2028-07-14</t>
+          <t>2028-12-31</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -39381,50 +39927,42 @@
         </is>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20251202800104</t>
+          <t>20251215800970</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LNGC</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>367200</v>
+        <v>140700</v>
       </c>
       <c r="E28" t="n">
-        <v>253.383</v>
+        <v>117.843</v>
       </c>
       <c r="F28" t="n">
-        <v>1449.19</v>
+        <v>1193.96</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -39439,36 +39977,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20251215800970</t>
+          <t>20251219800421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>LNGC</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>140700</v>
+        <v>1047200</v>
       </c>
       <c r="E29" t="n">
-        <v>117.843</v>
+        <v>769.491</v>
       </c>
       <c r="F29" t="n">
-        <v>1193.96</v>
+        <v>1360.9</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2029-02-02</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -39483,44 +40029,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20251219800421</t>
+          <t>20251219800433</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1047200</v>
+        <v>689600</v>
       </c>
       <c r="E30" t="n">
-        <v>769.491</v>
+        <v>475.852</v>
       </c>
       <c r="F30" t="n">
-        <v>1360.9</v>
+        <v>1449.19</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2029-02-02</t>
+          <t>2028-11-20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -39529,50 +40075,45 @@
         </is>
       </c>
       <c r="L30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20251219800433</t>
+          <t>20251224800162</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>689600</v>
+        <v>375000</v>
       </c>
       <c r="E31" t="n">
-        <v>475.852</v>
+        <v>258.765</v>
       </c>
       <c r="F31" t="n">
         <v>1449.19</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2028-11-20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>②BEP</t>
+          <t>2028-07-31</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -39587,39 +40128,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20251224800162</t>
+          <t>20251226800855</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>375000</v>
+        <v>844700</v>
       </c>
       <c r="E32" t="n">
-        <v>258.765</v>
+        <v>582.877</v>
       </c>
       <c r="F32" t="n">
         <v>1449.19</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2028-07-31</t>
+          <t>2029-12-20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -39628,45 +40169,45 @@
         </is>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20251226800855</t>
+          <t>20260106800156</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NAVAL</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>844700</v>
+        <v>1499300</v>
       </c>
       <c r="E33" t="n">
-        <v>582.877</v>
+        <v>1022.631</v>
       </c>
       <c r="F33" t="n">
-        <v>1449.19</v>
+        <v>1466.12</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2029-12-20</t>
+          <t>2029-03-27</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -39675,45 +40216,50 @@
         </is>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260106800156</t>
+          <t>20260116800207</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1499300</v>
+        <v>175800</v>
       </c>
       <c r="E34" t="n">
-        <v>1022.631</v>
+        <v>119.908</v>
       </c>
       <c r="F34" t="n">
         <v>1466.12</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2029-03-27</t>
+          <t>2028-05-31</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -39722,50 +40268,45 @@
         </is>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260116800207</t>
+          <t>20260120800211</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>175800</v>
+        <v>481600</v>
       </c>
       <c r="E35" t="n">
-        <v>119.908</v>
+        <v>328.486</v>
       </c>
       <c r="F35" t="n">
         <v>1466.12</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2028-05-31</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-06-30</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -39780,39 +40321,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260120800211</t>
+          <t>20260202800947</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>481600</v>
+        <v>357500</v>
       </c>
       <c r="E36" t="n">
-        <v>328.486</v>
+        <v>243.841</v>
       </c>
       <c r="F36" t="n">
         <v>1466.12</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -39821,13 +40367,13 @@
         </is>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260202800947</t>
+          <t>20260226800208</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -39839,32 +40385,27 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>357500</v>
+        <v>367800</v>
       </c>
       <c r="E37" t="n">
-        <v>243.841</v>
+        <v>250.866</v>
       </c>
       <c r="F37" t="n">
         <v>1466.12</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -39879,39 +40420,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260226800208</t>
+          <t>20260227800230</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>367800</v>
+        <v>372400</v>
       </c>
       <c r="E38" t="n">
-        <v>250.866</v>
+        <v>254.004</v>
       </c>
       <c r="F38" t="n">
         <v>1466.12</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -39926,39 +40467,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260227800230</t>
+          <t>20260304800002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>372400</v>
+        <v>529300</v>
       </c>
       <c r="E39" t="n">
-        <v>254.004</v>
+        <v>365.239</v>
       </c>
       <c r="F39" t="n">
-        <v>1466.12</v>
+        <v>1449.19</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -39973,44 +40519,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260304800002</t>
+          <t>20260305800849</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>529300</v>
+        <v>1487200</v>
       </c>
       <c r="E40" t="n">
-        <v>365.239</v>
+        <v>1014.378</v>
       </c>
       <c r="F40" t="n">
-        <v>1449.19</v>
+        <v>1466.12</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -40025,39 +40566,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260305800849</t>
+          <t>20260306800225</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>1487200</v>
+        <v>263200</v>
       </c>
       <c r="E41" t="n">
-        <v>1014.378</v>
+        <v>179.521</v>
       </c>
       <c r="F41" t="n">
         <v>1466.12</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2029-05-31</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -40066,50 +40612,50 @@
         </is>
       </c>
       <c r="L41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260306800225</t>
+          <t>20260310800414</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>263200</v>
+        <v>340200</v>
       </c>
       <c r="E42" t="n">
-        <v>179.521</v>
+        <v>232.041</v>
       </c>
       <c r="F42" t="n">
         <v>1466.12</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
+          <t>2028-12-29</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -40118,50 +40664,45 @@
         </is>
       </c>
       <c r="L42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260310800414</t>
+          <t>20260316800234</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>340200</v>
+        <v>823700</v>
       </c>
       <c r="E43" t="n">
-        <v>232.041</v>
+        <v>561.823</v>
       </c>
       <c r="F43" t="n">
         <v>1466.12</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2028-12-29</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -40176,39 +40717,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260316800234</t>
+          <t>20260403800582</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>823700</v>
+        <v>349800</v>
       </c>
       <c r="E44" t="n">
-        <v>561.823</v>
+        <v>232.928</v>
       </c>
       <c r="F44" t="n">
-        <v>1466.12</v>
+        <v>1501.75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2029-03-30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -40217,28 +40763,28 @@
         </is>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260403800582</t>
+          <t>20260403800587</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>349800</v>
+        <v>611700</v>
       </c>
       <c r="E45" t="n">
-        <v>232.928</v>
+        <v>407.325</v>
       </c>
       <c r="F45" t="n">
         <v>1501.75</v>
@@ -40255,12 +40801,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2029-03-30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -40269,45 +40810,50 @@
         </is>
       </c>
       <c r="L45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260403800587</t>
+          <t>20260408800703</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>611700</v>
+        <v>770200</v>
       </c>
       <c r="E46" t="n">
-        <v>407.325</v>
+        <v>512.8680000000001</v>
       </c>
       <c r="F46" t="n">
         <v>1501.75</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -40322,44 +40868,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260408800703</t>
+          <t>20260416800167</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>770200</v>
+        <v>346600</v>
       </c>
       <c r="E47" t="n">
-        <v>512.8680000000001</v>
+        <v>230.797</v>
       </c>
       <c r="F47" t="n">
         <v>1501.75</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2029-04-30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -40374,7 +40920,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260416800167</t>
+          <t>20260417800196</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -40383,35 +40929,30 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>346600</v>
+        <v>674700</v>
       </c>
       <c r="E48" t="n">
-        <v>230.797</v>
+        <v>449.276</v>
       </c>
       <c r="F48" t="n">
         <v>1501.75</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -40426,39 +40967,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260417800196</t>
+          <t>20260422800051</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>674700</v>
+        <v>514800</v>
       </c>
       <c r="E49" t="n">
-        <v>449.276</v>
+        <v>342.8</v>
       </c>
       <c r="F49" t="n">
         <v>1501.75</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -40467,28 +41008,25 @@
         </is>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260422800051</t>
+          <t>20260422800184</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAVAL</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D50" t="n">
-        <v>514800</v>
+        <v>627100</v>
       </c>
       <c r="E50" t="n">
-        <v>342.8</v>
+        <v>417.579</v>
       </c>
       <c r="F50" t="n">
         <v>1501.75</v>
@@ -40505,7 +41043,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2030-10-21</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -40520,36 +41058,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260422800184</t>
+          <t>20260504800307</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>627100</v>
+        <v>504800</v>
       </c>
       <c r="E51" t="n">
-        <v>417.579</v>
+        <v>336.141</v>
       </c>
       <c r="F51" t="n">
         <v>1501.75</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2030-10-21</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -40564,39 +41105,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260504800307</t>
+          <t>20260508800186</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>504800</v>
+        <v>1778700</v>
       </c>
       <c r="E52" t="n">
-        <v>336.141</v>
+        <v>1184.418</v>
       </c>
       <c r="F52" t="n">
         <v>1501.75</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -40605,45 +41146,50 @@
         </is>
       </c>
       <c r="L52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260508800186</t>
+          <t>20260513800195</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1778700</v>
+        <v>748500</v>
       </c>
       <c r="E53" t="n">
-        <v>1184.418</v>
+        <v>498.419</v>
       </c>
       <c r="F53" t="n">
         <v>1501.75</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-07-23</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -40652,13 +41198,13 @@
         </is>
       </c>
       <c r="L53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260513800195</t>
+          <t>20260514800347</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -40670,32 +41216,27 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>748500</v>
+        <v>743900</v>
       </c>
       <c r="E54" t="n">
-        <v>498.419</v>
+        <v>495.355</v>
       </c>
       <c r="F54" t="n">
         <v>1501.75</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2029-07-23</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-03-30</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -40704,45 +41245,50 @@
         </is>
       </c>
       <c r="L54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260514800347</t>
+          <t>20260521800360</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>743900</v>
+        <v>1078200</v>
       </c>
       <c r="E55" t="n">
-        <v>495.355</v>
+        <v>717.962</v>
       </c>
       <c r="F55" t="n">
         <v>1501.75</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2029-03-30</t>
+          <t>2029-12-20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -40757,7 +41303,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260521800360</t>
+          <t>20260601800400</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -40766,35 +41312,30 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>1078200</v>
+        <v>1416100</v>
       </c>
       <c r="E56" t="n">
-        <v>717.962</v>
+        <v>942.967</v>
       </c>
       <c r="F56" t="n">
         <v>1501.75</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2029-12-20</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2030-06-30</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -40809,7 +41350,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260601800400</t>
+          <t>20260629800351</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -40818,30 +41359,35 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1416100</v>
+        <v>366000</v>
       </c>
       <c r="E57" t="n">
-        <v>942.967</v>
+        <v>243.716</v>
       </c>
       <c r="F57" t="n">
         <v>1501.75</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2030-06-30</t>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -40850,50 +41396,45 @@
         </is>
       </c>
       <c r="L57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260629800351</t>
+          <t>20260701800239</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>366000</v>
+        <v>492800</v>
       </c>
       <c r="E58" t="n">
-        <v>243.716</v>
+        <v>328.15</v>
       </c>
       <c r="F58" t="n">
         <v>1501.75</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2029-12-31</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -40908,86 +41449,91 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260701800239</t>
+          <t>20260709800139</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>469900</v>
+      </c>
+      <c r="E59" t="n">
+        <v>330.981</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2029-06-30</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L59" t="b">
         <v>1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>492800</v>
-      </c>
-      <c r="E59" t="n">
-        <v>328.15</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1501.75</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2029-05-31</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="L59" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260709800139</t>
+          <t>20260713800202</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>469900</v>
+        <v>545600</v>
       </c>
       <c r="E60" t="n">
-        <v>330.981</v>
+        <v>384.301</v>
       </c>
       <c r="F60" t="n">
         <v>1419.72</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2030-05-31</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -41002,44 +41548,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260713800202</t>
+          <t>20260810800150</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VLGC</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>3</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D61" t="n">
-        <v>545600</v>
+        <v>956000</v>
       </c>
       <c r="E61" t="n">
-        <v>384.301</v>
+        <v>673.372</v>
       </c>
       <c r="F61" t="n">
         <v>1419.72</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2030-05-31</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>④호황</t>
+          <t>2030-07-30</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -41048,42 +41586,45 @@
         </is>
       </c>
       <c r="L61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260810800150</t>
+          <t>20260824800125</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>956000</v>
+        <v>515400</v>
       </c>
       <c r="E62" t="n">
-        <v>673.372</v>
+        <v>363.029</v>
       </c>
       <c r="F62" t="n">
         <v>1419.72</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2030-07-30</t>
+          <t>2030-03-31</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -41092,45 +41633,50 @@
         </is>
       </c>
       <c r="L62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260824800125</t>
+          <t>20260903800523</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>OFFSH</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>515400</v>
+        <v>878100</v>
       </c>
       <c r="E63" t="n">
-        <v>363.029</v>
+        <v>783.039</v>
       </c>
       <c r="F63" t="n">
-        <v>1419.72</v>
+        <v>1121.4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2030-03-31</t>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -41139,50 +41685,42 @@
         </is>
       </c>
       <c r="L63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260903800523</t>
+          <t>20260908800414</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OFFSH</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D64" t="n">
-        <v>878100</v>
+        <v>333000</v>
       </c>
       <c r="E64" t="n">
-        <v>783.039</v>
+        <v>287.091</v>
       </c>
       <c r="F64" t="n">
-        <v>1121.4</v>
+        <v>1159.91</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>②BEP</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -41197,36 +41735,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260908800414</t>
+          <t>20260930800164</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>333000</v>
+        <v>1953900</v>
       </c>
       <c r="E65" t="n">
-        <v>287.091</v>
+        <v>1485.076</v>
       </c>
       <c r="F65" t="n">
-        <v>1159.91</v>
+        <v>1315.69</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -41239,89 +41780,42 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260930800164</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>OFFSH</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1953900</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1485.076</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1315.69</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2027-06-01</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="L66" t="b">
-        <v>0</v>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
+          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 22건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 22건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
+          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 7%, ③중마진 80%, ④호황 13%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 7%, ③중마진 80%, ④호황 13% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
+          <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>⚠ 정기보고서 부문 매출(3개월분)을 만들 수 없어 화해 없음</t>
         </is>
@@ -48457,7 +48951,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>48471.7</v>
+        <v>55023.1</v>
       </c>
     </row>
     <row r="30">
@@ -48477,7 +48971,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.66</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="32">
@@ -48497,7 +48991,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2311</v>
+        <v>0.2624</v>
       </c>
     </row>
     <row r="34">
@@ -48507,7 +49001,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="35">
@@ -48517,7 +49011,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>539000</v>
+        <v>612400</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66101억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66085억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68341억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68322억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72257억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72239억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76505억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76487억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 81467억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 81450억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 86550억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 86534억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91777억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91761억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95826억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95812억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98590억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98578억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66101억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66085억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68341억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68322억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72257억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72239억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76505억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76487억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 81467억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 81450억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 86550억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 86534억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91777억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91761억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95826억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95812억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98590억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98578억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174629억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 186852억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 186846억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191133억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191124억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 204881억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 204869억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 219578억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 219562억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 235249억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 235231억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 243228억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 243207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 260656억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 260632억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 174629억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 174627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 186852억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 186846억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191133억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191124억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 204881억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 204869억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 219578억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 219562억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 235249억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 235231억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 243228억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 243207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 260656억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 260632억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52173.4</v>
+        <v>52163.4</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.26</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2488</v>
+        <v>0.2487</v>
       </c>
     </row>
     <row r="34">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>326500</v>
+        <v>318000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>317000</v>
+        <v>315000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>326000</v>
+        <v>323333.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9445,33 +9445,33 @@
         <v>0.216028511</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.143190334</v>
+        <v>0.142915298</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.183492873</v>
+        <v>0.183171287</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.141112015</v>
+        <v>0.140821438</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169899434</v>
+        <v>0.169630757</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.232461037</v>
+        <v>0.232502488</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.266447424</v>
+        <v>0.266556701</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.270143598</v>
+        <v>0.270253352</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.252558461</v>
+        <v>0.252660156</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.210190441</v>
+        <v>0.210286204</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.155847303</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.155748294</v>
+        <v>0.155748422</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.15574832</v>
+        <v>0.155748294</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.15573892</v>
+        <v>0.155738919</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.155711892</v>
+        <v>0.155711957</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.155692099</v>
+        <v>0.155692193</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.155672243</v>
+        <v>0.155672267</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.155652507</v>
+        <v>0.155652496</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.155602503</v>
+        <v>0.155602588</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.155529698</v>
+        <v>0.155529725</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.003514836</v>
+        <v>-0.006243027</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.003271131</v>
+        <v>0.002970843</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.00598699</v>
+        <v>-0.002614163</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.895478556</v>
+        <v>8697.892412749999</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002844482</v>
+        <v>-0.002264879</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.004812724</v>
+        <v>-0.003687274</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.002724579</v>
+        <v>-0.00239325</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.893653011</v>
+        <v>8697.891794404</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.00317619</v>
+        <v>-0.006586482</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.006671081</v>
+        <v>-0.001070063</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004410641</v>
+        <v>0.001563051</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.00535832</v>
+        <v>-0.00684972</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.006076084</v>
+        <v>-0.004820371</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.900751345</v>
+        <v>8697.902263468</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.002731222</v>
+        <v>-0.009696305000000001</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.000774366</v>
+        <v>-0.002236226</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.005507986</v>
+        <v>0.002016013</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.896710743</v>
+        <v>8697.890905613</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.004682261</v>
+        <v>-0.002746641</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002722228</v>
+        <v>0.001726244</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09654497200000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.08943116800000001</v>
+        <v>0.089409878</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.08530268000000001</v>
+        <v>0.085281384</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.02753237</v>
+        <v>0.027512483</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.086041592</v>
+        <v>0.08602697500000001</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.084690052</v>
+        <v>0.084678687</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.083256251</v>
+        <v>0.083247656</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039130015</v>
+        <v>0.03911972</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082254207</v>
+        <v>0.082250138</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.078514262</v>
+        <v>0.078512183</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.07654037599999999</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.072218105</v>
+        <v>0.072200974</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.06999008499999999</v>
+        <v>0.069972363</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.022913402</v>
+        <v>0.022896593</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07192999799999999</v>
+        <v>0.071917144</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.071732134</v>
+        <v>0.071721717</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.07137036200000001</v>
+        <v>0.071362199</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.033915844</v>
+        <v>0.033906512</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.071653175</v>
+        <v>0.07164866</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.06907182100000001</v>
+        <v>0.06906912699999999</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>326500</v>
+        <v>318000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269005504941</v>
+        <v>0.1989270050870875</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842985053168442</v>
+        <v>0.04842986213712466</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600276276448862</v>
+        <v>0.7600275607956595</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816788900288804</v>
+        <v>0.02816795178321848</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311622497288482</v>
+        <v>0.1311627713429104</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39551,79 +39551,79 @@
         <v>34.199</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>58.831</v>
+        <v>58.893</v>
       </c>
       <c r="N5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="O5" s="27" t="n">
-        <v>65.631</v>
+        <v>65.82599999999999</v>
       </c>
       <c r="P5" s="27" t="n">
-        <v>66.36</v>
+        <v>66.557</v>
       </c>
       <c r="Q5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="R5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="S5" s="27" t="n">
-        <v>65.631</v>
+        <v>65.82599999999999</v>
       </c>
       <c r="T5" s="27" t="n">
-        <v>66.36</v>
+        <v>66.557</v>
       </c>
       <c r="U5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="V5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="W5" s="27" t="n">
-        <v>66.36</v>
+        <v>66.557</v>
       </c>
       <c r="X5" s="27" t="n">
-        <v>66.36</v>
+        <v>66.557</v>
       </c>
       <c r="Y5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="Z5" s="27" t="n">
-        <v>67.089</v>
+        <v>67.289</v>
       </c>
       <c r="AA5" s="27" t="n">
-        <v>65.631</v>
+        <v>65.82599999999999</v>
       </c>
       <c r="AB5" s="27" t="n">
-        <v>23.894</v>
+        <v>24.091</v>
       </c>
       <c r="AC5" s="27" t="n">
-        <v>70.495</v>
+        <v>70.694</v>
       </c>
       <c r="AD5" s="27" t="n">
-        <v>140.062</v>
+        <v>140.261</v>
       </c>
       <c r="AE5" s="27" t="n">
-        <v>306.595</v>
+        <v>306.79</v>
       </c>
       <c r="AF5" s="27" t="n">
-        <v>459.729</v>
+        <v>459.926</v>
       </c>
       <c r="AG5" s="27" t="n">
-        <v>554.121</v>
+        <v>554.3200000000001</v>
       </c>
       <c r="AH5" s="27" t="n">
-        <v>556.5549999999999</v>
+        <v>556.754</v>
       </c>
       <c r="AI5" s="27" t="n">
-        <v>544.456</v>
+        <v>544.651</v>
       </c>
       <c r="AJ5" s="27" t="n">
-        <v>550.505</v>
+        <v>550.702</v>
       </c>
       <c r="AK5" s="27" t="n">
-        <v>552.622</v>
+        <v>552.756</v>
       </c>
       <c r="AL5" s="27" t="n">
         <v>544.494</v>
@@ -39665,25 +39665,25 @@
         <v>18.786</v>
       </c>
       <c r="AY5" s="27" t="n">
-        <v>164.738</v>
+        <v>165</v>
       </c>
       <c r="AZ5" s="27" t="n">
-        <v>266.169</v>
+        <v>266.961</v>
       </c>
       <c r="BA5" s="27" t="n">
-        <v>266.169</v>
+        <v>266.961</v>
       </c>
       <c r="BB5" s="27" t="n">
-        <v>266.898</v>
+        <v>267.692</v>
       </c>
       <c r="BC5" s="27" t="n">
-        <v>300.082</v>
+        <v>300.872</v>
       </c>
       <c r="BD5" s="27" t="n">
-        <v>1877</v>
+        <v>1877.79</v>
       </c>
       <c r="BE5" s="27" t="n">
-        <v>2192.077</v>
+        <v>2192.603</v>
       </c>
       <c r="BF5" s="27" t="n">
         <v>2045.825</v>
@@ -39911,79 +39911,79 @@
         <v>4.671</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>8.523999999999999</v>
+        <v>8.586</v>
       </c>
       <c r="N7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="O7" s="27" t="n">
-        <v>16.418</v>
+        <v>16.612</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="Q7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="R7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="S7" s="27" t="n">
-        <v>16.418</v>
+        <v>16.612</v>
       </c>
       <c r="T7" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="U7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="V7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="W7" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="X7" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="Y7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="Z7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="AA7" s="27" t="n">
-        <v>16.418</v>
+        <v>16.612</v>
       </c>
       <c r="AB7" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="AC7" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="AD7" s="27" t="n">
-        <v>15.961</v>
+        <v>16.16</v>
       </c>
       <c r="AE7" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AF7" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AG7" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AH7" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AI7" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AJ7" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AK7" s="27" t="n">
-        <v>8.128</v>
+        <v>8.262</v>
       </c>
       <c r="AW7" s="27" t="n">
         <v>6.159</v>
@@ -39992,25 +39992,25 @@
         <v>18.786</v>
       </c>
       <c r="AY7" s="27" t="n">
-        <v>34.596</v>
+        <v>34.858</v>
       </c>
       <c r="AZ7" s="27" t="n">
-        <v>66.58199999999999</v>
+        <v>67.373</v>
       </c>
       <c r="BA7" s="27" t="n">
-        <v>66.58199999999999</v>
+        <v>67.373</v>
       </c>
       <c r="BB7" s="27" t="n">
-        <v>66.764</v>
+        <v>67.55800000000001</v>
       </c>
       <c r="BC7" s="27" t="n">
-        <v>65.761</v>
+        <v>66.551</v>
       </c>
       <c r="BD7" s="27" t="n">
-        <v>47.847</v>
+        <v>48.639</v>
       </c>
       <c r="BE7" s="27" t="n">
-        <v>31.855</v>
+        <v>32.381</v>
       </c>
     </row>
     <row r="8">
@@ -40436,79 +40436,79 @@
         <v>4.671</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>8.523999999999999</v>
+        <v>8.586</v>
       </c>
       <c r="N13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="O13" s="27" t="n">
-        <v>16.418</v>
+        <v>16.612</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="Q13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="R13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="S13" s="27" t="n">
-        <v>16.418</v>
+        <v>16.612</v>
       </c>
       <c r="T13" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="U13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="V13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="W13" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="X13" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="Y13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="Z13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="AA13" s="27" t="n">
-        <v>16.418</v>
+        <v>16.612</v>
       </c>
       <c r="AB13" s="27" t="n">
-        <v>16.6</v>
+        <v>16.797</v>
       </c>
       <c r="AC13" s="27" t="n">
-        <v>16.782</v>
+        <v>16.982</v>
       </c>
       <c r="AD13" s="27" t="n">
-        <v>15.961</v>
+        <v>16.16</v>
       </c>
       <c r="AE13" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AF13" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AG13" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AH13" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AI13" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AJ13" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AK13" s="27" t="n">
-        <v>8.128</v>
+        <v>8.262</v>
       </c>
       <c r="AW13" s="27" t="n">
         <v>6.159</v>
@@ -40517,25 +40517,25 @@
         <v>18.786</v>
       </c>
       <c r="AY13" s="27" t="n">
-        <v>34.596</v>
+        <v>34.858</v>
       </c>
       <c r="AZ13" s="27" t="n">
-        <v>66.58199999999999</v>
+        <v>67.373</v>
       </c>
       <c r="BA13" s="27" t="n">
-        <v>66.58199999999999</v>
+        <v>67.373</v>
       </c>
       <c r="BB13" s="27" t="n">
-        <v>66.764</v>
+        <v>67.55800000000001</v>
       </c>
       <c r="BC13" s="27" t="n">
-        <v>65.761</v>
+        <v>66.551</v>
       </c>
       <c r="BD13" s="27" t="n">
-        <v>47.847</v>
+        <v>48.639</v>
       </c>
       <c r="BE13" s="27" t="n">
-        <v>31.855</v>
+        <v>32.381</v>
       </c>
     </row>
     <row r="14">
@@ -40889,79 +40889,79 @@
         <v>1131.31</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>1129.71</v>
+        <v>1129.74</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="R17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1133.43</v>
+        <v>1133.51</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1184.07</v>
+        <v>1183.87</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1315.33</v>
+        <v>1314.89</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1383.31</v>
+        <v>1383</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1424.95</v>
+        <v>1424.78</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1447.25</v>
+        <v>1447.13</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1452.67</v>
+        <v>1452.57</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1452.53</v>
+        <v>1452.42</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1452.53</v>
+        <v>1452.42</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1452.53</v>
+        <v>1452.42</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1454.61</v>
+        <v>1454.54</v>
       </c>
       <c r="AL17" s="13" t="n">
         <v>1459.01</v>
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
     </row>
     <row r="19">
@@ -41177,112 +41177,112 @@
         <v>1128.26</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>1138.77</v>
+        <v>1138.79</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>1148.45</v>
+        <v>1148.51</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>1155.13</v>
+        <v>1155.19</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>1172.03</v>
+        <v>1172.08</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>1195.98</v>
+        <v>1196.03</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>1201.44</v>
+        <v>1201.49</v>
       </c>
       <c r="S19" s="13" t="n">
-        <v>1176.49</v>
+        <v>1176.54</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>1188.11</v>
+        <v>1188.16</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>1187.49</v>
+        <v>1187.54</v>
       </c>
       <c r="V19" s="13" t="n">
-        <v>1190</v>
+        <v>1190.06</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>1192.44</v>
+        <v>1192.5</v>
       </c>
       <c r="X19" s="13" t="n">
-        <v>1204.78</v>
+        <v>1204.84</v>
       </c>
       <c r="Y19" s="13" t="n">
-        <v>1200.27</v>
+        <v>1200.32</v>
       </c>
       <c r="Z19" s="13" t="n">
-        <v>1212.29</v>
+        <v>1212.35</v>
       </c>
       <c r="AA19" s="13" t="n">
-        <v>1229.08</v>
+        <v>1229.14</v>
       </c>
       <c r="AB19" s="13" t="n">
-        <v>1248.41</v>
+        <v>1248.27</v>
       </c>
       <c r="AC19" s="13" t="n">
-        <v>1336.82</v>
+        <v>1336.51</v>
       </c>
       <c r="AD19" s="13" t="n">
-        <v>1403.08</v>
+        <v>1402.85</v>
       </c>
       <c r="AE19" s="13" t="n">
-        <v>1437.3</v>
+        <v>1437.18</v>
       </c>
       <c r="AF19" s="13" t="n">
-        <v>1463.6</v>
+        <v>1463.51</v>
       </c>
       <c r="AG19" s="13" t="n">
-        <v>1442.5</v>
+        <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1423.2</v>
+        <v>1422.05</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1421.25</v>
+        <v>1419.89</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1421.25</v>
+        <v>1419.89</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1422.71</v>
+        <v>1421.37</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1425.79</v>
+        <v>1424.5</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1425.79</v>
+        <v>1424.5</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1425.75</v>
+        <v>1424.46</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1425.41</v>
+        <v>1424.12</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1425.96</v>
+        <v>1424.67</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1433.28</v>
+        <v>1431.99</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1439.64</v>
+        <v>1438.35</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1442.42</v>
+        <v>1441.13</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1439.03</v>
+        <v>1437.74</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1397.61</v>
+        <v>1396.32</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1397.61</v>
+        <v>1396.32</v>
       </c>
     </row>
     <row r="20">
@@ -41321,112 +41321,112 @@
         <v>38584.8</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>66994.60000000001</v>
+        <v>67067.39999999999</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>77048.8</v>
+        <v>77281.3</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>75812.5</v>
+        <v>76041.2</v>
       </c>
       <c r="P20" s="18" t="n">
-        <v>77775.89999999999</v>
+        <v>78010.5</v>
       </c>
       <c r="Q20" s="18" t="n">
-        <v>80237.5</v>
+        <v>80479.5</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>80603.60000000001</v>
+        <v>80846.60000000001</v>
       </c>
       <c r="S20" s="18" t="n">
-        <v>77213.8</v>
+        <v>77446.7</v>
       </c>
       <c r="T20" s="18" t="n">
-        <v>78843</v>
+        <v>79080.7</v>
       </c>
       <c r="U20" s="18" t="n">
-        <v>79667.7</v>
+        <v>79908</v>
       </c>
       <c r="V20" s="18" t="n">
-        <v>79836.60000000001</v>
+        <v>80077.3</v>
       </c>
       <c r="W20" s="18" t="n">
-        <v>79130.60000000001</v>
+        <v>79369.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>79949.7</v>
+        <v>80190.7</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>80525.10000000001</v>
+        <v>80767.89999999999</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>81331.8</v>
+        <v>81577</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>80665.89999999999</v>
+        <v>80909.10000000001</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>29829</v>
+        <v>30071.6</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>94238.89999999999</v>
+        <v>94483.5</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>196518.1</v>
+        <v>196766.5</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>440669.5</v>
+        <v>440913.4</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>672859.3</v>
+        <v>673108</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>799317.5</v>
+        <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>792089.8</v>
+        <v>791731.2</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>773808.8</v>
+        <v>773343.2</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>782406.6</v>
+        <v>781935.9</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>786220.6</v>
+        <v>785670.9</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>776333.9</v>
+        <v>775631.5</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>767895.5</v>
+        <v>767200.8</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>761966</v>
+        <v>761276.6</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>721800.2</v>
+        <v>721147</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>665121.3</v>
+        <v>664519.6</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>501522.4</v>
+        <v>501071</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>351629</v>
+        <v>351313.9</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224765.3</v>
+        <v>224564.2</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124747.7</v>
+        <v>124635.9</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>34017.1</v>
+        <v>33985.7</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23056</v>
+        <v>23034.8</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41435,34 +41435,34 @@
         <v>22348.4</v>
       </c>
       <c r="AY20" s="18" t="n">
-        <v>188034</v>
+        <v>188339.3</v>
       </c>
       <c r="AZ20" s="18" t="n">
-        <v>314429.5</v>
+        <v>315377.8</v>
       </c>
       <c r="BA20" s="18" t="n">
-        <v>315561.1</v>
+        <v>316512.7</v>
       </c>
       <c r="BB20" s="18" t="n">
-        <v>320937.2</v>
+        <v>321904.9</v>
       </c>
       <c r="BC20" s="18" t="n">
-        <v>401251.9</v>
+        <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704936.1</v>
+        <v>2705316.6</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3118769.9</v>
+        <v>3116581.5</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2916783</v>
+        <v>2914144</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1202664.4</v>
+        <v>1201585</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>57073.1</v>
+        <v>57020.5</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>777395.7</v>
+        <v>776807.6</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>759457.1</v>
+        <v>758770</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>767895.5</v>
+        <v>767200.8</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>776333.9</v>
+        <v>775631.5</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>776333.9</v>
+        <v>775631.5</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>767895.5</v>
+        <v>767200.8</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>761966</v>
+        <v>761276.6</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>721800.2</v>
+        <v>721147</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>665121.3</v>
+        <v>664519.6</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>501522.4</v>
+        <v>501071</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>351629</v>
+        <v>351313.9</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224765.3</v>
+        <v>224564.2</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124747.7</v>
+        <v>124635.9</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>34017.1</v>
+        <v>33985.7</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23056</v>
+        <v>23034.8</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2645487.2</v>
+        <v>2644899.1</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3080020.4</v>
+        <v>3077233.8</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2916783</v>
+        <v>2914144</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1202664.4</v>
+        <v>1201585</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>57073.1</v>
+        <v>57020.5</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>742574.1</v>
+        <v>742013</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>725440</v>
+        <v>724784.3</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>733500.5</v>
+        <v>732837.4</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>741560.9</v>
+        <v>740890.6</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>741560.9</v>
+        <v>740890.6</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>733500.5</v>
+        <v>732837.4</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>727570.9</v>
+        <v>726913.3</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>687027.2</v>
+        <v>686406</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>630348.3</v>
+        <v>629778.7</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>467505.3</v>
+        <v>467085.3</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>317234</v>
+        <v>316950.6</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189992.2</v>
+        <v>189823.3</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89974.7</v>
+        <v>89894.89999999999</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34821.5</v>
+        <v>34794.7</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>34017.1</v>
+        <v>33985.7</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34395.1</v>
+        <v>34363.3</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34773</v>
+        <v>34740.9</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34773</v>
+        <v>34740.9</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34395.1</v>
+        <v>34363.3</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34395.1</v>
+        <v>34363.3</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34773</v>
+        <v>34740.9</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34773</v>
+        <v>34740.9</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>34017.1</v>
+        <v>33985.7</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34395.1</v>
+        <v>34363.3</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34773</v>
+        <v>34740.9</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34773</v>
+        <v>34740.9</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>34017.1</v>
+        <v>33985.7</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23056</v>
+        <v>23034.8</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1354.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1351.18)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
     </row>
@@ -44257,7 +44257,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260908800414</t>
+          <t>20261006800410</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -44271,79 +44271,79 @@
         </is>
       </c>
       <c r="M52" s="27" t="n">
-        <v>3.802</v>
+        <v>3.864</v>
       </c>
       <c r="N52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="O52" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="P52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="Q52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="R52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="S52" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="T52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="U52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="V52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="W52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="X52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="Y52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="Z52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AA52" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AB52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AC52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AD52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AE52" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AF52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AG52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AH52" s="27" t="n">
-        <v>12.06</v>
+        <v>12.26</v>
       </c>
       <c r="AI52" s="27" t="n">
-        <v>11.798</v>
+        <v>11.993</v>
       </c>
       <c r="AJ52" s="27" t="n">
-        <v>11.929</v>
+        <v>12.126</v>
       </c>
       <c r="AK52" s="27" t="n">
-        <v>8.135999999999999</v>
+        <v>8.262</v>
       </c>
       <c r="BJ52" s="35" t="n">
         <v>0</v>
@@ -44363,7 +44363,7 @@
         <v>1</v>
       </c>
       <c r="BP52" s="27" t="n">
-        <v>287.091</v>
+        <v>291.833</v>
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260908800414</t>
+          <t>20261006800410</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -48737,36 +48737,39 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20260908800414</t>
+          <t>20260930800164</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>333000</v>
+        <v>1953900</v>
       </c>
       <c r="E120" t="n">
-        <v>287.091</v>
+        <v>1485.076</v>
       </c>
       <c r="F120" t="n">
-        <v>1159.91</v>
+        <v>1315.69</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -48775,7 +48778,7 @@
         </is>
       </c>
       <c r="M120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -48787,48 +48790,45 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>20260930800164</t>
+          <t>20261006800410</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OFFSH</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>338500</v>
+      </c>
+      <c r="E121" t="n">
+        <v>291.833</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1159.91</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M121" t="b">
         <v>1</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1953900</v>
-      </c>
-      <c r="E121" t="n">
-        <v>1485.076</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1315.69</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2027-06-01</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M121" t="b">
-        <v>0</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -50552,7 +50552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66085억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68322억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72239억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72216억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76487억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76466억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 81450억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 81430억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 86534억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 86515억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91761억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91743억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95812억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95795억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98578억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98563억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66085억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68322억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72239억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72216억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76487억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76466억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 81450억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 81430억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 86534억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 86515억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91761억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91743억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95812억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95795억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98578억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98563억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174624억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 186846억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 186839억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191124억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191114억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 204869억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 204855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 219562억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 219545억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 235231억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 235210억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 243207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 243182억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 260632억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 260604억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 174627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 174624억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 186846억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 186839억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191124억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191114억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 204869억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 204855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 219562억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 219545억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 235231억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 235210억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 243207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 243182억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 260632억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 260604억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52163.4</v>
+        <v>52152.3</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.1</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>318000</v>
+        <v>301500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>315000</v>
+        <v>300000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>323333.3</v>
+        <v>318125</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9445,33 +9445,33 @@
         <v>0.216028511</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.142915298</v>
+        <v>0.142678782</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.183171287</v>
+        <v>0.182782386</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.140821438</v>
+        <v>0.140470146</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169630757</v>
+        <v>0.169306002</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.232502488</v>
+        <v>0.232448838</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.266556701</v>
+        <v>0.266689106</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.270253352</v>
+        <v>0.270385904</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.252660156</v>
+        <v>0.252783018</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.210286204</v>
+        <v>0.210402388</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.155847303</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.155748422</v>
+        <v>0.155748237</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.155748294</v>
+        <v>0.155748304</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.155738919</v>
+        <v>0.155738958</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.155711957</v>
+        <v>0.155711882</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.155692193</v>
+        <v>0.155692173</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.155672267</v>
+        <v>0.155672247</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.155652496</v>
+        <v>0.155652572</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.155602588</v>
+        <v>0.15560255</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.155529725</v>
+        <v>0.155529648</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.006243027</v>
+        <v>-0.005315898</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.002970843</v>
+        <v>-0.005842529</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.002614163</v>
+        <v>-0.005571996</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.892412749999</v>
+        <v>8697.896700060001</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002264879</v>
+        <v>-0.012176408</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.003687274</v>
+        <v>0.006635305</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.00239325</v>
+        <v>-0.017140091</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.891794404</v>
+        <v>8697.892765336999</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.006586482</v>
+        <v>0.003225331</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.001070063</v>
+        <v>-0.015214281</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.001563051</v>
+        <v>0.00371177</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.00684972</v>
+        <v>-0.003748382</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.004820371</v>
+        <v>-0.005254226</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.902263468</v>
+        <v>8697.895030801999</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.009696305000000001</v>
+        <v>-0.006020146</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.002236226</v>
+        <v>0.000539745</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.002016013</v>
+        <v>-0.007334909</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.890905613</v>
+        <v>8697.899628773001</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.002746641</v>
+        <v>-4.336e-06</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.001726244</v>
+        <v>-0.00765715</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09654497200000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.089409878</v>
+        <v>0.089391554</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.085281384</v>
+        <v>0.08525518</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.027512483</v>
+        <v>0.027488272</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08602697500000001</v>
+        <v>0.086008741</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.084678687</v>
+        <v>0.084664421</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.083247656</v>
+        <v>0.08323687</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.03911972</v>
+        <v>0.039107128</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082250138</v>
+        <v>0.08224476</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.078512183</v>
+        <v>0.078509336</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.07654037599999999</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.072200974</v>
+        <v>0.072186115</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.069972363</v>
+        <v>0.069950655</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.022896593</v>
+        <v>0.022876341</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.071917144</v>
+        <v>0.071901088</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.071721717</v>
+        <v>0.07170879400000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071362199</v>
+        <v>0.071351945</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.033906512</v>
+        <v>0.033895127</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.07164866</v>
+        <v>0.071642943</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.06906912699999999</v>
+        <v>0.069065613</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,11 +12327,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>318000</v>
+        <v>301500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 325,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 326,000원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989270050870875</v>
+        <v>0.198927021045511</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842986213712466</v>
+        <v>0.04842985639836901</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600275607956595</v>
+        <v>0.7600276855038979</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816795178321848</v>
+        <v>0.02816775752324768</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311627713429104</v>
+        <v>0.131161593485744</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1422.05</v>
+        <v>1421.12</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1419.89</v>
+        <v>1418.33</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1419.89</v>
+        <v>1418.33</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1421.37</v>
+        <v>1419.81</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1424.5</v>
+        <v>1422.94</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1424.5</v>
+        <v>1422.94</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1424.46</v>
+        <v>1422.9</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1424.12</v>
+        <v>1422.56</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1424.67</v>
+        <v>1423.11</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1431.99</v>
+        <v>1430.43</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1438.35</v>
+        <v>1436.79</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1441.13</v>
+        <v>1439.57</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1437.74</v>
+        <v>1436.18</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1396.32</v>
+        <v>1394.76</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1396.32</v>
+        <v>1394.76</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>791731.2</v>
+        <v>791213.4</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>773343.2</v>
+        <v>772493.6</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>781935.9</v>
+        <v>781076.8</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>785670.9</v>
+        <v>784808.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>775631.5</v>
+        <v>774782.1</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>767200.8</v>
+        <v>766360.6</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>761276.6</v>
+        <v>760442.9</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>721147</v>
+        <v>720357</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>664519.6</v>
+        <v>663792</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>501071</v>
+        <v>500525.1</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>351313.9</v>
+        <v>350932.9</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224564.2</v>
+        <v>224321.2</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124635.9</v>
+        <v>124500.6</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33985.7</v>
+        <v>33947.7</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23034.8</v>
+        <v>23009</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2705316.6</v>
+        <v>2704798.8</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3116581.5</v>
+        <v>3113161.1</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2914144</v>
+        <v>2910952.5</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1201585</v>
+        <v>1200279.8</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>57020.5</v>
+        <v>56956.7</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>776807.6</v>
+        <v>776301.3</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>758770</v>
+        <v>757939</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>767200.8</v>
+        <v>766360.6</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>775631.5</v>
+        <v>774782.1</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>775631.5</v>
+        <v>774782.1</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>767200.8</v>
+        <v>766360.6</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>761276.6</v>
+        <v>760442.9</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>721147</v>
+        <v>720357</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>664519.6</v>
+        <v>663792</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>501071</v>
+        <v>500525.1</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>351313.9</v>
+        <v>350932.9</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224564.2</v>
+        <v>224321.2</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124635.9</v>
+        <v>124500.6</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33985.7</v>
+        <v>33947.7</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23034.8</v>
+        <v>23009</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2644899.1</v>
+        <v>2644392.8</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3077233.8</v>
+        <v>3073863.8</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2914144</v>
+        <v>2910952.5</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1201585</v>
+        <v>1200279.8</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>57020.5</v>
+        <v>56956.7</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>742013</v>
+        <v>741529.7</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>724784.3</v>
+        <v>723991.3</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>732837.4</v>
+        <v>732035.6</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>740890.6</v>
+        <v>740080</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>740890.6</v>
+        <v>740080</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>732837.4</v>
+        <v>732035.6</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>726913.3</v>
+        <v>726117.9</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>686406</v>
+        <v>685654.9</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>629778.7</v>
+        <v>629089.9</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>467085.3</v>
+        <v>466577.4</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316950.6</v>
+        <v>316608</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189823.3</v>
+        <v>189619</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89894.89999999999</v>
+        <v>89798.5</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34794.7</v>
+        <v>34771.5</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33985.7</v>
+        <v>33947.7</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34363.3</v>
+        <v>34324.9</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34740.9</v>
+        <v>34702.1</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34740.9</v>
+        <v>34702.1</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34363.3</v>
+        <v>34324.9</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34363.3</v>
+        <v>34324.9</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34740.9</v>
+        <v>34702.1</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34740.9</v>
+        <v>34702.1</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33985.7</v>
+        <v>33947.7</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34363.3</v>
+        <v>34324.9</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34740.9</v>
+        <v>34702.1</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34740.9</v>
+        <v>34702.1</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33985.7</v>
+        <v>33947.7</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23034.8</v>
+        <v>23009</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1351.18)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1348.08)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
     </row>
@@ -50552,7 +50552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -782,61 +782,61 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.2% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
@@ -2009,121 +2009,121 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 13.9% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.2% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 13.9% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.2% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
@@ -2135,55 +2135,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 162867억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 162967억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174624억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 186839억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191114억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191629억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 204855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205537억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 219545억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220413억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 235210억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236284억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 243182억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244484억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 260604억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 262166억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2195,55 +2195,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 162867억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 162967억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 174624억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 174855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 186839억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191114억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191629억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 204855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205537억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 219545억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220413억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 235210억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236284억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 243182억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244484억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 260604억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 262166억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52152.3</v>
+        <v>52706.2</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="32">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2487</v>
+        <v>0.2513</v>
       </c>
     </row>
     <row r="34">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="35">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>578800</v>
+        <v>585100</v>
       </c>
     </row>
     <row r="36">
@@ -9753,42 +9753,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.155847303</v>
+        <v>0.157199692</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.155748237</v>
+        <v>0.157499765</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.155748304</v>
+        <v>0.157499698</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.155738958</v>
+        <v>0.157528168</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.155711882</v>
+        <v>0.157610285</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.155692173</v>
+        <v>0.157670322</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.155672247</v>
+        <v>0.157730324</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.155652572</v>
+        <v>0.157790298</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.15560255</v>
+        <v>0.157941955</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.155529648</v>
+        <v>0.158163123</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.005315898</v>
+        <v>-0.006049329</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.005842529</v>
+        <v>0.0044282</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.005571996</v>
+        <v>-0.006699788</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.896700060001</v>
+        <v>8697.895923168</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.012176408</v>
+        <v>-0.001766182</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.006635305</v>
+        <v>0.004740559</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.017140091</v>
+        <v>-0.000935746</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.892765336999</v>
+        <v>8697.894731036</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.003225331</v>
+        <v>-0.008516075</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.015214281</v>
+        <v>0.008235241000000001</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.00371177</v>
+        <v>-0.007448392</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.003748382</v>
+        <v>0.00548471</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005254226</v>
+        <v>-0.0006277709999999999</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.895030801999</v>
+        <v>8697.886102434</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.006020146</v>
+        <v>0.002329323</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.000539745</v>
+        <v>-0.003318412</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.007334909</v>
+        <v>0.004937247</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.899628773001</v>
+        <v>8697.892285987</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-4.336e-06</v>
+        <v>-0.002999723</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.00765715</v>
+        <v>-0.008072785000000001</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11507,36 +11507,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.09654497200000001</v>
+        <v>0.09737772</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.089391554</v>
+        <v>0.090320909</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.08525518</v>
+        <v>0.08606834100000001</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.027488272</v>
+        <v>0.028372962</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.086008741</v>
+        <v>0.086773089</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.084664421</v>
+        <v>0.085399181</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.08323687</v>
+        <v>0.083944137</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039107128</v>
+        <v>0.040012505</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.08224476</v>
+        <v>0.082964418</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.078509336</v>
+        <v>0.079286182</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11635,36 +11635,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>0.07654037599999999</v>
+        <v>0.07720057499999999</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.072186115</v>
+        <v>0.07294725000000001</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.069950655</v>
+        <v>0.07063826500000001</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.022876341</v>
+        <v>0.023621945</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.071901088</v>
+        <v>0.072578352</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07170879400000001</v>
+        <v>0.07237450400000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071351945</v>
+        <v>0.07200543399999999</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.033895127</v>
+        <v>0.034704082</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.071642943</v>
+        <v>0.072326773</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069065613</v>
+        <v>0.06980583999999999</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.198927021045511</v>
+        <v>0.1989269049503004</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600276855038979</v>
+        <v>0.7600274998828247</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816775752324768</v>
+        <v>0.02816786899666996</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.131161593485744</v>
+        <v>0.1311621945482075</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39059,7 +39059,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>코호트 표(가정): ①적자 −5% ②BEP 0% ③중마진 5% ④호황 10% ⑤초호황 15% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 미적용</t>
+          <t>코호트 표(레퍼런스 실측 캘리브레이션): ①적자 −1.1% ②BEP 1% ③중마진 4.3% ④호황 5.4% ⑤초호황 10.8% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 미적용</t>
         </is>
       </c>
     </row>
@@ -41945,115 +41945,115 @@
         </is>
       </c>
       <c r="L24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="M24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="N24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="O24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="P24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="Q24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="R24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="S24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="T24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="U24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="V24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="W24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="X24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="Y24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="Z24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="AA24" s="21" t="n">
-        <v>0.1</v>
+        <v>0.054</v>
       </c>
       <c r="AB24" s="21" t="n">
-        <v>0.12</v>
+        <v>0.0756</v>
       </c>
       <c r="AC24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AD24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AE24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AF24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AG24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AH24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AI24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AJ24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AK24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AL24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AM24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AN24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AO24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AP24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AQ24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AR24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AS24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AT24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AU24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AV24" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="26">
@@ -48861,7 +48861,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 OPM 표 assumed 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 바꾸려면 --opm-table reference_calibrated(오너 결정 — 하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
+          <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
         </is>
       </c>
     </row>

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,7 +668,7 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66063억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
@@ -686,25 +686,25 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76466억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76465억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 81430억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 81429억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 86515억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 86514억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91743억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91742억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
@@ -716,7 +716,7 @@
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98563억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,7 +1775,7 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66063억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -1793,25 +1793,25 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76466억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76465억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 81430억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 81429억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 86515억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 86514억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91743억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91742억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -1823,7 +1823,7 @@
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98563억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174854억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187205억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191629억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205537억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205535억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220413억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220411억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236284억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236282억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244484억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 262166억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 262164억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 174855억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 174854억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187207억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187205억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191629억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205537억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205535억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220413억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220411억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236284억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236282억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244484억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 262166억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 262164억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52706.2</v>
+        <v>52704.4</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.72</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>301500</v>
+        <v>291500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>300000</v>
+        <v>291500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>318125</v>
+        <v>312600</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9445,33 +9445,33 @@
         <v>0.216028511</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.142678782</v>
+        <v>0.142535007</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.182782386</v>
+        <v>0.18277563</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.140470146</v>
+        <v>0.140464209</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169306002</v>
+        <v>0.169300361</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.232448838</v>
+        <v>0.232598666</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.266689106</v>
+        <v>0.266691356</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.270385904</v>
+        <v>0.270388097</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.252783018</v>
+        <v>0.252785072</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.210402388</v>
+        <v>0.210404244</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.157199692</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157499765</v>
+        <v>0.157499721</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157499698</v>
+        <v>0.157499663</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.157528168</v>
+        <v>0.157528104</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610285</v>
+        <v>0.157610303</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670322</v>
+        <v>0.157670298</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157730324</v>
+        <v>0.157730289</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157790298</v>
+        <v>0.157790384</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157941955</v>
+        <v>0.157941939</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.158163123</v>
+        <v>0.158163124</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.006049329</v>
+        <v>-0.006038523</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.0044282</v>
+        <v>0.002574129</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.006699788</v>
+        <v>-0.006829382</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.895923168</v>
+        <v>8697.905401504</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.001766182</v>
+        <v>-0.004704037</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.004740559</v>
+        <v>0.00149535</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.000935746</v>
+        <v>-0.004397061</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.894731036</v>
+        <v>8697.907132561</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.008516075</v>
+        <v>-0.004545176</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.008235241000000001</v>
+        <v>4.0132e-05</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.007448392</v>
+        <v>-0.005586979</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.00548471</v>
+        <v>0.001120918</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.0006277709999999999</v>
+        <v>0.000431345</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.886102434</v>
+        <v>8697.896985521</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.002329323</v>
+        <v>0.009101353</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.003318412</v>
+        <v>-0.00662646</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.004937247</v>
+        <v>0.001622874</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.892285987</v>
+        <v>8697.901190762999</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.002999723</v>
+        <v>-0.00037793</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.008072785000000001</v>
+        <v>0.010601124</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09737772</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.090320909</v>
+        <v>0.090309665</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.08606834100000001</v>
+        <v>0.086068671</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028372962</v>
+        <v>0.028372733</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.086773089</v>
+        <v>0.086773478</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.085399181</v>
+        <v>0.08539962199999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.083944137</v>
+        <v>0.083944561</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.040012505</v>
+        <v>0.040012576</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082964418</v>
+        <v>0.08296479</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.079286182</v>
+        <v>0.07928660899999999</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.07720057499999999</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.07294725000000001</v>
+        <v>0.07293823000000001</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.07063826500000001</v>
+        <v>0.07063834400000001</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023621945</v>
+        <v>0.023621715</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.072578352</v>
+        <v>0.072578556</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07237450400000001</v>
+        <v>0.07237476900000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.07200543399999999</v>
+        <v>0.07200570100000001</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034704082</v>
+        <v>0.034704102</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.072326773</v>
+        <v>0.072327014</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.06980583999999999</v>
+        <v>0.069806144</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,11 +12327,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>301500</v>
+        <v>291500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 326,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 318,500원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269049503004</v>
+        <v>0.1989269117390589</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842985639836901</v>
+        <v>0.04842986796370174</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600274998828247</v>
+        <v>0.7600276585539911</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816786899666996</v>
+        <v>0.02816792194489136</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311621945482075</v>
+        <v>0.1311624444580518</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1421.12</v>
+        <v>1420.55</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1418.33</v>
+        <v>1418.3</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1418.33</v>
+        <v>1418.3</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1419.81</v>
+        <v>1419.78</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1422.94</v>
+        <v>1422.91</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1422.94</v>
+        <v>1422.91</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1422.9</v>
+        <v>1422.87</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1422.56</v>
+        <v>1422.54</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1423.11</v>
+        <v>1423.08</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1430.43</v>
+        <v>1430.4</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1436.79</v>
+        <v>1436.76</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1439.57</v>
+        <v>1439.54</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1436.18</v>
+        <v>1436.16</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1394.76</v>
+        <v>1394.73</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1394.76</v>
+        <v>1394.73</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>791213.4</v>
+        <v>790899.4</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>772493.6</v>
+        <v>772478.8</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>781076.8</v>
+        <v>781061.9</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>784808.6</v>
+        <v>784793.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>774782.1</v>
+        <v>774767.4</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>766360.6</v>
+        <v>766346</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>760442.9</v>
+        <v>760428.4</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>720357</v>
+        <v>720343.3</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>663792</v>
+        <v>663779.4</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>500525.1</v>
+        <v>500515.7</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>350932.9</v>
+        <v>350926.3</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224321.2</v>
+        <v>224316.9</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124500.6</v>
+        <v>124498.3</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33947.7</v>
+        <v>33947.1</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23009</v>
+        <v>23008.6</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704798.8</v>
+        <v>2704484.8</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3113161.1</v>
+        <v>3113101.7</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2910952.5</v>
+        <v>2910897.1</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1200279.8</v>
+        <v>1200257.2</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>56956.7</v>
+        <v>56955.7</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>776301.3</v>
+        <v>775994.2</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>757939</v>
+        <v>757924.6</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>766360.6</v>
+        <v>766346</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>774782.1</v>
+        <v>774767.4</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>774782.1</v>
+        <v>774767.4</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>766360.6</v>
+        <v>766346</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>760442.9</v>
+        <v>760428.4</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>720357</v>
+        <v>720343.3</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>663792</v>
+        <v>663779.4</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>500525.1</v>
+        <v>500515.7</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>350932.9</v>
+        <v>350926.3</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224321.2</v>
+        <v>224316.9</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124500.6</v>
+        <v>124498.3</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33947.7</v>
+        <v>33947.1</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23009</v>
+        <v>23008.6</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2644392.8</v>
+        <v>2644085.7</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3073863.8</v>
+        <v>3073805.4</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2910952.5</v>
+        <v>2910897.1</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1200279.8</v>
+        <v>1200257.2</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>56956.7</v>
+        <v>56955.7</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>741529.7</v>
+        <v>741236.7</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>723991.3</v>
+        <v>723977.6</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>732035.6</v>
+        <v>732021.8</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>740080</v>
+        <v>740066</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>740080</v>
+        <v>740066</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>732035.6</v>
+        <v>732021.8</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>726117.9</v>
+        <v>726104.2</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>685654.9</v>
+        <v>685641.9</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>629089.9</v>
+        <v>629077.9</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>466577.4</v>
+        <v>466568.6</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316608</v>
+        <v>316602.1</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189619</v>
+        <v>189615.5</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89798.5</v>
+        <v>89796.8</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34771.5</v>
+        <v>34757.5</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33947.7</v>
+        <v>33947.1</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34324.9</v>
+        <v>34324.3</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34702.1</v>
+        <v>34701.5</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34702.1</v>
+        <v>34701.5</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34324.9</v>
+        <v>34324.3</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34324.9</v>
+        <v>34324.3</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34702.1</v>
+        <v>34701.5</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34702.1</v>
+        <v>34701.5</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33947.7</v>
+        <v>33947.1</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34324.9</v>
+        <v>34324.3</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34702.1</v>
+        <v>34701.5</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34702.1</v>
+        <v>34701.5</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33947.7</v>
+        <v>33947.1</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23009</v>
+        <v>23008.6</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1348.08)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1346.2)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
     </row>
@@ -50552,7 +50552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -662,61 +662,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 65394억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 65950억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66063억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66794억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68524억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72216억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76465억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76054억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 81429억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80843억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 86514억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85845억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91742억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91102억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95795억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95298억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1769,61 +1769,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 65394억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 65950억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66063억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66794억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68524억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72216억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76465억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76054억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 81429억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80843억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 86514억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85845억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91742억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91102억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95795억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95298억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2135,55 +2135,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 162967억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 163066억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 174854억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175083억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187205억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187476억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205535억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205710억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220411억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236282억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236234억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244320억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 262164억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261913억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2195,55 +2195,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 162967억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 163066억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 174854억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 175083억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187205억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187476억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191627억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205535억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205710억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220411억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236282억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236234억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244320억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 262164억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261913억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 지배주주순이익 face 누락 분기는 당기순이익 − 비지배 로 파생: 2025Q1, 2026Q1 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -9878/-8080/-13801/-2147(중위 -8979억) → 추정 2026Q3 +87억(차 +9066억, +101%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 지배주주순이익 face 누락 분기는 당기순이익 − 비지배 로 파생: 2025Q1, 2026Q1 / 총차입금 이자율: 주석 연율 13.1% 가 CF 연율 4.1% 의 3.2배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -9878/-8080/-13801/-2147(중위 -8979억) → 추정 2026Q3 +87억(차 +9066억, +101%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52704.4</v>
+        <v>52969.2</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="32">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2513</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="34">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="35">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>585100</v>
+        <v>589300</v>
       </c>
     </row>
     <row r="36">
@@ -9442,36 +9442,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.216028511</v>
+        <v>0.226363624</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.142535007</v>
+        <v>0.155168022</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.18277563</v>
+        <v>0.186664271</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.140464209</v>
+        <v>0.138181595</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169300361</v>
+        <v>0.153211523</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.232598666</v>
+        <v>0.210341641</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.266691356</v>
+        <v>0.252765513</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.270388097</v>
+        <v>0.264055764</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.252785072</v>
+        <v>0.253025621</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.210404244</v>
+        <v>0.21593999</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9753,42 +9753,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.157199692</v>
+        <v>0.157199651</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157499721</v>
+        <v>0.157499793</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157499663</v>
+        <v>0.157499666</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.157528104</v>
+        <v>0.157528099</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610303</v>
+        <v>0.157610322</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670298</v>
+        <v>0.157670352</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157730289</v>
+        <v>0.157730341</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157790384</v>
+        <v>0.157790302</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157941939</v>
+        <v>0.15794197</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.158163124</v>
+        <v>0.15816305</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>-0.006038523</v>
+        <v>0.001106638</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.002574129</v>
+        <v>-0.007716634</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.006829382</v>
+        <v>-0.003573621</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.905401504</v>
+        <v>8697.905435942001</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.004704037</v>
+        <v>-0.002661438</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.00149535</v>
+        <v>-0.003162238</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.004397061</v>
+        <v>-0.006335116</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.907132561</v>
+        <v>8697.89940909</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.004545176</v>
+        <v>-0.004980519</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>4.0132e-05</v>
+        <v>0.006659276</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>-0.005586979</v>
+        <v>0.002006057</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.001120918</v>
+        <v>-0.005301114</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.000431345</v>
+        <v>-0.003433113</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.896985521</v>
+        <v>8697.889534013</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.009101353</v>
+        <v>-0.001876903</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00662646</v>
+        <v>0.000256807</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.001622874</v>
+        <v>-0.007636122</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.901190762999</v>
+        <v>8697.895871911</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.00037793</v>
+        <v>0.000779149</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.010601124</v>
+        <v>0.000940287</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11507,36 +11507,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.09737772</v>
+        <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.090309665</v>
+        <v>0.09123277</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.086068671</v>
+        <v>0.086218297</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028372733</v>
+        <v>0.028168659</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.086773478</v>
+        <v>0.086193113</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.08539962199999999</v>
+        <v>0.084721186</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.083944561</v>
+        <v>0.083284343</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.040012576</v>
+        <v>0.039463916</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.08296479</v>
+        <v>0.082607655</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.07928660899999999</v>
+        <v>0.079163915</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11635,36 +11635,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>0.07720057499999999</v>
+        <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.07293823000000001</v>
+        <v>0.073694262</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.07063834400000001</v>
+        <v>0.070781438</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023621715</v>
+        <v>0.023458616</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.072578556</v>
+        <v>0.072111275</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07237476900000001</v>
+        <v>0.071810757</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.07200570100000001</v>
+        <v>0.071443147</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034704102</v>
+        <v>0.034227213</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.072327014</v>
+        <v>0.072008593</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069806144</v>
+        <v>0.069689061</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269117390589</v>
+        <v>0.1989269453606115</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842986796370174</v>
+        <v>0.04842985260668738</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600276585539911</v>
+        <v>0.7600274746310191</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816792194489136</v>
+        <v>0.02816795829895443</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311624444580518</v>
+        <v>0.1311627175772724</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -49151,39 +49151,39 @@
         <v>0</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>1394.71</v>
+        <v>1006.48</v>
       </c>
       <c r="G6" s="20">
         <f>SUM(E6:F6)</f>
         <v/>
       </c>
       <c r="H6" s="34" t="n">
-        <v>5232.92</v>
+        <v>4164.54</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>10995.73</v>
+        <v>9391.610000000001</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>18164.23</v>
+        <v>16168.84</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>26219.54</v>
+        <v>23977.29</v>
       </c>
       <c r="L6" s="20">
         <f>SUM(H6:K6)</f>
         <v/>
       </c>
       <c r="M6" s="34" t="n">
-        <v>34642.75</v>
+        <v>32298.09</v>
       </c>
       <c r="N6" s="34" t="n">
-        <v>42914.95</v>
+        <v>40612.33</v>
       </c>
       <c r="O6" s="34" t="n">
-        <v>50517.26</v>
+        <v>48401.1</v>
       </c>
       <c r="P6" s="34" t="n">
-        <v>56930.76</v>
+        <v>55145.52</v>
       </c>
       <c r="Q6" s="20">
         <f>SUM(M6:P6)</f>
@@ -49763,39 +49763,39 @@
         <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>1003.97</v>
+        <v>614.73</v>
       </c>
       <c r="G18" s="20">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>3766.79</v>
+        <v>2695.64</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>7914.88</v>
+        <v>6306.65</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>13074.59</v>
+        <v>11074.16</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>18872.35</v>
+        <v>16624.54</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
-        <v>24934.51</v>
+        <v>22584.18</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>30887.49</v>
+        <v>28579.5</v>
       </c>
       <c r="O18" s="34" t="n">
-        <v>36357.66</v>
+        <v>34236.87</v>
       </c>
       <c r="P18" s="34" t="n">
-        <v>40971.45</v>
+        <v>39182.67</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -50069,39 +50069,39 @@
         <v>0</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>2149.63</v>
+        <v>1762.6</v>
       </c>
       <c r="G24" s="20">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>8065.84</v>
+        <v>7000.62</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>16949.53</v>
+        <v>15350.03</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>28001.65</v>
+        <v>26011.72</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>40423.14</v>
+        <v>38186.66</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>53414.94</v>
+        <v>51075.78</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>66177.98</v>
+        <v>63880.01</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>77913.19</v>
+        <v>75800.27</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>87821.52</v>
+        <v>86037.53</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66794억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66791억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68524억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68546억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72093억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76054억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76075억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 80843억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 85845억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91102억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91120억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95298억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66794억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66791억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68524억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68546억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72071억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72093억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76054억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76075억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 80843억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 85845억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91102억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91120억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95298억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2147,43 +2147,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187476억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187479억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191881억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205710억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205721억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220497억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236234억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236252억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244320억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244341억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261913억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261937억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2207,43 +2207,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187476억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187479억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191881억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205710억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205721억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220482억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220497억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236234억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236252억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244320억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244341억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 261913억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261937억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52969.2</v>
+        <v>52977.1</v>
       </c>
     </row>
     <row r="30">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>291500</v>
+        <v>290000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9445,33 +9445,33 @@
         <v>0.226363624</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.155168022</v>
+        <v>0.15513122</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.186664271</v>
+        <v>0.187038432</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.138181595</v>
+        <v>0.138519781</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153211523</v>
+        <v>0.153522679</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.210341641</v>
+        <v>0.210675755</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.252765513</v>
+        <v>0.252645276</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.264055764</v>
+        <v>0.26393207</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.253025621</v>
+        <v>0.252908698</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.21593999</v>
+        <v>0.215828677</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.157199651</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157499793</v>
+        <v>0.15749982</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157499666</v>
+        <v>0.157499796</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.157528099</v>
+        <v>0.15752814</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610322</v>
+        <v>0.157610232</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670352</v>
+        <v>0.157670282</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157730341</v>
+        <v>0.15773029</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157790302</v>
+        <v>0.157790319</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.15794197</v>
+        <v>0.157942009</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.15816305</v>
+        <v>0.158163085</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.001106638</v>
+        <v>0.002045864</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.007716634</v>
+        <v>-0.003682209</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.003573621</v>
+        <v>0.007503897</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.905435942001</v>
+        <v>8697.897663690001</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.002661438</v>
+        <v>-0.007159025</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.003162238</v>
+        <v>-0.003574436</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.006335116</v>
+        <v>-0.007352606</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.89940909</v>
+        <v>8697.905035341</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.004980519</v>
+        <v>-0.0031769</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.006659276</v>
+        <v>-0.005028694</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.002006057</v>
+        <v>0.003657883</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.005301114</v>
+        <v>-8.830000000000001e-05</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.003433113</v>
+        <v>-0.005521165</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.889534013</v>
+        <v>8697.903175617999</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.001876903</v>
+        <v>-0.009691629</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.000256807</v>
+        <v>-0.005581683</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.007636122</v>
+        <v>-0.000260482</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.895871911</v>
+        <v>8697.902376376</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.000779149</v>
+        <v>-0.005163005</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.000940287</v>
+        <v>-0.005611329</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.09123277</v>
+        <v>0.091229885</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.086218297</v>
+        <v>0.08624531000000001</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028168659</v>
+        <v>0.028192563</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.086193113</v>
+        <v>0.08621218</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.084721186</v>
+        <v>0.08473632</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.083284343</v>
+        <v>0.083296066</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039463916</v>
+        <v>0.039476702</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082607655</v>
+        <v>0.082614035</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.079163915</v>
+        <v>0.079167798</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.073694262</v>
+        <v>0.073691932</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.070781438</v>
+        <v>0.070803581</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023458616</v>
+        <v>0.023478611</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.072111275</v>
+        <v>0.072127763</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.071810757</v>
+        <v>0.07182427399999999</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071443147</v>
+        <v>0.071453985</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034227213</v>
+        <v>0.034238702</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.072008593</v>
+        <v>0.07201512</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069689061</v>
+        <v>0.069693321</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 318,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 301,500원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269453606115</v>
+        <v>0.1989269481862587</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842985260668738</v>
+        <v>0.04842986317141213</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600274746310191</v>
+        <v>0.7600275542688268</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816795829895443</v>
+        <v>0.02816777281250812</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311627175772724</v>
+        <v>0.1311616137776667</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1420.55</v>
+        <v>1420.42</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1418.3</v>
+        <v>1419.73</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1418.3</v>
+        <v>1419.73</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1419.78</v>
+        <v>1421.21</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1422.91</v>
+        <v>1424.34</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1422.91</v>
+        <v>1424.34</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1422.87</v>
+        <v>1424.3</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1422.54</v>
+        <v>1423.97</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1423.08</v>
+        <v>1424.51</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1430.4</v>
+        <v>1431.84</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1436.76</v>
+        <v>1438.19</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1439.54</v>
+        <v>1440.97</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1436.16</v>
+        <v>1437.59</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1394.73</v>
+        <v>1396.16</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1394.73</v>
+        <v>1396.16</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>790899.4</v>
+        <v>790822.6</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>772478.8</v>
+        <v>773258.2</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>781061.9</v>
+        <v>781850</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>784793.6</v>
+        <v>785584.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>774767.4</v>
+        <v>775546.6</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>766346</v>
+        <v>767116.7</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>760428.4</v>
+        <v>761193.2</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>720343.3</v>
+        <v>721068</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>663779.4</v>
+        <v>664446.9</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>500515.7</v>
+        <v>501016.4</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>350926.3</v>
+        <v>351275.8</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224316.9</v>
+        <v>224539.9</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124498.3</v>
+        <v>124622.3</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33947.1</v>
+        <v>33981.9</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23008.6</v>
+        <v>23032.2</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704484.8</v>
+        <v>2704408</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3113101.7</v>
+        <v>3116239.4</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2910897.1</v>
+        <v>2913824.8</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1200257.2</v>
+        <v>1201454.4</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>56955.7</v>
+        <v>57014.1</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>775994.2</v>
+        <v>775919</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>757924.6</v>
+        <v>758686.9</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>766346</v>
+        <v>767116.7</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>774767.4</v>
+        <v>775546.6</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>774767.4</v>
+        <v>775546.6</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>766346</v>
+        <v>767116.7</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>760428.4</v>
+        <v>761193.2</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>720343.3</v>
+        <v>721068</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>663779.4</v>
+        <v>664446.9</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>500515.7</v>
+        <v>501016.4</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>350926.3</v>
+        <v>351275.8</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224316.9</v>
+        <v>224539.9</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124498.3</v>
+        <v>124622.3</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33947.1</v>
+        <v>33981.9</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23008.6</v>
+        <v>23032.2</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2644085.7</v>
+        <v>2644010.5</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3073805.4</v>
+        <v>3076896.8</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2910897.1</v>
+        <v>2913824.8</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1200257.2</v>
+        <v>1201454.4</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>56955.7</v>
+        <v>57014.1</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>741236.7</v>
+        <v>741164.9</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>723977.6</v>
+        <v>724705</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>732021.8</v>
+        <v>732757.3</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>740066</v>
+        <v>740809.5</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>740066</v>
+        <v>740809.5</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>732021.8</v>
+        <v>732757.3</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>726104.2</v>
+        <v>726833.7</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>685641.9</v>
+        <v>686330.9</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>629077.9</v>
+        <v>629709.8</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>466568.6</v>
+        <v>467034.5</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316602.1</v>
+        <v>316916.4</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189615.5</v>
+        <v>189802.9</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89796.8</v>
+        <v>89885.3</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34757.5</v>
+        <v>34754.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33947.1</v>
+        <v>33981.9</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34324.3</v>
+        <v>34359.5</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34701.5</v>
+        <v>34737.1</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34701.5</v>
+        <v>34737.1</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34324.3</v>
+        <v>34359.5</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34324.3</v>
+        <v>34359.5</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34701.5</v>
+        <v>34737.1</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34701.5</v>
+        <v>34737.1</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33947.1</v>
+        <v>33981.9</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34324.3</v>
+        <v>34359.5</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34701.5</v>
+        <v>34737.1</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34701.5</v>
+        <v>34737.1</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33947.1</v>
+        <v>33981.9</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23008.6</v>
+        <v>23032.2</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1346.2)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1345.74)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66791억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66789억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68546억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68537억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72093억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72084억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76075억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76066억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 80863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80855억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 85863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85856억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91120억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91113억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95308억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98309억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66791억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66789억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68546억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68537억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72093억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72084억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76075억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76066억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 80863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80855억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 85863억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85856억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91120억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91113억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95308억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98315억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98309억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175083억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175082억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187479억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187477억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191881억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191877억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205721억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205716억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220497억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220490억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236252억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236244억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244341억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244331억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261937억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261926억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 175083억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 175082억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187479억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187477억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191881억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191877억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205721억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205716억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220497억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220490억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236252억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236244억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244341억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244331억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 261937억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261926억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52977.1</v>
+        <v>52973.1</v>
       </c>
     </row>
     <row r="30">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9445,33 +9445,33 @@
         <v>0.226363624</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.15513122</v>
+        <v>0.155083254</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.187038432</v>
+        <v>0.18688378</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.138519781</v>
+        <v>0.138380205</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153522679</v>
+        <v>0.153394259</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.210675755</v>
+        <v>0.210603789</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.252645276</v>
+        <v>0.252695065</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.26393207</v>
+        <v>0.263983028</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.252908698</v>
+        <v>0.252956812</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215828677</v>
+        <v>0.215874859</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.157199651</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.15749982</v>
+        <v>0.157499669</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157499796</v>
+        <v>0.157499723</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.15752814</v>
+        <v>0.157528266</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610232</v>
+        <v>0.157610342</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670282</v>
+        <v>0.157670324</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.15773029</v>
+        <v>0.157730362</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157790319</v>
+        <v>0.15779038</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157942009</v>
+        <v>0.157941992</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.158163085</v>
+        <v>0.158163018</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.002045864</v>
+        <v>0.002219706</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.003682209</v>
+        <v>0.001992804</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.007503897</v>
+        <v>-0.008844609999999999</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.897663690001</v>
+        <v>8697.904508838999</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.007159025</v>
+        <v>0.004886995</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.003574436</v>
+        <v>-0.001840368</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.007352606</v>
+        <v>-0.001684756</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.905035341</v>
+        <v>8697.891046711</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.0031769</v>
+        <v>-0.006822408</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.005028694</v>
+        <v>0.002582778</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.003657883</v>
+        <v>0.006392947</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-8.830000000000001e-05</v>
+        <v>-0.000733656</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.005521165</v>
+        <v>0.003949213</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.903175617999</v>
+        <v>8697.900429216001</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.009691629</v>
+        <v>-0.000320234</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.005581683</v>
+        <v>0.004160542</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.000260482</v>
+        <v>-0.001710315</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.902376376</v>
+        <v>8697.901816695001</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.005163005</v>
+        <v>0.00551919</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.005611329</v>
+        <v>-0.002624819</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.091229885</v>
+        <v>0.091226089</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.08624531000000001</v>
+        <v>0.086234479</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028192563</v>
+        <v>0.028182823</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08621218</v>
+        <v>0.08620475</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.08473632</v>
+        <v>0.08473035399999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.083296066</v>
+        <v>0.08329144199999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039476702</v>
+        <v>0.039471625</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082614035</v>
+        <v>0.082611647</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.079167798</v>
+        <v>0.079166414</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.073691932</v>
+        <v>0.07368886500000001</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.070803581</v>
+        <v>0.070794645</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023478611</v>
+        <v>0.023470499</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.072127763</v>
+        <v>0.072121168</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07182427399999999</v>
+        <v>0.07181889499999999</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071453985</v>
+        <v>0.071449755</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034238702</v>
+        <v>0.034234033</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.07201512</v>
+        <v>0.07201263199999999</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069693321</v>
+        <v>0.069691718</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269481862587</v>
+        <v>0.1989270140199398</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842986317141213</v>
+        <v>0.04842984396020988</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600275542688268</v>
+        <v>0.7600277752656174</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816777281250812</v>
+        <v>0.02816787182365922</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311616137776667</v>
+        <v>0.1311619244925925</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1420.42</v>
+        <v>1420.24</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1419.73</v>
+        <v>1419.14</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1419.73</v>
+        <v>1419.14</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1421.21</v>
+        <v>1420.62</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1424.34</v>
+        <v>1423.75</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1424.34</v>
+        <v>1423.75</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1424.3</v>
+        <v>1423.71</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1423.97</v>
+        <v>1423.38</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1424.51</v>
+        <v>1423.92</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1431.84</v>
+        <v>1431.24</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1438.19</v>
+        <v>1437.6</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1440.97</v>
+        <v>1440.38</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1437.59</v>
+        <v>1437</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1396.16</v>
+        <v>1395.57</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1396.16</v>
+        <v>1395.57</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>790822.6</v>
+        <v>790722.4</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>773258.2</v>
+        <v>772936.4</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>781850</v>
+        <v>781524.5</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>785584.6</v>
+        <v>785258</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>775546.6</v>
+        <v>775224.8</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>767116.7</v>
+        <v>766798.4</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>761193.2</v>
+        <v>760877.4</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>721068</v>
+        <v>720768.7</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>664446.9</v>
+        <v>664171.2</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>501016.4</v>
+        <v>500809.6</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>351275.8</v>
+        <v>351131.5</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224539.9</v>
+        <v>224447.8</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124622.3</v>
+        <v>124571.1</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33981.9</v>
+        <v>33967.5</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23032.2</v>
+        <v>23022.4</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704408</v>
+        <v>2704307.8</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3116239.4</v>
+        <v>3114943.7</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2913824.8</v>
+        <v>2912615.7</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1201454.4</v>
+        <v>1200960</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>57014.1</v>
+        <v>56989.9</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>775919</v>
+        <v>775821</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>758686.9</v>
+        <v>758372.1</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>767116.7</v>
+        <v>766798.4</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>775546.6</v>
+        <v>775224.8</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>775546.6</v>
+        <v>775224.8</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>767116.7</v>
+        <v>766798.4</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>761193.2</v>
+        <v>760877.4</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>721068</v>
+        <v>720768.7</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>664446.9</v>
+        <v>664171.2</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>501016.4</v>
+        <v>500809.6</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>351275.8</v>
+        <v>351131.5</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224539.9</v>
+        <v>224447.8</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124622.3</v>
+        <v>124571.1</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33981.9</v>
+        <v>33967.5</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23032.2</v>
+        <v>23022.4</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2644010.5</v>
+        <v>2643912.5</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3076896.8</v>
+        <v>3075620.1</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2913824.8</v>
+        <v>2912615.7</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1201454.4</v>
+        <v>1200960</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>57014.1</v>
+        <v>56989.9</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>741164.9</v>
+        <v>741071.4</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>724705</v>
+        <v>724404.6</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>732757.3</v>
+        <v>732453.5</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>740809.5</v>
+        <v>740502.4</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>740809.5</v>
+        <v>740502.4</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>732757.3</v>
+        <v>732453.5</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>726833.7</v>
+        <v>726532.4</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>686330.9</v>
+        <v>686046.4</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>629709.8</v>
+        <v>629448.8</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>467034.5</v>
+        <v>466842.1</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316916.4</v>
+        <v>316786.6</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189802.9</v>
+        <v>189725.5</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89885.3</v>
+        <v>89848.8</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34754.1</v>
+        <v>34749.6</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33981.9</v>
+        <v>33967.5</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34359.5</v>
+        <v>34344.9</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34737.1</v>
+        <v>34722.3</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34737.1</v>
+        <v>34722.3</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34359.5</v>
+        <v>34344.9</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34359.5</v>
+        <v>34344.9</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34737.1</v>
+        <v>34722.3</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34737.1</v>
+        <v>34722.3</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33981.9</v>
+        <v>33967.5</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34359.5</v>
+        <v>34344.9</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34737.1</v>
+        <v>34722.3</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34737.1</v>
+        <v>34722.3</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33981.9</v>
+        <v>33967.5</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23032.2</v>
+        <v>23022.4</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1345.74)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1345.14)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.5</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="33">
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>291500</v>
+        <v>279500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>290000</v>
+        <v>276500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>312600</v>
+        <v>307083.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>291500</v>
+        <v>279500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -50552,7 +50552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66789억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66782억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68537억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68498억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72084억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72044억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76066억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76023억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 80855억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80813억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 85856억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85815억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91113억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91074억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95308억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95271억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98309억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98275억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66789억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66782억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68537억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68498억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72084억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72044억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76066억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76023억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 80855억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80813억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 85856억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85815억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91113억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91074억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95308억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95271억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98309억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98275억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175082억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175081억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187477억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187469억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191877억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191862억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205716억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205693억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220490억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220459억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236244억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236206억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244331억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244286억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261926억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 175082억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 175081억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187477억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187469억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191877억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191862억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205716억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205693억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220490억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220459억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236244억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236206억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244331억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244286억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 261926억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.8, "op_wape_pct": 40.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "subsidiary_yard_scaled", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 74060.53, "rev_act": 75814.36, "op_pred": 7553.95, "op_act": 10537.75}, {"q": "2025Q4", "rev_pred": 74060.53, "rev_act": 81516.57, "op_pred": 7553.95, "op_act": 10379.19}, {"q": "2026Q1", "rev_pred": 73789.18, "rev_act": 81408.9, "op_pred": 7526.28, "op_act": 13559.7}, {"q": "2026Q2", "rev_pred": 73924.83, "rev_act": 89270.46, "op_pred": 7540.11, "op_act": 16451.46}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 9.8, "op_wape_pct": 40.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "subsidiary_yard_scaled", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 74060.61, "rev_act": 75814.36, "op_pred": 7553.97, "op_act": 10537.75}, {"q": "2025Q4", "rev_pred": 74060.61, "rev_act": 81516.57, "op_pred": 7553.97, "op_act": 10379.19}, {"q": "2026Q1", "rev_pred": 73788.96, "rev_act": 81408.9, "op_pred": 7526.26, "op_act": 13559.7}, {"q": "2026Q2", "rev_pred": 73924.76, "rev_act": 89270.46, "op_pred": 7540.11, "op_act": 16451.46}]}</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52973.1</v>
+        <v>52956.6</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.28</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="33">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2526</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="34">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>279500</v>
+        <v>276500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>276500</v>
+        <v>262000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>307083.3</v>
+        <v>302642.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9442,36 +9442,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.226363624</v>
+        <v>0.226362569</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.155083254</v>
+        <v>0.154959353</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.18688378</v>
+        <v>0.186218988</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.138380205</v>
+        <v>0.137745392</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153394259</v>
+        <v>0.152737876</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.210603789</v>
+        <v>0.210105183</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.252695065</v>
+        <v>0.252807895</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.263983028</v>
+        <v>0.264144399</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.252956812</v>
+        <v>0.253186906</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215874859</v>
+        <v>0.216089934</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9753,42 +9753,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.157199651</v>
+        <v>0.157199786</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157499669</v>
+        <v>0.157499783</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157499723</v>
+        <v>0.15749966</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.157528266</v>
+        <v>0.15752814</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610342</v>
+        <v>0.157610372</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670324</v>
+        <v>0.157670318</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157730362</v>
+        <v>0.157730319</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.15779038</v>
+        <v>0.157790273</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157941992</v>
+        <v>0.157941995</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.158163018</v>
+        <v>0.158163114</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.002219706</v>
+        <v>0.001735375</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.001992804</v>
+        <v>-0.004371235</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.008844609999999999</v>
+        <v>-0.009984971</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.904508838999</v>
+        <v>8697.896243351001</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.004886995</v>
+        <v>0.003162072</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.001840368</v>
+        <v>-0.007466016</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.001684756</v>
+        <v>-9.2557e-05</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.891046711</v>
+        <v>8697.891142806</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.006822408</v>
+        <v>-0.002831835</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.002582778</v>
+        <v>-0.003464242</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.006392947</v>
+        <v>0.004254596</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.000733656</v>
+        <v>-0.005011322</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.003949213</v>
+        <v>-0.007369384</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.900429216001</v>
+        <v>8697.899979692</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.000320234</v>
+        <v>-0.001926596</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.004160542</v>
+        <v>0.00145439</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.001710315</v>
+        <v>-0.004271596</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.901816695001</v>
+        <v>8697.899567716</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.00551919</v>
+        <v>-0.005081042</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.002624819</v>
+        <v>-0.00053805</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.091226089</v>
+        <v>0.09121644800000001</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.086234479</v>
+        <v>0.08618772199999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028182823</v>
+        <v>0.028138167</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08620475</v>
+        <v>0.08616430999999999</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.08473035399999999</v>
+        <v>0.084697994</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.08329144199999999</v>
+        <v>0.08326604899999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039471625</v>
+        <v>0.039443766</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082611647</v>
+        <v>0.082597139</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.079166414</v>
+        <v>0.079156981</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.07368886500000001</v>
+        <v>0.073681077</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.070794645</v>
+        <v>0.070756148</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023470499</v>
+        <v>0.023433054</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.072121168</v>
+        <v>0.07208632099999999</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07181889499999999</v>
+        <v>0.071789964</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071449755</v>
+        <v>0.071426323</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034234033</v>
+        <v>0.034209026</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.07201263199999999</v>
+        <v>0.071998021</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069691718</v>
+        <v>0.06968152800000001</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,11 +12327,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>279500</v>
+        <v>276500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 301,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 291,500원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989270140199398</v>
+        <v>0.1989269798832284</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842984396020988</v>
+        <v>0.04842985910825098</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600277752656174</v>
+        <v>0.7600276249667989</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816787182365922</v>
+        <v>0.0281677858078709</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311619244925925</v>
+        <v>0.1311616506964567</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1420.24</v>
+        <v>1419.78</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1419.14</v>
+        <v>1416.62</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1419.14</v>
+        <v>1416.62</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1420.62</v>
+        <v>1418.1</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1423.75</v>
+        <v>1421.23</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1423.75</v>
+        <v>1421.23</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1423.71</v>
+        <v>1421.19</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1423.38</v>
+        <v>1420.86</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1423.92</v>
+        <v>1421.4</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1431.24</v>
+        <v>1428.72</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1437.6</v>
+        <v>1435.08</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1440.38</v>
+        <v>1437.86</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1437</v>
+        <v>1434.48</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1395.57</v>
+        <v>1393.05</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1395.57</v>
+        <v>1393.05</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>790722.4</v>
+        <v>790470.2</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>772936.4</v>
+        <v>771563.8</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>781524.5</v>
+        <v>780136.8</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>785258</v>
+        <v>783865</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>775224.8</v>
+        <v>773852.7</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>766798.4</v>
+        <v>765441.2</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>760877.4</v>
+        <v>759530.6</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>720768.7</v>
+        <v>719492.6</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>664171.2</v>
+        <v>662995.8</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>500809.6</v>
+        <v>499927.8</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>351131.5</v>
+        <v>350516</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224447.8</v>
+        <v>224055.2</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124571.1</v>
+        <v>124352.7</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33967.5</v>
+        <v>33906.2</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23022.4</v>
+        <v>22980.9</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704307.8</v>
+        <v>2704055.6</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3114943.7</v>
+        <v>3109418.3</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2912615.7</v>
+        <v>2907460.2</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1200960</v>
+        <v>1198851.7</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>56989.9</v>
+        <v>56887.1</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>775821</v>
+        <v>775574.4</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>758372.1</v>
+        <v>757029.8</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>766798.4</v>
+        <v>765441.2</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>775224.8</v>
+        <v>773852.7</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>775224.8</v>
+        <v>773852.7</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>766798.4</v>
+        <v>765441.2</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>760877.4</v>
+        <v>759530.6</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>720768.7</v>
+        <v>719492.6</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>664171.2</v>
+        <v>662995.8</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>500809.6</v>
+        <v>499927.8</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>351131.5</v>
+        <v>350516</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224447.8</v>
+        <v>224055.2</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124571.1</v>
+        <v>124352.7</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33967.5</v>
+        <v>33906.2</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23022.4</v>
+        <v>22980.9</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2643912.5</v>
+        <v>2643665.9</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3075620.1</v>
+        <v>3070176.4</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2912615.7</v>
+        <v>2907460.2</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1200960</v>
+        <v>1198851.7</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>56989.9</v>
+        <v>56887.1</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>741071.4</v>
+        <v>740836</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>724404.6</v>
+        <v>723123.6</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>732453.5</v>
+        <v>731158.3</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>740502.4</v>
+        <v>739193</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>740502.4</v>
+        <v>739193</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>732453.5</v>
+        <v>731158.3</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>726532.4</v>
+        <v>725247.7</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>686046.4</v>
+        <v>684833</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>629448.8</v>
+        <v>628336.1</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>466842.1</v>
+        <v>466021.7</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316786.6</v>
+        <v>316233.1</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189725.5</v>
+        <v>189395.5</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89848.8</v>
+        <v>89693</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34749.6</v>
+        <v>34738.3</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33967.5</v>
+        <v>33906.2</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34344.9</v>
+        <v>34282.9</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34722.3</v>
+        <v>34659.7</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34722.3</v>
+        <v>34659.7</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34344.9</v>
+        <v>34282.9</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34344.9</v>
+        <v>34282.9</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34722.3</v>
+        <v>34659.7</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34722.3</v>
+        <v>34659.7</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33967.5</v>
+        <v>33906.2</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34344.9</v>
+        <v>34282.9</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34722.3</v>
+        <v>34659.7</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34722.3</v>
+        <v>34659.7</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33967.5</v>
+        <v>33906.2</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23022.4</v>
+        <v>22980.9</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1345.14)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.63)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
     </row>
@@ -48737,48 +48737,45 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20260930800164</t>
+          <t>20261006800410</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OFFSH</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>338500</v>
+      </c>
+      <c r="E120" t="n">
+        <v>291.833</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1159.91</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M120" t="b">
         <v>1</v>
-      </c>
-      <c r="D120" t="n">
-        <v>1953900</v>
-      </c>
-      <c r="E120" t="n">
-        <v>1485.076</v>
-      </c>
-      <c r="F120" t="n">
-        <v>1315.69</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2027-06-01</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M120" t="b">
-        <v>0</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -48790,36 +48787,39 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>20261006800410</t>
+          <t>20261013800237</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>338500</v>
+        <v>1964800</v>
       </c>
       <c r="E121" t="n">
-        <v>291.833</v>
+        <v>1493.361</v>
       </c>
       <c r="F121" t="n">
-        <v>1159.91</v>
+        <v>1315.69</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="M121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" t="b">
         <v>1</v>
@@ -50552,7 +50552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66782억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 66780억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68498억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68536억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72044억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72081억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76023억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 76059억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 80813억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80847억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 85815억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85848억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91074억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 91106억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95271억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 95300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98275억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 98302억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66782억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 66780억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68498억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68536억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72044억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72081억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76023억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 76059억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 80813억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80847억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 85815억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85848억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91074억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 91106억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95271억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 95300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98275억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 98302억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2147,43 +2147,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187469억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187475억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191862억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191875억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205693억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205712억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220459억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220485억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236206억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236238억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244286억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244324억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261918억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2207,43 +2207,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187469억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187475억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191862억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191875억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205693억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205712억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220459억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220485억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236206억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236238억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244286억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244324억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 261874억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261918억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52956.6</v>
+        <v>52970.9</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="32">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2525</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="34">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>276500</v>
+        <v>276000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>302642.9</v>
+        <v>299250</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9445,33 +9445,33 @@
         <v>0.226362569</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.154959353</v>
+        <v>0.154940093</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.186218988</v>
+        <v>0.186875182</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.137745392</v>
+        <v>0.138338422</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.152737876</v>
+        <v>0.153283179</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.210105183</v>
+        <v>0.210643384</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.252807895</v>
+        <v>0.252596505</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.264144399</v>
+        <v>0.26392718</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.253186906</v>
+        <v>0.25298186</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.216089934</v>
+        <v>0.215894908</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.157199786</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157499783</v>
+        <v>0.157499754</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.15749966</v>
+        <v>0.157499726</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.15752814</v>
+        <v>0.157528144</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610372</v>
+        <v>0.157610364</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670318</v>
+        <v>0.157670322</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157730319</v>
+        <v>0.157730365</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157790273</v>
+        <v>0.157790375</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157941995</v>
+        <v>0.157941976</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.158163114</v>
+        <v>0.15816308</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.001735375</v>
+        <v>0.00262769</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.004371235</v>
+        <v>-0.003646454</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>-0.009984971</v>
+        <v>0.005051696</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.896243351001</v>
+        <v>8697.895321619</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.003162072</v>
+        <v>-0.000154997</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.007466016</v>
+        <v>-0.004387371</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-9.2557e-05</v>
+        <v>-0.001767916</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.891142806</v>
+        <v>8697.903342363999</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.002831835</v>
+        <v>-0.012008685</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.003464242</v>
+        <v>-0.002323612</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004254596</v>
+        <v>0.004986382</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.005011322</v>
+        <v>-0.006411314</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.007369384</v>
+        <v>-0.000898777</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.899979692</v>
+        <v>8697.906724398001</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>-0.001926596</v>
+        <v>0.000594322</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.00145439</v>
+        <v>-0.000765314</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.004271596</v>
+        <v>-0.002506646</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.899567716</v>
+        <v>8697.895077707</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.005081042</v>
+        <v>-0.007024248</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.00053805</v>
+        <v>0.004948396</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.09121644800000001</v>
+        <v>0.091214929</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.08618772199999999</v>
+        <v>0.08623473399999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028138167</v>
+        <v>0.028179966</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.08616430999999999</v>
+        <v>0.086197565</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.084697994</v>
+        <v>0.08472436899999999</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.08326604899999999</v>
+        <v>0.08328648499999999</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039443766</v>
+        <v>0.0394662</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082597139</v>
+        <v>0.082608128</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.079156981</v>
+        <v>0.07916352</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.073681077</v>
+        <v>0.073679851</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.070756148</v>
+        <v>0.070794725</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023433054</v>
+        <v>0.023468028</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07208632099999999</v>
+        <v>0.07211506299999999</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.071789964</v>
+        <v>0.07181361</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071426323</v>
+        <v>0.071445204</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034209026</v>
+        <v>0.034229237</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.071998021</v>
+        <v>0.072009243</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.06968152800000001</v>
+        <v>0.069688853</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,11 +12327,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>276500</v>
+        <v>276000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 291,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 282,000원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269798832284</v>
+        <v>0.198926907005909</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842985910825098</v>
+        <v>0.04842983750424198</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600276249667989</v>
+        <v>0.7600276295178083</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0281677858078709</v>
+        <v>0.02816782154068848</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311616506964567</v>
+        <v>0.1311618617080665</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1419.78</v>
+        <v>1419.71</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1416.62</v>
+        <v>1419.13</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1416.62</v>
+        <v>1419.13</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1418.1</v>
+        <v>1420.61</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1421.23</v>
+        <v>1423.74</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1421.23</v>
+        <v>1423.74</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1421.19</v>
+        <v>1423.7</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1420.86</v>
+        <v>1423.36</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1421.4</v>
+        <v>1423.91</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1428.72</v>
+        <v>1431.23</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1435.08</v>
+        <v>1437.59</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1437.86</v>
+        <v>1440.37</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1434.48</v>
+        <v>1436.98</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1393.05</v>
+        <v>1395.56</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1393.05</v>
+        <v>1395.56</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>790470.2</v>
+        <v>790430.1</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>771563.8</v>
+        <v>772929.8</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>780136.8</v>
+        <v>781517.9</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>783865</v>
+        <v>785251.3</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>773852.7</v>
+        <v>775218.3</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>765441.2</v>
+        <v>766792</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>759530.6</v>
+        <v>760871</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>719492.6</v>
+        <v>720762.6</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>662995.8</v>
+        <v>664165.6</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>499927.8</v>
+        <v>500805.4</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>350516</v>
+        <v>351128.6</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224055.2</v>
+        <v>224446</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124352.7</v>
+        <v>124570.1</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33906.2</v>
+        <v>33967.2</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>22980.9</v>
+        <v>23022.2</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704055.6</v>
+        <v>2704015.5</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3109418.3</v>
+        <v>3114917.3</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2907460.2</v>
+        <v>2912591.2</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1198851.7</v>
+        <v>1200950.1</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>56887.1</v>
+        <v>56989.4</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>775574.4</v>
+        <v>775535.2</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>757029.8</v>
+        <v>758365.7</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>765441.2</v>
+        <v>766792</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>773852.7</v>
+        <v>775218.3</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>773852.7</v>
+        <v>775218.3</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>765441.2</v>
+        <v>766792</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>759530.6</v>
+        <v>760871</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>719492.6</v>
+        <v>720762.6</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>662995.8</v>
+        <v>664165.6</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>499927.8</v>
+        <v>500805.4</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>350516</v>
+        <v>351128.6</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224055.2</v>
+        <v>224446</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124352.7</v>
+        <v>124570.1</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33906.2</v>
+        <v>33967.2</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>22980.9</v>
+        <v>23022.2</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2643665.9</v>
+        <v>2643626.7</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3070176.4</v>
+        <v>3075594.3</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2907460.2</v>
+        <v>2912591.2</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1198851.7</v>
+        <v>1200950.1</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>56887.1</v>
+        <v>56989.4</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>740836</v>
+        <v>740798.6</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>723123.6</v>
+        <v>724398.5</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>731158.3</v>
+        <v>732447.3</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>739193</v>
+        <v>740496.2</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>739193</v>
+        <v>740496.2</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>731158.3</v>
+        <v>732447.3</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>725247.7</v>
+        <v>726526.3</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>684833</v>
+        <v>686040.6</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>628336.1</v>
+        <v>629443.5</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>466021.7</v>
+        <v>466838.2</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316233.1</v>
+        <v>316783.9</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189395.5</v>
+        <v>189723.9</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89693</v>
+        <v>89848</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34738.3</v>
+        <v>34736.5</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33906.2</v>
+        <v>33967.2</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34282.9</v>
+        <v>34344.6</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34659.7</v>
+        <v>34722.1</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34659.7</v>
+        <v>34722.1</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34282.9</v>
+        <v>34344.6</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34282.9</v>
+        <v>34344.6</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34659.7</v>
+        <v>34722.1</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34659.7</v>
+        <v>34722.1</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33906.2</v>
+        <v>33967.2</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34282.9</v>
+        <v>34344.6</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34659.7</v>
+        <v>34722.1</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34659.7</v>
+        <v>34722.1</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33906.2</v>
+        <v>33967.2</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>22980.9</v>
+        <v>23022.2</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.63)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.39)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
     </row>
@@ -50552,7 +50552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 66780억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 67139억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68536억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 68778억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72081억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72100억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 76059억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 75903억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 80847억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 85848억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85477억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 91106억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 90701억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 95300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 94918억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 98302억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 97985억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 66780억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 67139억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68536억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 68778억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72081억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72100억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 76059억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 75903억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 80847억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 85848억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85477억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 91106억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 90701억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 95300억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 94918억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 98302억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 97985억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175081억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175143억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187475억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187578억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191875억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191980억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205712억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205787억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220485억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220506억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236238억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236189억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244324억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244199억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261918억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261718억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 175081억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 175143억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187475억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187578억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191875억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 191980억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205712억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205787억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220485억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220506억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236238억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236189억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244324억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244199억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 261918억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261718억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4839,7 +4839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52970.9</v>
+        <v>53083.2</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.21</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="33">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2526</v>
+        <v>0.2531</v>
       </c>
     </row>
     <row r="34">
@@ -8049,35 +8049,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8168,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8287,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8406,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8525,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8644,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8763,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8882,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9017,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>276000</v>
+        <v>271500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9199,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>262000</v>
+        <v>254500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9290,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>299250</v>
+        <v>290000</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9445,33 +9445,33 @@
         <v>0.226362569</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.154940093</v>
+        <v>0.161143004</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.186875182</v>
+        <v>0.191059736</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.138338422</v>
+        <v>0.138624967</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153283179</v>
+        <v>0.150926654</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.210643384</v>
+        <v>0.199926489</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.252596505</v>
+        <v>0.24280111</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.26392718</v>
+        <v>0.258004037</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.25298186</v>
+        <v>0.250504283</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.215894908</v>
+        <v>0.216271127</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9756,39 @@
         <v>0.157199786</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157499754</v>
+        <v>0.157474523</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157499726</v>
+        <v>0.157471221</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.157528144</v>
+        <v>0.157499716</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157610364</v>
+        <v>0.157575529</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157670322</v>
+        <v>0.157635541</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157730365</v>
+        <v>0.157692405</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157790375</v>
+        <v>0.157749302</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157941976</v>
+        <v>0.157894548</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.15816308</v>
+        <v>0.158103028</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11123,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.00262769</v>
+        <v>0.001880563</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.003646454</v>
+        <v>-0.001293359</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.005051696</v>
+        <v>0.000332475</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.895321619</v>
+        <v>8697.899452186</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>-0.000154997</v>
+        <v>0.000188625</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.004387371</v>
+        <v>-0.01256862</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.001767916</v>
+        <v>-0.000911501</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.903342363999</v>
+        <v>8697.907012047001</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.012008685</v>
+        <v>9.579199999999999e-05</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.002323612</v>
+        <v>-0.01221717</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11251,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004986382</v>
+        <v>0.003521945</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.006411314</v>
+        <v>-0.005032497</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.000898777</v>
+        <v>-0.003096059</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.906724398001</v>
+        <v>8697.901307758</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.000594322</v>
+        <v>0.003373897</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.000765314</v>
+        <v>-0.00998307</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.002506646</v>
+        <v>-0.001373716</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.895077707</v>
+        <v>8697.90448126</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.007024248</v>
+        <v>-0.002004959</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.004948396</v>
+        <v>-0.011332408</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11510,33 @@
         <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.091214929</v>
+        <v>0.091684719</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.08623473399999999</v>
+        <v>0.086483518</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028179966</v>
+        <v>0.028171054</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.086197565</v>
+        <v>0.085954353</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.08472436899999999</v>
+        <v>0.08438123</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.08328648499999999</v>
+        <v>0.08290913</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.0394662</v>
+        <v>0.039102084</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082608128</v>
+        <v>0.082308799</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.07916352</v>
+        <v>0.078952812</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11638,33 @@
         <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.073679851</v>
+        <v>0.07405932899999999</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.070794725</v>
+        <v>0.071004492</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023468028</v>
+        <v>0.023463138</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07211506299999999</v>
+        <v>0.07191923</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07181361</v>
+        <v>0.071527412</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071445204</v>
+        <v>0.071122616</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.034229237</v>
+        <v>0.033912409</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.072009243</v>
+        <v>0.07174285900000001</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069688853</v>
+        <v>0.069496167</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,11 +12327,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>276000</v>
+        <v>271500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 282,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 263,000원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.198926907005909</v>
+        <v>0.1989269006109433</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842983750424198</v>
+        <v>0.04842985688977399</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600276295178083</v>
+        <v>0.7600275533939465</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816782154068848</v>
+        <v>0.02816790642121412</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311618617080665</v>
+        <v>0.1311624324275712</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38720,7 +38720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ128"/>
+  <dimension ref="A1:BQ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -41096,49 +41096,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
     </row>
     <row r="19">
@@ -41240,49 +41240,49 @@
         <v>1442.42</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1419.71</v>
+        <v>1419.33</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1419.13</v>
+        <v>1416.32</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1419.13</v>
+        <v>1416.32</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1420.61</v>
+        <v>1417.81</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1423.74</v>
+        <v>1420.93</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1423.74</v>
+        <v>1420.93</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1423.7</v>
+        <v>1420.9</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1423.36</v>
+        <v>1420.56</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1423.91</v>
+        <v>1421.1</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1431.23</v>
+        <v>1428.43</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1437.59</v>
+        <v>1434.79</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1440.37</v>
+        <v>1437.57</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1436.98</v>
+        <v>1434.18</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1395.56</v>
+        <v>1392.75</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1395.56</v>
+        <v>1392.75</v>
       </c>
     </row>
     <row r="20">
@@ -41384,49 +41384,49 @@
         <v>799564</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>790430.1</v>
+        <v>790216.3</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>772929.8</v>
+        <v>771402.1</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>781517.9</v>
+        <v>779973.2</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>785251.3</v>
+        <v>783700.8</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>775218.3</v>
+        <v>773690.9</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>766792</v>
+        <v>765281.3</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>760871</v>
+        <v>759371.9</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>720762.6</v>
+        <v>719342.2</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>664165.6</v>
+        <v>662857.2</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>500805.4</v>
+        <v>499823.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>351128.6</v>
+        <v>350443.4</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224446</v>
+        <v>224008.9</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124570.1</v>
+        <v>124326.9</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33967.2</v>
+        <v>33899</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>23022.2</v>
+        <v>22976</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41450,19 +41450,19 @@
         <v>402230.7</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2704015.5</v>
+        <v>2703801.7</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3114917.3</v>
+        <v>3108767</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2912591.2</v>
+        <v>2906852.6</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1200950.1</v>
+        <v>1198603.1</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>56989.4</v>
+        <v>56875</v>
       </c>
     </row>
     <row r="21">
@@ -41564,49 +41564,49 @@
         <v>784391.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>775535.2</v>
+        <v>775326.1</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>758365.7</v>
+        <v>756871.6</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>766792</v>
+        <v>765281.3</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>775218.3</v>
+        <v>773690.9</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>775218.3</v>
+        <v>773690.9</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>766792</v>
+        <v>765281.3</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>760871</v>
+        <v>759371.9</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>720762.6</v>
+        <v>719342.2</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>664165.6</v>
+        <v>662857.2</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>500805.4</v>
+        <v>499823.9</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>351128.6</v>
+        <v>350443.4</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224446</v>
+        <v>224008.9</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124570.1</v>
+        <v>124326.9</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33967.2</v>
+        <v>33899</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>23022.2</v>
+        <v>22976</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41630,19 +41630,19 @@
         <v>319391.5</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2643626.7</v>
+        <v>2643417.6</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3075594.3</v>
+        <v>3069534.7</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2912591.2</v>
+        <v>2906852.6</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1200950.1</v>
+        <v>1198603.1</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>56989.4</v>
+        <v>56875</v>
       </c>
     </row>
     <row r="22">
@@ -41744,43 +41744,43 @@
         <v>752546.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>740798.6</v>
+        <v>740599.1</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>724398.5</v>
+        <v>722972.6</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>732447.3</v>
+        <v>731005.7</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>740496.2</v>
+        <v>739038.7</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>740496.2</v>
+        <v>739038.7</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>732447.3</v>
+        <v>731005.7</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>726526.3</v>
+        <v>725096.3</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>686040.6</v>
+        <v>684690</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>629443.5</v>
+        <v>628205</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>466838.2</v>
+        <v>465925</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316783.9</v>
+        <v>316167.8</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189723.9</v>
+        <v>189356.6</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89848</v>
+        <v>89674.60000000001</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41888,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34736.5</v>
+        <v>34727</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33967.2</v>
+        <v>33899</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34344.6</v>
+        <v>34275.6</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34722.1</v>
+        <v>34652.3</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34722.1</v>
+        <v>34652.3</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34344.6</v>
+        <v>34275.6</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34344.6</v>
+        <v>34275.6</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34722.1</v>
+        <v>34652.3</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34722.1</v>
+        <v>34652.3</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33967.2</v>
+        <v>33899</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34344.6</v>
+        <v>34275.6</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34722.1</v>
+        <v>34652.3</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34722.1</v>
+        <v>34652.3</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33967.2</v>
+        <v>33899</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>23022.2</v>
+        <v>22976</v>
       </c>
     </row>
     <row r="24">
@@ -42224,63 +42224,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.39)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1342.11)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
     </row>
@@ -48838,49 +48838,102 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
-        </is>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20261015800358</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>4</v>
+      </c>
+      <c r="D122" t="n">
+        <v>625800</v>
+      </c>
+      <c r="E122" t="n">
+        <v>466.281</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1342.11</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M122" t="b">
+        <v>0</v>
+      </c>
+      <c r="N122" t="b">
+        <v>0</v>
+      </c>
+      <c r="O122" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 22건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
+          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → HEDGE 70% 가정(레퍼런스 SLS 시트 HEDGE 행은 미포 65%·삼성重 100% — 그 사이에 둔 설정값). hedge_rate 는 계약별 수주시점 환율로 대체)</t>
+          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 23건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
+          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → HEDGE 70% 가정(레퍼런스 SLS 시트 HEDGE 행은 미포 65%·삼성重 100% — 그 사이에 둔 설정값). hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 7%, ③중마진 80%, ④호황 13%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
+          <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 7%, ③중마진 80%, ④호황 13%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>⚠ 정기보고서 부문 매출(3개월분)을 만들 수 없어 화해 없음</t>
         </is>
@@ -49158,32 +49211,32 @@
         <v/>
       </c>
       <c r="H6" s="34" t="n">
-        <v>4164.54</v>
+        <v>3980.69</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>9391.610000000001</v>
+        <v>8885.68</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>16168.84</v>
+        <v>15409.2</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>23977.29</v>
+        <v>23032.36</v>
       </c>
       <c r="L6" s="20">
         <f>SUM(H6:K6)</f>
         <v/>
       </c>
       <c r="M6" s="34" t="n">
-        <v>32298.09</v>
+        <v>31236.27</v>
       </c>
       <c r="N6" s="34" t="n">
-        <v>40612.33</v>
+        <v>39502</v>
       </c>
       <c r="O6" s="34" t="n">
-        <v>48401.1</v>
+        <v>47310.68</v>
       </c>
       <c r="P6" s="34" t="n">
-        <v>55145.52</v>
+        <v>54143.41</v>
       </c>
       <c r="Q6" s="20">
         <f>SUM(M6:P6)</f>
@@ -49770,32 +49823,32 @@
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>2695.64</v>
+        <v>2511.31</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>6306.65</v>
+        <v>5799.41</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>11074.16</v>
+        <v>10312.57</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>16624.54</v>
+        <v>15677.23</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
-        <v>22584.18</v>
+        <v>21519.73</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>28579.5</v>
+        <v>27466.5</v>
       </c>
       <c r="O18" s="34" t="n">
-        <v>34236.87</v>
+        <v>33143.91</v>
       </c>
       <c r="P18" s="34" t="n">
-        <v>39182.67</v>
+        <v>38178.36</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -50076,32 +50129,32 @@
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>7000.62</v>
+        <v>6817.34</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>15350.03</v>
+        <v>14845.59</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>26011.72</v>
+        <v>25254.28</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>38186.66</v>
+        <v>37244.33</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>51075.78</v>
+        <v>50016.68</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>63880.01</v>
+        <v>62772.29</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>75800.27</v>
+        <v>74712.07000000001</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>86037.53</v>
+        <v>85036.96000000001</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -50552,7 +50605,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55813,7 +55866,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/009540_model.xlsx
+++ b/argus/kship/models/009540_model.xlsx
@@ -668,55 +668,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 67139억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 67417억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 68778억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 69011억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 72100억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 72162억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 75903억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 75834억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 80562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 80393억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 85477억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 85242억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 90701억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 90441억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 94918억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 94674억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-HD현대重 모델 매출 97985억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
+HD현대重 모델 매출 97792억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -836,7 +836,7 @@
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(자회사 OPM 14.2% + 실측 차이 +1.7%p)</t>
+매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
@@ -1775,55 +1775,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 67139억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 67417억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 68778억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 69011억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 72100억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 72162억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 75903억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 75834억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 80562억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 80393억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 85477억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 85242억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 90701억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 90441억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 94918억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 94674억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: HD현대重 모델 매출 97985억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
+        <t>추정: HD현대重 모델 매출 97792억 × 연결/자회사 비율 1.410(2025Q4·2026Q1·2026Q2 실측 중위; 삼호·기타 자회사·내부거래 포함)
 [yoy]</t>
       </text>
     </comment>
@@ -2063,7 +2063,7 @@
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(자회사 OPM 14.2% + 실측 차이 +1.7%p)
+        <t>추정: 매출액 × OPM(자회사 OPM 14.1% + 실측 차이 +1.7%p)
 [ratio]</t>
       </text>
     </comment>
@@ -2123,7 +2123,7 @@
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 자회사 OPM 14.2% + 실측 차이 +1.7%p
+        <t>추정: 자회사 OPM 14.1% + 실측 차이 +1.7%p
 [divide]</t>
       </text>
     </comment>
@@ -2141,49 +2141,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175143억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 175191억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187578억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 187666억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 191980억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 192077억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205787억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 205870억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220506억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 220556억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236189억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 236194억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244199억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 244154억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261718억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.85억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 261625억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2201,49 +2201,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 175143억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 175191억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 187578억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 187666억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 191980억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 192077억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 205787억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 205870억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 220506억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 220556억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 236189억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 236194억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 244199억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 244154억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 261718억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 261625억 × 2.82%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 29860억 × 13.12%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4316,6 +4316,16 @@
       </text>
     </comment>
     <comment ref="BJ52" authorId="0" shapeId="0">
+      <text>
+        <t>모델 포함 규칙: 해양(type≠OTHER) · origin 분기말까지 체결분(이후 체결은 패널 신규수주에 포함으로 봄). 0 으로 바꾸면 그 계약을 매출에서 뺀다</t>
+      </text>
+    </comment>
+    <comment ref="BJ53" authorId="0" shapeId="0">
+      <text>
+        <t>모델 포함 규칙: 해양(type≠OTHER) · origin 분기말까지 체결분(이후 체결은 패널 신규수주에 포함으로 봄). 0 으로 바꾸면 그 계약을 매출에서 뺀다</t>
+      </text>
+    </comment>
+    <comment ref="BJ54" authorId="0" shapeId="0">
       <text>
         <t>모델 포함 규칙: 해양(type≠OTHER) · origin 분기말까지 체결분(이후 체결은 패널 신규수주에 포함으로 봄). 0 으로 바꾸면 그 계약을 매출에서 뺀다</t>
       </text>
@@ -4839,7 +4849,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5465,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>53083.2</v>
+        <v>53187.7</v>
       </c>
     </row>
     <row r="30">
@@ -5475,7 +5485,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.11</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="32">
@@ -5485,7 +5495,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="33">
@@ -5495,7 +5505,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2531</v>
+        <v>0.2536</v>
       </c>
     </row>
     <row r="34">
@@ -5505,7 +5515,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="35">
@@ -5515,7 +5525,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>589300</v>
+        <v>591400</v>
       </c>
     </row>
     <row r="36">
@@ -8049,35 +8059,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8168,35 +8178,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8287,35 +8297,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8406,35 +8416,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8525,35 +8535,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8644,35 +8654,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8763,35 +8773,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8882,35 +8892,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9017,7 +9027,7 @@
         <v>326500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>271500</v>
+        <v>244000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9199,7 +9209,7 @@
         <v>314000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>254500</v>
+        <v>236500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9290,7 +9300,7 @@
         <v>356596.8</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>290000</v>
+        <v>277375</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9445,33 +9455,33 @@
         <v>0.226362569</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.161143004</v>
+        <v>0.165955523</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.191059736</v>
+        <v>0.195102169</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.138624967</v>
+        <v>0.139614096</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.150926654</v>
+        <v>0.149867885</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.199926489</v>
+        <v>0.192461462</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.24280111</v>
+        <v>0.235184</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.258004037</v>
+        <v>0.253296935</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.250504283</v>
+        <v>0.248440581</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.216271127</v>
+        <v>0.216434279</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9756,39 +9766,39 @@
         <v>0.157199786</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.157474523</v>
+        <v>0.157455509</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.157471221</v>
+        <v>0.157446017</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.157499716</v>
+        <v>0.157471238</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.157575529</v>
+        <v>0.15754711</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.157635541</v>
+        <v>0.157603956</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.157692405</v>
+        <v>0.157657606</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.157749302</v>
+        <v>0.157714468</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.157894548</v>
+        <v>0.157853439</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.158103028</v>
+        <v>0.158052494</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -11123,36 +11133,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.001880563</v>
+        <v>0.000819238</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>-0.001293359</v>
+        <v>-0.002107975</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.000332475</v>
+        <v>-0.001047343</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>8697.899452186</v>
+        <v>8697.9032683</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.000188625</v>
+        <v>-0.003300753</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.01256862</v>
+        <v>-0.007320257</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.000911501</v>
+        <v>-7.2968e-05</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>8697.907012047001</v>
+        <v>8697.889283655</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>9.579199999999999e-05</v>
+        <v>-0.006933671</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>-0.01221717</v>
+        <v>-0.000392328</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -11251,36 +11261,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.003521945</v>
+        <v>0.001881628</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>-0.005032497</v>
+        <v>-0.004786166</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>-0.003096059</v>
+        <v>-0.000730637</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>8697.901307758</v>
+        <v>8697.899136796001</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.003373897</v>
+        <v>-0.006248691</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>-0.00998307</v>
+        <v>-0.00353087</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.001373716</v>
+        <v>-0.008283745</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>8697.90448126</v>
+        <v>8697.896050742</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.002004959</v>
+        <v>-0.011110072</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>-0.011332408</v>
+        <v>-0.00034731</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -11510,33 +11520,33 @@
         <v>0.09820029600000001</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.091684719</v>
+        <v>0.092049436</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.086483518</v>
+        <v>0.08673146399999999</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.028171054</v>
+        <v>0.028214778</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.085954353</v>
+        <v>0.085813295</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.08438123</v>
+        <v>0.08415466200000001</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.08290913</v>
+        <v>0.082649204</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.039102084</v>
+        <v>0.03885699</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.082308799</v>
+        <v>0.082099924</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.078952812</v>
+        <v>0.078808594</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11638,33 +11648,33 @@
         <v>0.077852775</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.07405932899999999</v>
+        <v>0.074353933</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.071004492</v>
+        <v>0.07121226</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.023463138</v>
+        <v>0.023501817</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07191923</v>
+        <v>0.071808345</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.071527412</v>
+        <v>0.07134046400000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.071122616</v>
+        <v>0.070902321</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.033912409</v>
+        <v>0.033699917</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.07174285900000001</v>
+        <v>0.071558952</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.069496167</v>
+        <v>0.069365833</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -12327,11 +12337,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>271500</v>
+        <v>244000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 263,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 252,000원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -12367,7 +12377,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -12602,7 +12612,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.1989269006109433</v>
+        <v>0.1989269737448312</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12641,7 +12651,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.04842985688977399</v>
+        <v>0.04842985667619831</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12690,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.7600275533939465</v>
+        <v>0.7600274826120655</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12719,7 +12729,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02816790642121412</v>
+        <v>0.02816784761777558</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12758,7 +12768,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.1311624324275712</v>
+        <v>0.1311621321579165</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13197,7 +13207,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23724,7 +23734,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38720,7 +38730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ129"/>
+  <dimension ref="A1:BQ136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -39590,67 +39600,67 @@
         <v>67.289</v>
       </c>
       <c r="Z5" s="27" t="n">
-        <v>67.289</v>
+        <v>85.10299999999999</v>
       </c>
       <c r="AA5" s="27" t="n">
-        <v>65.82599999999999</v>
+        <v>94.45699999999999</v>
       </c>
       <c r="AB5" s="27" t="n">
-        <v>24.091</v>
+        <v>53.04</v>
       </c>
       <c r="AC5" s="27" t="n">
-        <v>70.694</v>
+        <v>99.961</v>
       </c>
       <c r="AD5" s="27" t="n">
-        <v>140.261</v>
+        <v>169.529</v>
       </c>
       <c r="AE5" s="27" t="n">
-        <v>306.79</v>
+        <v>335.421</v>
       </c>
       <c r="AF5" s="27" t="n">
-        <v>459.926</v>
+        <v>488.875</v>
       </c>
       <c r="AG5" s="27" t="n">
-        <v>554.3200000000001</v>
+        <v>583.587</v>
       </c>
       <c r="AH5" s="27" t="n">
-        <v>556.754</v>
+        <v>630.653</v>
       </c>
       <c r="AI5" s="27" t="n">
-        <v>544.651</v>
+        <v>627.523</v>
       </c>
       <c r="AJ5" s="27" t="n">
-        <v>550.702</v>
+        <v>634.495</v>
       </c>
       <c r="AK5" s="27" t="n">
-        <v>552.756</v>
+        <v>637.47</v>
       </c>
       <c r="AL5" s="27" t="n">
-        <v>544.494</v>
+        <v>629.208</v>
       </c>
       <c r="AM5" s="27" t="n">
-        <v>538.576</v>
+        <v>622.369</v>
       </c>
       <c r="AN5" s="27" t="n">
-        <v>534.432</v>
+        <v>618.225</v>
       </c>
       <c r="AO5" s="27" t="n">
-        <v>506.379</v>
+        <v>591.093</v>
       </c>
       <c r="AP5" s="27" t="n">
-        <v>466.438</v>
+        <v>551.152</v>
       </c>
       <c r="AQ5" s="27" t="n">
-        <v>349.912</v>
+        <v>432.784</v>
       </c>
       <c r="AR5" s="27" t="n">
-        <v>244.248</v>
+        <v>328.041</v>
       </c>
       <c r="AS5" s="27" t="n">
-        <v>155.825</v>
+        <v>240.539</v>
       </c>
       <c r="AT5" s="27" t="n">
-        <v>86.68899999999999</v>
+        <v>171.402</v>
       </c>
       <c r="AU5" s="27" t="n">
         <v>24.339</v>
@@ -39674,22 +39684,22 @@
         <v>266.961</v>
       </c>
       <c r="BB5" s="27" t="n">
-        <v>267.692</v>
+        <v>285.506</v>
       </c>
       <c r="BC5" s="27" t="n">
-        <v>300.872</v>
+        <v>416.987</v>
       </c>
       <c r="BD5" s="27" t="n">
-        <v>1877.79</v>
+        <v>2038.536</v>
       </c>
       <c r="BE5" s="27" t="n">
-        <v>2192.603</v>
+        <v>2528.696</v>
       </c>
       <c r="BF5" s="27" t="n">
-        <v>2045.825</v>
+        <v>2382.839</v>
       </c>
       <c r="BG5" s="27" t="n">
-        <v>836.674</v>
+        <v>1172.766</v>
       </c>
       <c r="BH5" s="27" t="n">
         <v>40.836</v>
@@ -39770,67 +39780,67 @@
         <v>50.307</v>
       </c>
       <c r="Z6" s="27" t="n">
-        <v>50.307</v>
+        <v>68.122</v>
       </c>
       <c r="AA6" s="27" t="n">
-        <v>49.213</v>
+        <v>77.84399999999999</v>
       </c>
       <c r="AB6" s="27" t="n">
-        <v>7.294</v>
+        <v>36.243</v>
       </c>
       <c r="AC6" s="27" t="n">
-        <v>53.713</v>
+        <v>82.98</v>
       </c>
       <c r="AD6" s="27" t="n">
-        <v>124.101</v>
+        <v>153.368</v>
       </c>
       <c r="AE6" s="27" t="n">
-        <v>294.797</v>
+        <v>323.428</v>
       </c>
       <c r="AF6" s="27" t="n">
-        <v>447.8</v>
+        <v>476.749</v>
       </c>
       <c r="AG6" s="27" t="n">
-        <v>542.0599999999999</v>
+        <v>571.328</v>
       </c>
       <c r="AH6" s="27" t="n">
-        <v>544.494</v>
+        <v>618.394</v>
       </c>
       <c r="AI6" s="27" t="n">
-        <v>532.658</v>
+        <v>615.53</v>
       </c>
       <c r="AJ6" s="27" t="n">
-        <v>538.576</v>
+        <v>622.369</v>
       </c>
       <c r="AK6" s="27" t="n">
-        <v>544.494</v>
+        <v>629.208</v>
       </c>
       <c r="AL6" s="27" t="n">
-        <v>544.494</v>
+        <v>629.208</v>
       </c>
       <c r="AM6" s="27" t="n">
-        <v>538.576</v>
+        <v>622.369</v>
       </c>
       <c r="AN6" s="27" t="n">
-        <v>534.432</v>
+        <v>618.225</v>
       </c>
       <c r="AO6" s="27" t="n">
-        <v>506.379</v>
+        <v>591.093</v>
       </c>
       <c r="AP6" s="27" t="n">
-        <v>466.438</v>
+        <v>551.152</v>
       </c>
       <c r="AQ6" s="27" t="n">
-        <v>349.912</v>
+        <v>432.784</v>
       </c>
       <c r="AR6" s="27" t="n">
-        <v>244.248</v>
+        <v>328.041</v>
       </c>
       <c r="AS6" s="27" t="n">
-        <v>155.825</v>
+        <v>240.539</v>
       </c>
       <c r="AT6" s="27" t="n">
-        <v>86.68899999999999</v>
+        <v>171.402</v>
       </c>
       <c r="AU6" s="27" t="n">
         <v>24.339</v>
@@ -39854,22 +39864,22 @@
         <v>199.587</v>
       </c>
       <c r="BB6" s="27" t="n">
-        <v>200.134</v>
+        <v>217.949</v>
       </c>
       <c r="BC6" s="27" t="n">
-        <v>234.321</v>
+        <v>350.435</v>
       </c>
       <c r="BD6" s="27" t="n">
-        <v>1829.151</v>
+        <v>1989.899</v>
       </c>
       <c r="BE6" s="27" t="n">
-        <v>2160.222</v>
+        <v>2496.315</v>
       </c>
       <c r="BF6" s="27" t="n">
-        <v>2045.825</v>
+        <v>2382.839</v>
       </c>
       <c r="BG6" s="27" t="n">
-        <v>836.674</v>
+        <v>1172.766</v>
       </c>
       <c r="BH6" s="27" t="n">
         <v>40.836</v>
@@ -40094,154 +40104,175 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>type:LNGC</t>
+          <t>type:CONT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>선종 LNGC</t>
-        </is>
+          <t>선종 CONT</t>
+        </is>
+      </c>
+      <c r="Z9" s="27" t="n">
+        <v>17.815</v>
+      </c>
+      <c r="AA9" s="27" t="n">
+        <v>28.631</v>
       </c>
       <c r="AB9" s="27" t="n">
-        <v>2.919</v>
+        <v>28.949</v>
       </c>
       <c r="AC9" s="27" t="n">
-        <v>53.713</v>
+        <v>29.267</v>
       </c>
       <c r="AD9" s="27" t="n">
-        <v>60.682</v>
+        <v>71.59399999999999</v>
       </c>
       <c r="AE9" s="27" t="n">
-        <v>89.625</v>
+        <v>147.926</v>
       </c>
       <c r="AF9" s="27" t="n">
-        <v>154.335</v>
+        <v>149.57</v>
       </c>
       <c r="AG9" s="27" t="n">
-        <v>176.152</v>
+        <v>151.213</v>
       </c>
       <c r="AH9" s="27" t="n">
-        <v>176.152</v>
+        <v>195.845</v>
       </c>
       <c r="AI9" s="27" t="n">
-        <v>172.322</v>
+        <v>202.167</v>
       </c>
       <c r="AJ9" s="27" t="n">
-        <v>174.237</v>
+        <v>204.414</v>
       </c>
       <c r="AK9" s="27" t="n">
-        <v>176.152</v>
+        <v>206.66</v>
       </c>
       <c r="AL9" s="27" t="n">
-        <v>176.152</v>
+        <v>206.66</v>
       </c>
       <c r="AM9" s="27" t="n">
-        <v>174.237</v>
+        <v>204.414</v>
       </c>
       <c r="AN9" s="27" t="n">
-        <v>174.237</v>
+        <v>204.414</v>
       </c>
       <c r="AO9" s="27" t="n">
-        <v>150.746</v>
+        <v>206.66</v>
       </c>
       <c r="AP9" s="27" t="n">
-        <v>150.746</v>
+        <v>188.409</v>
       </c>
       <c r="AQ9" s="27" t="n">
-        <v>93.956</v>
+        <v>162.105</v>
       </c>
       <c r="AR9" s="27" t="n">
-        <v>75.51900000000001</v>
+        <v>110.204</v>
       </c>
       <c r="AS9" s="27" t="n">
-        <v>46.123</v>
+        <v>84.714</v>
+      </c>
+      <c r="AT9" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="BB9" s="27" t="n">
+        <v>17.815</v>
       </c>
       <c r="BC9" s="27" t="n">
-        <v>117.314</v>
+        <v>158.441</v>
       </c>
       <c r="BD9" s="27" t="n">
-        <v>596.264</v>
+        <v>644.554</v>
       </c>
       <c r="BE9" s="27" t="n">
-        <v>698.8630000000001</v>
+        <v>819.901</v>
       </c>
       <c r="BF9" s="27" t="n">
-        <v>649.966</v>
+        <v>803.897</v>
       </c>
       <c r="BG9" s="27" t="n">
-        <v>215.598</v>
+        <v>441.737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>type:CONT</t>
+          <t>type:LNGC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>선종 CONT</t>
-        </is>
+          <t>선종 LNGC</t>
+        </is>
+      </c>
+      <c r="AB10" s="27" t="n">
+        <v>2.919</v>
+      </c>
+      <c r="AC10" s="27" t="n">
+        <v>53.713</v>
       </c>
       <c r="AD10" s="27" t="n">
-        <v>42.327</v>
+        <v>60.682</v>
       </c>
       <c r="AE10" s="27" t="n">
-        <v>119.295</v>
+        <v>89.625</v>
       </c>
       <c r="AF10" s="27" t="n">
-        <v>120.621</v>
+        <v>154.335</v>
       </c>
       <c r="AG10" s="27" t="n">
-        <v>121.946</v>
+        <v>176.152</v>
       </c>
       <c r="AH10" s="27" t="n">
-        <v>121.946</v>
+        <v>176.152</v>
       </c>
       <c r="AI10" s="27" t="n">
-        <v>119.295</v>
+        <v>172.322</v>
       </c>
       <c r="AJ10" s="27" t="n">
-        <v>120.621</v>
+        <v>174.237</v>
       </c>
       <c r="AK10" s="27" t="n">
-        <v>121.946</v>
+        <v>176.152</v>
       </c>
       <c r="AL10" s="27" t="n">
-        <v>121.946</v>
+        <v>176.152</v>
       </c>
       <c r="AM10" s="27" t="n">
-        <v>120.621</v>
+        <v>174.237</v>
       </c>
       <c r="AN10" s="27" t="n">
-        <v>120.621</v>
+        <v>174.237</v>
       </c>
       <c r="AO10" s="27" t="n">
-        <v>121.946</v>
+        <v>150.746</v>
       </c>
       <c r="AP10" s="27" t="n">
-        <v>103.696</v>
+        <v>150.746</v>
       </c>
       <c r="AQ10" s="27" t="n">
-        <v>79.233</v>
+        <v>93.956</v>
       </c>
       <c r="AR10" s="27" t="n">
-        <v>26.411</v>
+        <v>75.51900000000001</v>
+      </c>
+      <c r="AS10" s="27" t="n">
+        <v>46.123</v>
       </c>
       <c r="BC10" s="27" t="n">
-        <v>42.327</v>
+        <v>117.314</v>
       </c>
       <c r="BD10" s="27" t="n">
-        <v>483.808</v>
+        <v>596.264</v>
       </c>
       <c r="BE10" s="27" t="n">
-        <v>483.808</v>
+        <v>698.8630000000001</v>
       </c>
       <c r="BF10" s="27" t="n">
-        <v>466.884</v>
+        <v>649.966</v>
       </c>
       <c r="BG10" s="27" t="n">
-        <v>105.644</v>
+        <v>215.598</v>
       </c>
     </row>
     <row r="11">
@@ -40627,62 +40658,68 @@
           <t>코호트 ⑤초호황</t>
         </is>
       </c>
+      <c r="Z15" s="27" t="n">
+        <v>17.815</v>
+      </c>
+      <c r="AA15" s="27" t="n">
+        <v>28.631</v>
+      </c>
       <c r="AB15" s="27" t="n">
-        <v>2.919</v>
+        <v>31.868</v>
       </c>
       <c r="AC15" s="27" t="n">
-        <v>53.713</v>
+        <v>82.98</v>
       </c>
       <c r="AD15" s="27" t="n">
-        <v>124.101</v>
+        <v>153.368</v>
       </c>
       <c r="AE15" s="27" t="n">
-        <v>294.797</v>
+        <v>323.428</v>
       </c>
       <c r="AF15" s="27" t="n">
-        <v>447.8</v>
+        <v>476.749</v>
       </c>
       <c r="AG15" s="27" t="n">
-        <v>542.0599999999999</v>
+        <v>571.328</v>
       </c>
       <c r="AH15" s="27" t="n">
-        <v>544.494</v>
+        <v>618.394</v>
       </c>
       <c r="AI15" s="27" t="n">
-        <v>532.658</v>
+        <v>615.53</v>
       </c>
       <c r="AJ15" s="27" t="n">
-        <v>538.576</v>
+        <v>622.369</v>
       </c>
       <c r="AK15" s="27" t="n">
-        <v>544.494</v>
+        <v>629.208</v>
       </c>
       <c r="AL15" s="27" t="n">
-        <v>544.494</v>
+        <v>629.208</v>
       </c>
       <c r="AM15" s="27" t="n">
-        <v>538.576</v>
+        <v>622.369</v>
       </c>
       <c r="AN15" s="27" t="n">
-        <v>534.432</v>
+        <v>618.225</v>
       </c>
       <c r="AO15" s="27" t="n">
-        <v>506.379</v>
+        <v>591.093</v>
       </c>
       <c r="AP15" s="27" t="n">
-        <v>466.438</v>
+        <v>551.152</v>
       </c>
       <c r="AQ15" s="27" t="n">
-        <v>349.912</v>
+        <v>432.784</v>
       </c>
       <c r="AR15" s="27" t="n">
-        <v>244.248</v>
+        <v>328.041</v>
       </c>
       <c r="AS15" s="27" t="n">
-        <v>155.825</v>
+        <v>240.539</v>
       </c>
       <c r="AT15" s="27" t="n">
-        <v>86.68899999999999</v>
+        <v>171.402</v>
       </c>
       <c r="AU15" s="27" t="n">
         <v>24.339</v>
@@ -40690,20 +40727,23 @@
       <c r="AV15" s="27" t="n">
         <v>16.497</v>
       </c>
+      <c r="BB15" s="27" t="n">
+        <v>17.815</v>
+      </c>
       <c r="BC15" s="27" t="n">
-        <v>180.733</v>
+        <v>296.847</v>
       </c>
       <c r="BD15" s="27" t="n">
-        <v>1829.151</v>
+        <v>1989.899</v>
       </c>
       <c r="BE15" s="27" t="n">
-        <v>2160.222</v>
+        <v>2496.315</v>
       </c>
       <c r="BF15" s="27" t="n">
-        <v>2045.825</v>
+        <v>2382.839</v>
       </c>
       <c r="BG15" s="27" t="n">
-        <v>836.674</v>
+        <v>1172.766</v>
       </c>
       <c r="BH15" s="27" t="n">
         <v>40.836</v>
@@ -40928,67 +40968,67 @@
         <v>1133.51</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1133.51</v>
+        <v>1188.52</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1133.51</v>
+        <v>1213.16</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1183.87</v>
+        <v>1299.82</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1314.89</v>
+        <v>1338.73</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1383</v>
+        <v>1385.29</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1424.78</v>
+        <v>1422.35</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1447.13</v>
+        <v>1444.12</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1452.57</v>
+        <v>1449.75</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1452.42</v>
+        <v>1439.58</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1452.42</v>
+        <v>1437.24</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1452.42</v>
+        <v>1437.24</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1454.54</v>
+        <v>1438.98</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1459.01</v>
+        <v>1442.65</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1459.01</v>
+        <v>1442.65</v>
       </c>
       <c r="AN17" s="13" t="n">
-        <v>1458.95</v>
+        <v>1442.49</v>
       </c>
       <c r="AO17" s="13" t="n">
-        <v>1458.47</v>
+        <v>1441.13</v>
       </c>
       <c r="AP17" s="13" t="n">
-        <v>1459.25</v>
+        <v>1440.53</v>
       </c>
       <c r="AQ17" s="13" t="n">
-        <v>1469.71</v>
+        <v>1444.39</v>
       </c>
       <c r="AR17" s="13" t="n">
-        <v>1478.79</v>
+        <v>1442.7</v>
       </c>
       <c r="AS17" s="13" t="n">
-        <v>1482.77</v>
+        <v>1431.6</v>
       </c>
       <c r="AT17" s="13" t="n">
-        <v>1477.93</v>
+        <v>1408.52</v>
       </c>
       <c r="AU17" s="13" t="n">
         <v>1418.75</v>
@@ -41096,49 +41136,49 @@
         <v>1418.75</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
     </row>
     <row r="19">
@@ -41216,73 +41256,73 @@
         <v>1200.32</v>
       </c>
       <c r="Z19" s="13" t="n">
-        <v>1212.35</v>
+        <v>1250.85</v>
       </c>
       <c r="AA19" s="13" t="n">
-        <v>1229.14</v>
+        <v>1284.9</v>
       </c>
       <c r="AB19" s="13" t="n">
-        <v>1248.27</v>
+        <v>1329.43</v>
       </c>
       <c r="AC19" s="13" t="n">
-        <v>1336.51</v>
+        <v>1353.2</v>
       </c>
       <c r="AD19" s="13" t="n">
-        <v>1402.85</v>
+        <v>1404.46</v>
       </c>
       <c r="AE19" s="13" t="n">
-        <v>1437.18</v>
+        <v>1435.48</v>
       </c>
       <c r="AF19" s="13" t="n">
-        <v>1463.51</v>
+        <v>1461.41</v>
       </c>
       <c r="AG19" s="13" t="n">
-        <v>1442.42</v>
+        <v>1440.45</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1419.33</v>
+        <v>1408.95</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1416.32</v>
+        <v>1403.4</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1416.32</v>
+        <v>1403.4</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1417.81</v>
+        <v>1404.62</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>1420.93</v>
+        <v>1407.19</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>1420.93</v>
+        <v>1407.19</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>1420.9</v>
+        <v>1407.08</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>1420.56</v>
+        <v>1406.13</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>1421.1</v>
+        <v>1405.71</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>1428.43</v>
+        <v>1408.41</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>1434.79</v>
+        <v>1407.22</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>1437.57</v>
+        <v>1399.46</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>1434.18</v>
+        <v>1383.3</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>1392.75</v>
+        <v>1390.46</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>1392.75</v>
+        <v>1390.46</v>
       </c>
     </row>
     <row r="20">
@@ -41360,73 +41400,73 @@
         <v>80767.89999999999</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>81577</v>
+        <v>106451.9</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>80909.10000000001</v>
+        <v>121367.5</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>30071.6</v>
+        <v>70512.7</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>94483.5</v>
+        <v>135267.4</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>196766.5</v>
+        <v>238096.8</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>440913.4</v>
+        <v>481490.7</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>673108</v>
+        <v>714445.6</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>799564</v>
+        <v>840627.1</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>790216.3</v>
+        <v>888559.1</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>771402.1</v>
+        <v>880668.8</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>779973.2</v>
+        <v>890454</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>783700.8</v>
+        <v>895404.9</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>773690.9</v>
+        <v>885413.9</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>765281.3</v>
+        <v>875789.9</v>
       </c>
       <c r="AN20" s="18" t="n">
-        <v>759371.9</v>
+        <v>869890</v>
       </c>
       <c r="AO20" s="18" t="n">
-        <v>719342.2</v>
+        <v>831152.7</v>
       </c>
       <c r="AP20" s="18" t="n">
-        <v>662857.2</v>
+        <v>774759.4</v>
       </c>
       <c r="AQ20" s="18" t="n">
-        <v>499823.9</v>
+        <v>609537.5</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>350443.4</v>
+        <v>461627.5</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>224008.9</v>
+        <v>336623.9</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>124326.9</v>
+        <v>237100.5</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>33899</v>
+        <v>33843.1</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>22976</v>
+        <v>22938.1</v>
       </c>
       <c r="AW20" s="18" t="n">
         <v>7328.6</v>
@@ -41444,25 +41484,25 @@
         <v>316512.7</v>
       </c>
       <c r="BB20" s="18" t="n">
-        <v>321904.9</v>
+        <v>346779.8</v>
       </c>
       <c r="BC20" s="18" t="n">
-        <v>402230.7</v>
+        <v>565244.4</v>
       </c>
       <c r="BD20" s="18" t="n">
-        <v>2703801.7</v>
+        <v>2925122.5</v>
       </c>
       <c r="BE20" s="18" t="n">
-        <v>3108767</v>
+        <v>3551941.6</v>
       </c>
       <c r="BF20" s="18" t="n">
-        <v>2906852.6</v>
+        <v>3351592</v>
       </c>
       <c r="BG20" s="18" t="n">
-        <v>1198603.1</v>
+        <v>1644889.4</v>
       </c>
       <c r="BH20" s="18" t="n">
-        <v>56875</v>
+        <v>56781.2</v>
       </c>
     </row>
     <row r="21">
@@ -41540,73 +41580,73 @@
         <v>59958.2</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>60563.1</v>
+        <v>85438</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>60073</v>
+        <v>100531.4</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>9274.9</v>
+        <v>49715.9</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>73517.2</v>
+        <v>114301.1</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>176526.4</v>
+        <v>217856.8</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>425900.7</v>
+        <v>466478</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>657798.9</v>
+        <v>699136.5</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>784391.9</v>
+        <v>825455</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>775326.1</v>
+        <v>873685.9</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>756871.6</v>
+        <v>866165.8</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>765281.3</v>
+        <v>875789.9</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>773690.9</v>
+        <v>885413.9</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>773690.9</v>
+        <v>885413.9</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>765281.3</v>
+        <v>875789.9</v>
       </c>
       <c r="AN21" s="18" t="n">
-        <v>759371.9</v>
+        <v>869890</v>
       </c>
       <c r="AO21" s="18" t="n">
-        <v>719342.2</v>
+        <v>831152.7</v>
       </c>
       <c r="AP21" s="18" t="n">
-        <v>662857.2</v>
+        <v>774759.4</v>
       </c>
       <c r="AQ21" s="18" t="n">
-        <v>499823.9</v>
+        <v>609537.5</v>
       </c>
       <c r="AR21" s="18" t="n">
-        <v>350443.4</v>
+        <v>461627.5</v>
       </c>
       <c r="AS21" s="18" t="n">
-        <v>224008.9</v>
+        <v>336623.9</v>
       </c>
       <c r="AT21" s="18" t="n">
-        <v>124326.9</v>
+        <v>237100.5</v>
       </c>
       <c r="AU21" s="18" t="n">
-        <v>33899</v>
+        <v>33843.1</v>
       </c>
       <c r="AV21" s="18" t="n">
-        <v>22976</v>
+        <v>22938.1</v>
       </c>
       <c r="AW21" s="18" t="n">
         <v>0</v>
@@ -41624,25 +41664,25 @@
         <v>234942.9</v>
       </c>
       <c r="BB21" s="18" t="n">
-        <v>238969.7</v>
+        <v>263844.6</v>
       </c>
       <c r="BC21" s="18" t="n">
-        <v>319391.5</v>
+        <v>482405.2</v>
       </c>
       <c r="BD21" s="18" t="n">
-        <v>2643417.6</v>
+        <v>2864755.4</v>
       </c>
       <c r="BE21" s="18" t="n">
-        <v>3069534.7</v>
+        <v>3512783.5</v>
       </c>
       <c r="BF21" s="18" t="n">
-        <v>2906852.6</v>
+        <v>3351592</v>
       </c>
       <c r="BG21" s="18" t="n">
-        <v>1198603.1</v>
+        <v>1644889.4</v>
       </c>
       <c r="BH21" s="18" t="n">
-        <v>56875</v>
+        <v>56781.2</v>
       </c>
     </row>
     <row r="22">
@@ -41720,67 +41760,67 @@
         <v>59958.2</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>60563.1</v>
+        <v>85438</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>60073</v>
+        <v>100531.4</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>9274.9</v>
+        <v>49715.9</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>73517.2</v>
+        <v>114301.1</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>176526.4</v>
+        <v>217856.8</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>425900.7</v>
+        <v>466478</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>657798.9</v>
+        <v>699136.5</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>752546.1</v>
+        <v>793609.1</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>740599.1</v>
+        <v>749089.1</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>722972.6</v>
+        <v>721806</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>731005.7</v>
+        <v>729826.1</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>739038.7</v>
+        <v>737846.2</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>739038.7</v>
+        <v>737846.2</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>731005.7</v>
+        <v>729826.1</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>725096.3</v>
+        <v>723926.2</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>684690</v>
+        <v>683584.9</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>628205</v>
+        <v>627191.6</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>465925</v>
+        <v>465177.8</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>316167.8</v>
+        <v>315663.8</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>189356.6</v>
+        <v>189056.1</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>89674.60000000001</v>
+        <v>89532.8</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>0</v>
@@ -41888,49 +41928,49 @@
         <v>31845.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>34727</v>
+        <v>124596.7</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>33899</v>
+        <v>144359.8</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>34275.6</v>
+        <v>145963.8</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>34652.3</v>
+        <v>147567.8</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>34652.3</v>
+        <v>147567.8</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>34275.6</v>
+        <v>145963.8</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>34275.6</v>
+        <v>145963.8</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>34652.3</v>
+        <v>147567.8</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>34652.3</v>
+        <v>147567.8</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>33899</v>
+        <v>144359.8</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>34275.6</v>
+        <v>145963.8</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>34652.3</v>
+        <v>147567.8</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>34652.3</v>
+        <v>147567.8</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>33899</v>
+        <v>33843.1</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>22976</v>
+        <v>22938.1</v>
       </c>
     </row>
     <row r="24">
@@ -41987,13 +42027,13 @@
         <v>0.054</v>
       </c>
       <c r="Z24" s="21" t="n">
-        <v>0.054</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="AA24" s="21" t="n">
-        <v>0.054</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="AB24" s="21" t="n">
-        <v>0.0756</v>
+        <v>0.1015</v>
       </c>
       <c r="AC24" s="21" t="n">
         <v>0.108</v>
@@ -42224,63 +42264,63 @@
         <v/>
       </c>
       <c r="AH29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1342.11)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1337.49)</f>
         <v/>
       </c>
       <c r="AI29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AJ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AK29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AL29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AM29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AN29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AO29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AP29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AQ29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AR29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AS29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AT29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AU29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AV29" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
     </row>
@@ -44371,389 +44411,362 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20261020800226</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>컨테이너선 6척</t>
+        </is>
+      </c>
+      <c r="AH53" s="27" t="n">
+        <v>67.21899999999999</v>
+      </c>
+      <c r="AI53" s="27" t="n">
+        <v>82.872</v>
+      </c>
+      <c r="AJ53" s="27" t="n">
+        <v>83.79300000000001</v>
+      </c>
+      <c r="AK53" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="AL53" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="AM53" s="27" t="n">
+        <v>83.79300000000001</v>
+      </c>
+      <c r="AN53" s="27" t="n">
+        <v>83.79300000000001</v>
+      </c>
+      <c r="AO53" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="AP53" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="AQ53" s="27" t="n">
+        <v>82.872</v>
+      </c>
+      <c r="AR53" s="27" t="n">
+        <v>83.79300000000001</v>
+      </c>
+      <c r="AS53" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="AT53" s="27" t="n">
+        <v>84.714</v>
+      </c>
+      <c r="BJ53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK53" s="16" t="n">
+        <v>1337.49</v>
+      </c>
+      <c r="BL53" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM53" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="BN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="BP53" s="27" t="n">
+        <v>1076.419</v>
+      </c>
+      <c r="BQ53" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20261021800379</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>컨테이너선 2척</t>
+        </is>
+      </c>
+      <c r="Z54" s="27" t="n">
+        <v>17.815</v>
+      </c>
+      <c r="AA54" s="27" t="n">
+        <v>28.631</v>
+      </c>
+      <c r="AB54" s="27" t="n">
+        <v>28.949</v>
+      </c>
+      <c r="AC54" s="27" t="n">
+        <v>29.267</v>
+      </c>
+      <c r="AD54" s="27" t="n">
+        <v>29.267</v>
+      </c>
+      <c r="AE54" s="27" t="n">
+        <v>28.631</v>
+      </c>
+      <c r="AF54" s="27" t="n">
+        <v>28.949</v>
+      </c>
+      <c r="AG54" s="27" t="n">
+        <v>29.267</v>
+      </c>
+      <c r="AH54" s="27" t="n">
+        <v>6.682</v>
+      </c>
+      <c r="BJ54" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK54" s="16" t="n">
+        <v>1396.3</v>
+      </c>
+      <c r="BL54" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM54" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="BN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO54" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="BP54" s="27" t="n">
+        <v>227.458</v>
+      </c>
+      <c r="BQ54" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>② 계약별 원화(백만원, 수식)</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>ships</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20251121800424</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>VLCC</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>4</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>VLCC 4척</t>
-        </is>
-      </c>
-      <c r="AD55" s="18">
-        <f>IFERROR(AD33*$BJ33*(1+($BL33-1)*AD$30)*($D$27*$BK33+(1-$D$27)*AD$29),"")</f>
-        <v/>
-      </c>
-      <c r="AE55" s="18">
-        <f>IFERROR(AE33*$BJ33*(1+($BL33-1)*AE$30)*($D$27*$BK33+(1-$D$27)*AE$29),"")</f>
-        <v/>
-      </c>
-      <c r="AF55" s="18">
-        <f>IFERROR(AF33*$BJ33*(1+($BL33-1)*AF$30)*($D$27*$BK33+(1-$D$27)*AF$29),"")</f>
-        <v/>
-      </c>
-      <c r="AG55" s="18">
-        <f>IFERROR(AG33*$BJ33*(1+($BL33-1)*AG$30)*($D$27*$BK33+(1-$D$27)*AG$29),"")</f>
-        <v/>
-      </c>
-      <c r="AH55" s="18">
-        <f>IFERROR(AH33*$BJ33*(1+($BL33-1)*AH$30)*($D$27*$BK33+(1-$D$27)*AH$29),"")</f>
-        <v/>
-      </c>
-      <c r="AI55" s="18">
-        <f>IFERROR(AI33*$BJ33*(1+($BL33-1)*AI$30)*($D$27*$BK33+(1-$D$27)*AI$29),"")</f>
-        <v/>
-      </c>
-      <c r="AJ55" s="18">
-        <f>IFERROR(AJ33*$BJ33*(1+($BL33-1)*AJ$30)*($D$27*$BK33+(1-$D$27)*AJ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AK55" s="18">
-        <f>IFERROR(AK33*$BJ33*(1+($BL33-1)*AK$30)*($D$27*$BK33+(1-$D$27)*AK$29),"")</f>
-        <v/>
-      </c>
-      <c r="AL55" s="18">
-        <f>IFERROR(AL33*$BJ33*(1+($BL33-1)*AL$30)*($D$27*$BK33+(1-$D$27)*AL$29),"")</f>
-        <v/>
-      </c>
-      <c r="AM55" s="18">
-        <f>IFERROR(AM33*$BJ33*(1+($BL33-1)*AM$30)*($D$27*$BK33+(1-$D$27)*AM$29),"")</f>
-        <v/>
-      </c>
-      <c r="AN55" s="18">
-        <f>IFERROR(AN33*$BJ33*(1+($BL33-1)*AN$30)*($D$27*$BK33+(1-$D$27)*AN$29),"")</f>
-        <v/>
-      </c>
-      <c r="AO55" s="18">
-        <f>IFERROR(AO33*$BJ33*(1+($BL33-1)*AO$30)*($D$27*$BK33+(1-$D$27)*AO$29),"")</f>
-        <v/>
-      </c>
-      <c r="AP55" s="18">
-        <f>IFERROR(AP33*$BJ33*(1+($BL33-1)*AP$30)*($D$27*$BK33+(1-$D$27)*AP$29),"")</f>
-        <v/>
-      </c>
-      <c r="AQ55" s="18">
-        <f>IFERROR(AQ33*$BJ33*(1+($BL33-1)*AQ$30)*($D$27*$BK33+(1-$D$27)*AQ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AR55" s="18">
-        <f>IFERROR(AR33*$BJ33*(1+($BL33-1)*AR$30)*($D$27*$BK33+(1-$D$27)*AR$29),"")</f>
-        <v/>
-      </c>
-      <c r="AS55" s="18">
-        <f>IFERROR(AS33*$BJ33*(1+($BL33-1)*AS$30)*($D$27*$BK33+(1-$D$27)*AS$29),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20251124800131</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>6</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>컨테이너선 6척</t>
-        </is>
-      </c>
-      <c r="AD56" s="18">
-        <f>IFERROR(AD34*$BJ34*(1+($BL34-1)*AD$30)*($D$27*$BK34+(1-$D$27)*AD$29),"")</f>
-        <v/>
-      </c>
-      <c r="AE56" s="18">
-        <f>IFERROR(AE34*$BJ34*(1+($BL34-1)*AE$30)*($D$27*$BK34+(1-$D$27)*AE$29),"")</f>
-        <v/>
-      </c>
-      <c r="AF56" s="18">
-        <f>IFERROR(AF34*$BJ34*(1+($BL34-1)*AF$30)*($D$27*$BK34+(1-$D$27)*AF$29),"")</f>
-        <v/>
-      </c>
-      <c r="AG56" s="18">
-        <f>IFERROR(AG34*$BJ34*(1+($BL34-1)*AG$30)*($D$27*$BK34+(1-$D$27)*AG$29),"")</f>
-        <v/>
-      </c>
-      <c r="AH56" s="18">
-        <f>IFERROR(AH34*$BJ34*(1+($BL34-1)*AH$30)*($D$27*$BK34+(1-$D$27)*AH$29),"")</f>
-        <v/>
-      </c>
-      <c r="AI56" s="18">
-        <f>IFERROR(AI34*$BJ34*(1+($BL34-1)*AI$30)*($D$27*$BK34+(1-$D$27)*AI$29),"")</f>
-        <v/>
-      </c>
-      <c r="AJ56" s="18">
-        <f>IFERROR(AJ34*$BJ34*(1+($BL34-1)*AJ$30)*($D$27*$BK34+(1-$D$27)*AJ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AK56" s="18">
-        <f>IFERROR(AK34*$BJ34*(1+($BL34-1)*AK$30)*($D$27*$BK34+(1-$D$27)*AK$29),"")</f>
-        <v/>
-      </c>
-      <c r="AL56" s="18">
-        <f>IFERROR(AL34*$BJ34*(1+($BL34-1)*AL$30)*($D$27*$BK34+(1-$D$27)*AL$29),"")</f>
-        <v/>
-      </c>
-      <c r="AM56" s="18">
-        <f>IFERROR(AM34*$BJ34*(1+($BL34-1)*AM$30)*($D$27*$BK34+(1-$D$27)*AM$29),"")</f>
-        <v/>
-      </c>
-      <c r="AN56" s="18">
-        <f>IFERROR(AN34*$BJ34*(1+($BL34-1)*AN$30)*($D$27*$BK34+(1-$D$27)*AN$29),"")</f>
-        <v/>
-      </c>
-      <c r="AO56" s="18">
-        <f>IFERROR(AO34*$BJ34*(1+($BL34-1)*AO$30)*($D$27*$BK34+(1-$D$27)*AO$29),"")</f>
-        <v/>
-      </c>
-      <c r="AP56" s="18">
-        <f>IFERROR(AP34*$BJ34*(1+($BL34-1)*AP$30)*($D$27*$BK34+(1-$D$27)*AP$29),"")</f>
-        <v/>
-      </c>
-      <c r="AQ56" s="18">
-        <f>IFERROR(AQ34*$BJ34*(1+($BL34-1)*AQ$30)*($D$27*$BK34+(1-$D$27)*AQ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AR56" s="18">
-        <f>IFERROR(AR34*$BJ34*(1+($BL34-1)*AR$30)*($D$27*$BK34+(1-$D$27)*AR$29),"")</f>
-        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20251202800104</t>
+          <t>20251121800424</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LNGC 1척</t>
+          <t>VLCC 4척</t>
         </is>
       </c>
       <c r="AD57" s="18">
-        <f>IFERROR(AD35*$BJ35*(1+($BL35-1)*AD$30)*($D$27*$BK35+(1-$D$27)*AD$29),"")</f>
+        <f>IFERROR(AD33*$BJ33*(1+($BL33-1)*AD$30)*($D$27*$BK33+(1-$D$27)*AD$29),"")</f>
         <v/>
       </c>
       <c r="AE57" s="18">
-        <f>IFERROR(AE35*$BJ35*(1+($BL35-1)*AE$30)*($D$27*$BK35+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE33*$BJ33*(1+($BL33-1)*AE$30)*($D$27*$BK33+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF57" s="18">
-        <f>IFERROR(AF35*$BJ35*(1+($BL35-1)*AF$30)*($D$27*$BK35+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF33*$BJ33*(1+($BL33-1)*AF$30)*($D$27*$BK33+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG57" s="18">
-        <f>IFERROR(AG35*$BJ35*(1+($BL35-1)*AG$30)*($D$27*$BK35+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG33*$BJ33*(1+($BL33-1)*AG$30)*($D$27*$BK33+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH57" s="18">
-        <f>IFERROR(AH35*$BJ35*(1+($BL35-1)*AH$30)*($D$27*$BK35+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH33*$BJ33*(1+($BL33-1)*AH$30)*($D$27*$BK33+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI57" s="18">
-        <f>IFERROR(AI35*$BJ35*(1+($BL35-1)*AI$30)*($D$27*$BK35+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI33*$BJ33*(1+($BL33-1)*AI$30)*($D$27*$BK33+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ57" s="18">
-        <f>IFERROR(AJ35*$BJ35*(1+($BL35-1)*AJ$30)*($D$27*$BK35+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ33*$BJ33*(1+($BL33-1)*AJ$30)*($D$27*$BK33+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK57" s="18">
-        <f>IFERROR(AK35*$BJ35*(1+($BL35-1)*AK$30)*($D$27*$BK35+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK33*$BJ33*(1+($BL33-1)*AK$30)*($D$27*$BK33+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL57" s="18">
-        <f>IFERROR(AL35*$BJ35*(1+($BL35-1)*AL$30)*($D$27*$BK35+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL33*$BJ33*(1+($BL33-1)*AL$30)*($D$27*$BK33+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM57" s="18">
-        <f>IFERROR(AM35*$BJ35*(1+($BL35-1)*AM$30)*($D$27*$BK35+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM33*$BJ33*(1+($BL33-1)*AM$30)*($D$27*$BK33+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN57" s="18">
-        <f>IFERROR(AN35*$BJ35*(1+($BL35-1)*AN$30)*($D$27*$BK35+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN33*$BJ33*(1+($BL33-1)*AN$30)*($D$27*$BK33+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO57" s="18">
-        <f>IFERROR(AO35*$BJ35*(1+($BL35-1)*AO$30)*($D$27*$BK35+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO33*$BJ33*(1+($BL33-1)*AO$30)*($D$27*$BK33+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP57" s="18">
-        <f>IFERROR(AP35*$BJ35*(1+($BL35-1)*AP$30)*($D$27*$BK35+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP33*$BJ33*(1+($BL33-1)*AP$30)*($D$27*$BK33+(1-$D$27)*AP$29),"")</f>
+        <v/>
+      </c>
+      <c r="AQ57" s="18">
+        <f>IFERROR(AQ33*$BJ33*(1+($BL33-1)*AQ$30)*($D$27*$BK33+(1-$D$27)*AQ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AR57" s="18">
+        <f>IFERROR(AR33*$BJ33*(1+($BL33-1)*AR$30)*($D$27*$BK33+(1-$D$27)*AR$29),"")</f>
+        <v/>
+      </c>
+      <c r="AS57" s="18">
+        <f>IFERROR(AS33*$BJ33*(1+($BL33-1)*AS$30)*($D$27*$BK33+(1-$D$27)*AS$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20251215800970</t>
+          <t>20251124800131</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>태안화력 5~8호기 저탄장 옥내화 공사</t>
-        </is>
-      </c>
-      <c r="E58" s="18">
-        <f>IFERROR(E36*$BJ36*(1+($BL36-1)*E$30)*($D$27*$BK36+(1-$D$27)*E$29),"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="18">
-        <f>IFERROR(F36*$BJ36*(1+($BL36-1)*F$30)*($D$27*$BK36+(1-$D$27)*F$29),"")</f>
-        <v/>
-      </c>
-      <c r="G58" s="18">
-        <f>IFERROR(G36*$BJ36*(1+($BL36-1)*G$30)*($D$27*$BK36+(1-$D$27)*G$29),"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="18">
-        <f>IFERROR(H36*$BJ36*(1+($BL36-1)*H$30)*($D$27*$BK36+(1-$D$27)*H$29),"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="18">
-        <f>IFERROR(I36*$BJ36*(1+($BL36-1)*I$30)*($D$27*$BK36+(1-$D$27)*I$29),"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="18">
-        <f>IFERROR(J36*$BJ36*(1+($BL36-1)*J$30)*($D$27*$BK36+(1-$D$27)*J$29),"")</f>
-        <v/>
-      </c>
-      <c r="K58" s="18">
-        <f>IFERROR(K36*$BJ36*(1+($BL36-1)*K$30)*($D$27*$BK36+(1-$D$27)*K$29),"")</f>
-        <v/>
-      </c>
-      <c r="L58" s="18">
-        <f>IFERROR(L36*$BJ36*(1+($BL36-1)*L$30)*($D$27*$BK36+(1-$D$27)*L$29),"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="18">
-        <f>IFERROR(M36*$BJ36*(1+($BL36-1)*M$30)*($D$27*$BK36+(1-$D$27)*M$29),"")</f>
-        <v/>
-      </c>
-      <c r="N58" s="18">
-        <f>IFERROR(N36*$BJ36*(1+($BL36-1)*N$30)*($D$27*$BK36+(1-$D$27)*N$29),"")</f>
-        <v/>
-      </c>
-      <c r="O58" s="18">
-        <f>IFERROR(O36*$BJ36*(1+($BL36-1)*O$30)*($D$27*$BK36+(1-$D$27)*O$29),"")</f>
-        <v/>
-      </c>
-      <c r="P58" s="18">
-        <f>IFERROR(P36*$BJ36*(1+($BL36-1)*P$30)*($D$27*$BK36+(1-$D$27)*P$29),"")</f>
-        <v/>
-      </c>
-      <c r="Q58" s="18">
-        <f>IFERROR(Q36*$BJ36*(1+($BL36-1)*Q$30)*($D$27*$BK36+(1-$D$27)*Q$29),"")</f>
-        <v/>
-      </c>
-      <c r="R58" s="18">
-        <f>IFERROR(R36*$BJ36*(1+($BL36-1)*R$30)*($D$27*$BK36+(1-$D$27)*R$29),"")</f>
-        <v/>
-      </c>
-      <c r="S58" s="18">
-        <f>IFERROR(S36*$BJ36*(1+($BL36-1)*S$30)*($D$27*$BK36+(1-$D$27)*S$29),"")</f>
-        <v/>
-      </c>
-      <c r="T58" s="18">
-        <f>IFERROR(T36*$BJ36*(1+($BL36-1)*T$30)*($D$27*$BK36+(1-$D$27)*T$29),"")</f>
-        <v/>
-      </c>
-      <c r="U58" s="18">
-        <f>IFERROR(U36*$BJ36*(1+($BL36-1)*U$30)*($D$27*$BK36+(1-$D$27)*U$29),"")</f>
-        <v/>
-      </c>
-      <c r="V58" s="18">
-        <f>IFERROR(V36*$BJ36*(1+($BL36-1)*V$30)*($D$27*$BK36+(1-$D$27)*V$29),"")</f>
-        <v/>
-      </c>
-      <c r="W58" s="18">
-        <f>IFERROR(W36*$BJ36*(1+($BL36-1)*W$30)*($D$27*$BK36+(1-$D$27)*W$29),"")</f>
-        <v/>
-      </c>
-      <c r="X58" s="18">
-        <f>IFERROR(X36*$BJ36*(1+($BL36-1)*X$30)*($D$27*$BK36+(1-$D$27)*X$29),"")</f>
-        <v/>
-      </c>
-      <c r="Y58" s="18">
-        <f>IFERROR(Y36*$BJ36*(1+($BL36-1)*Y$30)*($D$27*$BK36+(1-$D$27)*Y$29),"")</f>
-        <v/>
-      </c>
-      <c r="Z58" s="18">
-        <f>IFERROR(Z36*$BJ36*(1+($BL36-1)*Z$30)*($D$27*$BK36+(1-$D$27)*Z$29),"")</f>
-        <v/>
-      </c>
-      <c r="AA58" s="18">
-        <f>IFERROR(AA36*$BJ36*(1+($BL36-1)*AA$30)*($D$27*$BK36+(1-$D$27)*AA$29),"")</f>
-        <v/>
-      </c>
-      <c r="AB58" s="18">
-        <f>IFERROR(AB36*$BJ36*(1+($BL36-1)*AB$30)*($D$27*$BK36+(1-$D$27)*AB$29),"")</f>
-        <v/>
-      </c>
-      <c r="AC58" s="18">
-        <f>IFERROR(AC36*$BJ36*(1+($BL36-1)*AC$30)*($D$27*$BK36+(1-$D$27)*AC$29),"")</f>
-        <v/>
+          <t>컨테이너선 6척</t>
+        </is>
       </c>
       <c r="AD58" s="18">
-        <f>IFERROR(AD36*$BJ36*(1+($BL36-1)*AD$30)*($D$27*$BK36+(1-$D$27)*AD$29),"")</f>
+        <f>IFERROR(AD34*$BJ34*(1+($BL34-1)*AD$30)*($D$27*$BK34+(1-$D$27)*AD$29),"")</f>
+        <v/>
+      </c>
+      <c r="AE58" s="18">
+        <f>IFERROR(AE34*$BJ34*(1+($BL34-1)*AE$30)*($D$27*$BK34+(1-$D$27)*AE$29),"")</f>
+        <v/>
+      </c>
+      <c r="AF58" s="18">
+        <f>IFERROR(AF34*$BJ34*(1+($BL34-1)*AF$30)*($D$27*$BK34+(1-$D$27)*AF$29),"")</f>
+        <v/>
+      </c>
+      <c r="AG58" s="18">
+        <f>IFERROR(AG34*$BJ34*(1+($BL34-1)*AG$30)*($D$27*$BK34+(1-$D$27)*AG$29),"")</f>
+        <v/>
+      </c>
+      <c r="AH58" s="18">
+        <f>IFERROR(AH34*$BJ34*(1+($BL34-1)*AH$30)*($D$27*$BK34+(1-$D$27)*AH$29),"")</f>
+        <v/>
+      </c>
+      <c r="AI58" s="18">
+        <f>IFERROR(AI34*$BJ34*(1+($BL34-1)*AI$30)*($D$27*$BK34+(1-$D$27)*AI$29),"")</f>
+        <v/>
+      </c>
+      <c r="AJ58" s="18">
+        <f>IFERROR(AJ34*$BJ34*(1+($BL34-1)*AJ$30)*($D$27*$BK34+(1-$D$27)*AJ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AK58" s="18">
+        <f>IFERROR(AK34*$BJ34*(1+($BL34-1)*AK$30)*($D$27*$BK34+(1-$D$27)*AK$29),"")</f>
+        <v/>
+      </c>
+      <c r="AL58" s="18">
+        <f>IFERROR(AL34*$BJ34*(1+($BL34-1)*AL$30)*($D$27*$BK34+(1-$D$27)*AL$29),"")</f>
+        <v/>
+      </c>
+      <c r="AM58" s="18">
+        <f>IFERROR(AM34*$BJ34*(1+($BL34-1)*AM$30)*($D$27*$BK34+(1-$D$27)*AM$29),"")</f>
+        <v/>
+      </c>
+      <c r="AN58" s="18">
+        <f>IFERROR(AN34*$BJ34*(1+($BL34-1)*AN$30)*($D$27*$BK34+(1-$D$27)*AN$29),"")</f>
+        <v/>
+      </c>
+      <c r="AO58" s="18">
+        <f>IFERROR(AO34*$BJ34*(1+($BL34-1)*AO$30)*($D$27*$BK34+(1-$D$27)*AO$29),"")</f>
+        <v/>
+      </c>
+      <c r="AP58" s="18">
+        <f>IFERROR(AP34*$BJ34*(1+($BL34-1)*AP$30)*($D$27*$BK34+(1-$D$27)*AP$29),"")</f>
+        <v/>
+      </c>
+      <c r="AQ58" s="18">
+        <f>IFERROR(AQ34*$BJ34*(1+($BL34-1)*AQ$30)*($D$27*$BK34+(1-$D$27)*AQ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AR58" s="18">
+        <f>IFERROR(AR34*$BJ34*(1+($BL34-1)*AR$30)*($D$27*$BK34+(1-$D$27)*AR$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20251219800421</t>
+          <t>20251202800104</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -44762,495 +44775,544 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LNGC 3척</t>
-        </is>
-      </c>
-      <c r="AB59" s="18">
-        <f>IFERROR(AB37*$BJ37*(1+($BL37-1)*AB$30)*($D$27*$BK37+(1-$D$27)*AB$29),"")</f>
-        <v/>
-      </c>
-      <c r="AC59" s="18">
-        <f>IFERROR(AC37*$BJ37*(1+($BL37-1)*AC$30)*($D$27*$BK37+(1-$D$27)*AC$29),"")</f>
-        <v/>
+          <t>LNGC 1척</t>
+        </is>
       </c>
       <c r="AD59" s="18">
-        <f>IFERROR(AD37*$BJ37*(1+($BL37-1)*AD$30)*($D$27*$BK37+(1-$D$27)*AD$29),"")</f>
+        <f>IFERROR(AD35*$BJ35*(1+($BL35-1)*AD$30)*($D$27*$BK35+(1-$D$27)*AD$29),"")</f>
         <v/>
       </c>
       <c r="AE59" s="18">
-        <f>IFERROR(AE37*$BJ37*(1+($BL37-1)*AE$30)*($D$27*$BK37+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE35*$BJ35*(1+($BL35-1)*AE$30)*($D$27*$BK35+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF59" s="18">
-        <f>IFERROR(AF37*$BJ37*(1+($BL37-1)*AF$30)*($D$27*$BK37+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF35*$BJ35*(1+($BL35-1)*AF$30)*($D$27*$BK35+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG59" s="18">
-        <f>IFERROR(AG37*$BJ37*(1+($BL37-1)*AG$30)*($D$27*$BK37+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG35*$BJ35*(1+($BL35-1)*AG$30)*($D$27*$BK35+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH59" s="18">
-        <f>IFERROR(AH37*$BJ37*(1+($BL37-1)*AH$30)*($D$27*$BK37+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH35*$BJ35*(1+($BL35-1)*AH$30)*($D$27*$BK35+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI59" s="18">
-        <f>IFERROR(AI37*$BJ37*(1+($BL37-1)*AI$30)*($D$27*$BK37+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI35*$BJ35*(1+($BL35-1)*AI$30)*($D$27*$BK35+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ59" s="18">
-        <f>IFERROR(AJ37*$BJ37*(1+($BL37-1)*AJ$30)*($D$27*$BK37+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ35*$BJ35*(1+($BL35-1)*AJ$30)*($D$27*$BK35+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK59" s="18">
-        <f>IFERROR(AK37*$BJ37*(1+($BL37-1)*AK$30)*($D$27*$BK37+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK35*$BJ35*(1+($BL35-1)*AK$30)*($D$27*$BK35+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL59" s="18">
-        <f>IFERROR(AL37*$BJ37*(1+($BL37-1)*AL$30)*($D$27*$BK37+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL35*$BJ35*(1+($BL35-1)*AL$30)*($D$27*$BK35+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM59" s="18">
-        <f>IFERROR(AM37*$BJ37*(1+($BL37-1)*AM$30)*($D$27*$BK37+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM35*$BJ35*(1+($BL35-1)*AM$30)*($D$27*$BK35+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN59" s="18">
-        <f>IFERROR(AN37*$BJ37*(1+($BL37-1)*AN$30)*($D$27*$BK37+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN35*$BJ35*(1+($BL35-1)*AN$30)*($D$27*$BK35+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO59" s="18">
-        <f>IFERROR(AO37*$BJ37*(1+($BL37-1)*AO$30)*($D$27*$BK37+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO35*$BJ35*(1+($BL35-1)*AO$30)*($D$27*$BK35+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP59" s="18">
-        <f>IFERROR(AP37*$BJ37*(1+($BL37-1)*AP$30)*($D$27*$BK37+(1-$D$27)*AP$29),"")</f>
-        <v/>
-      </c>
-      <c r="AQ59" s="18">
-        <f>IFERROR(AQ37*$BJ37*(1+($BL37-1)*AQ$30)*($D$27*$BK37+(1-$D$27)*AQ$29),"")</f>
+        <f>IFERROR(AP35*$BJ35*(1+($BL35-1)*AP$30)*($D$27*$BK35+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20251219800433</t>
+          <t>20251215800970</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>4</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>컨테이너선 4척</t>
-        </is>
+          <t>태안화력 5~8호기 저탄장 옥내화 공사</t>
+        </is>
+      </c>
+      <c r="E60" s="18">
+        <f>IFERROR(E36*$BJ36*(1+($BL36-1)*E$30)*($D$27*$BK36+(1-$D$27)*E$29),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="18">
+        <f>IFERROR(F36*$BJ36*(1+($BL36-1)*F$30)*($D$27*$BK36+(1-$D$27)*F$29),"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="18">
+        <f>IFERROR(G36*$BJ36*(1+($BL36-1)*G$30)*($D$27*$BK36+(1-$D$27)*G$29),"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="18">
+        <f>IFERROR(H36*$BJ36*(1+($BL36-1)*H$30)*($D$27*$BK36+(1-$D$27)*H$29),"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="18">
+        <f>IFERROR(I36*$BJ36*(1+($BL36-1)*I$30)*($D$27*$BK36+(1-$D$27)*I$29),"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="18">
+        <f>IFERROR(J36*$BJ36*(1+($BL36-1)*J$30)*($D$27*$BK36+(1-$D$27)*J$29),"")</f>
+        <v/>
+      </c>
+      <c r="K60" s="18">
+        <f>IFERROR(K36*$BJ36*(1+($BL36-1)*K$30)*($D$27*$BK36+(1-$D$27)*K$29),"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="18">
+        <f>IFERROR(L36*$BJ36*(1+($BL36-1)*L$30)*($D$27*$BK36+(1-$D$27)*L$29),"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="18">
+        <f>IFERROR(M36*$BJ36*(1+($BL36-1)*M$30)*($D$27*$BK36+(1-$D$27)*M$29),"")</f>
+        <v/>
+      </c>
+      <c r="N60" s="18">
+        <f>IFERROR(N36*$BJ36*(1+($BL36-1)*N$30)*($D$27*$BK36+(1-$D$27)*N$29),"")</f>
+        <v/>
+      </c>
+      <c r="O60" s="18">
+        <f>IFERROR(O36*$BJ36*(1+($BL36-1)*O$30)*($D$27*$BK36+(1-$D$27)*O$29),"")</f>
+        <v/>
+      </c>
+      <c r="P60" s="18">
+        <f>IFERROR(P36*$BJ36*(1+($BL36-1)*P$30)*($D$27*$BK36+(1-$D$27)*P$29),"")</f>
+        <v/>
+      </c>
+      <c r="Q60" s="18">
+        <f>IFERROR(Q36*$BJ36*(1+($BL36-1)*Q$30)*($D$27*$BK36+(1-$D$27)*Q$29),"")</f>
+        <v/>
+      </c>
+      <c r="R60" s="18">
+        <f>IFERROR(R36*$BJ36*(1+($BL36-1)*R$30)*($D$27*$BK36+(1-$D$27)*R$29),"")</f>
+        <v/>
+      </c>
+      <c r="S60" s="18">
+        <f>IFERROR(S36*$BJ36*(1+($BL36-1)*S$30)*($D$27*$BK36+(1-$D$27)*S$29),"")</f>
+        <v/>
+      </c>
+      <c r="T60" s="18">
+        <f>IFERROR(T36*$BJ36*(1+($BL36-1)*T$30)*($D$27*$BK36+(1-$D$27)*T$29),"")</f>
+        <v/>
+      </c>
+      <c r="U60" s="18">
+        <f>IFERROR(U36*$BJ36*(1+($BL36-1)*U$30)*($D$27*$BK36+(1-$D$27)*U$29),"")</f>
+        <v/>
+      </c>
+      <c r="V60" s="18">
+        <f>IFERROR(V36*$BJ36*(1+($BL36-1)*V$30)*($D$27*$BK36+(1-$D$27)*V$29),"")</f>
+        <v/>
+      </c>
+      <c r="W60" s="18">
+        <f>IFERROR(W36*$BJ36*(1+($BL36-1)*W$30)*($D$27*$BK36+(1-$D$27)*W$29),"")</f>
+        <v/>
+      </c>
+      <c r="X60" s="18">
+        <f>IFERROR(X36*$BJ36*(1+($BL36-1)*X$30)*($D$27*$BK36+(1-$D$27)*X$29),"")</f>
+        <v/>
+      </c>
+      <c r="Y60" s="18">
+        <f>IFERROR(Y36*$BJ36*(1+($BL36-1)*Y$30)*($D$27*$BK36+(1-$D$27)*Y$29),"")</f>
+        <v/>
+      </c>
+      <c r="Z60" s="18">
+        <f>IFERROR(Z36*$BJ36*(1+($BL36-1)*Z$30)*($D$27*$BK36+(1-$D$27)*Z$29),"")</f>
+        <v/>
+      </c>
+      <c r="AA60" s="18">
+        <f>IFERROR(AA36*$BJ36*(1+($BL36-1)*AA$30)*($D$27*$BK36+(1-$D$27)*AA$29),"")</f>
+        <v/>
+      </c>
+      <c r="AB60" s="18">
+        <f>IFERROR(AB36*$BJ36*(1+($BL36-1)*AB$30)*($D$27*$BK36+(1-$D$27)*AB$29),"")</f>
+        <v/>
+      </c>
+      <c r="AC60" s="18">
+        <f>IFERROR(AC36*$BJ36*(1+($BL36-1)*AC$30)*($D$27*$BK36+(1-$D$27)*AC$29),"")</f>
+        <v/>
       </c>
       <c r="AD60" s="18">
-        <f>IFERROR(AD38*$BJ38*(1+($BL38-1)*AD$30)*($D$27*$BK38+(1-$D$27)*AD$29),"")</f>
-        <v/>
-      </c>
-      <c r="AE60" s="18">
-        <f>IFERROR(AE38*$BJ38*(1+($BL38-1)*AE$30)*($D$27*$BK38+(1-$D$27)*AE$29),"")</f>
-        <v/>
-      </c>
-      <c r="AF60" s="18">
-        <f>IFERROR(AF38*$BJ38*(1+($BL38-1)*AF$30)*($D$27*$BK38+(1-$D$27)*AF$29),"")</f>
-        <v/>
-      </c>
-      <c r="AG60" s="18">
-        <f>IFERROR(AG38*$BJ38*(1+($BL38-1)*AG$30)*($D$27*$BK38+(1-$D$27)*AG$29),"")</f>
-        <v/>
-      </c>
-      <c r="AH60" s="18">
-        <f>IFERROR(AH38*$BJ38*(1+($BL38-1)*AH$30)*($D$27*$BK38+(1-$D$27)*AH$29),"")</f>
-        <v/>
-      </c>
-      <c r="AI60" s="18">
-        <f>IFERROR(AI38*$BJ38*(1+($BL38-1)*AI$30)*($D$27*$BK38+(1-$D$27)*AI$29),"")</f>
-        <v/>
-      </c>
-      <c r="AJ60" s="18">
-        <f>IFERROR(AJ38*$BJ38*(1+($BL38-1)*AJ$30)*($D$27*$BK38+(1-$D$27)*AJ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AK60" s="18">
-        <f>IFERROR(AK38*$BJ38*(1+($BL38-1)*AK$30)*($D$27*$BK38+(1-$D$27)*AK$29),"")</f>
-        <v/>
-      </c>
-      <c r="AL60" s="18">
-        <f>IFERROR(AL38*$BJ38*(1+($BL38-1)*AL$30)*($D$27*$BK38+(1-$D$27)*AL$29),"")</f>
-        <v/>
-      </c>
-      <c r="AM60" s="18">
-        <f>IFERROR(AM38*$BJ38*(1+($BL38-1)*AM$30)*($D$27*$BK38+(1-$D$27)*AM$29),"")</f>
-        <v/>
-      </c>
-      <c r="AN60" s="18">
-        <f>IFERROR(AN38*$BJ38*(1+($BL38-1)*AN$30)*($D$27*$BK38+(1-$D$27)*AN$29),"")</f>
-        <v/>
-      </c>
-      <c r="AO60" s="18">
-        <f>IFERROR(AO38*$BJ38*(1+($BL38-1)*AO$30)*($D$27*$BK38+(1-$D$27)*AO$29),"")</f>
-        <v/>
-      </c>
-      <c r="AP60" s="18">
-        <f>IFERROR(AP38*$BJ38*(1+($BL38-1)*AP$30)*($D$27*$BK38+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AD36*$BJ36*(1+($BL36-1)*AD$30)*($D$27*$BK36+(1-$D$27)*AD$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260116800207</t>
+          <t>20251219800421</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VLGC 1척</t>
-        </is>
+          <t>LNGC 3척</t>
+        </is>
+      </c>
+      <c r="AB61" s="18">
+        <f>IFERROR(AB37*$BJ37*(1+($BL37-1)*AB$30)*($D$27*$BK37+(1-$D$27)*AB$29),"")</f>
+        <v/>
+      </c>
+      <c r="AC61" s="18">
+        <f>IFERROR(AC37*$BJ37*(1+($BL37-1)*AC$30)*($D$27*$BK37+(1-$D$27)*AC$29),"")</f>
+        <v/>
+      </c>
+      <c r="AD61" s="18">
+        <f>IFERROR(AD37*$BJ37*(1+($BL37-1)*AD$30)*($D$27*$BK37+(1-$D$27)*AD$29),"")</f>
+        <v/>
       </c>
       <c r="AE61" s="18">
-        <f>IFERROR(AE39*$BJ39*(1+($BL39-1)*AE$30)*($D$27*$BK39+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE37*$BJ37*(1+($BL37-1)*AE$30)*($D$27*$BK37+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF61" s="18">
-        <f>IFERROR(AF39*$BJ39*(1+($BL39-1)*AF$30)*($D$27*$BK39+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF37*$BJ37*(1+($BL37-1)*AF$30)*($D$27*$BK37+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG61" s="18">
-        <f>IFERROR(AG39*$BJ39*(1+($BL39-1)*AG$30)*($D$27*$BK39+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG37*$BJ37*(1+($BL37-1)*AG$30)*($D$27*$BK37+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH61" s="18">
-        <f>IFERROR(AH39*$BJ39*(1+($BL39-1)*AH$30)*($D$27*$BK39+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH37*$BJ37*(1+($BL37-1)*AH$30)*($D$27*$BK37+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI61" s="18">
-        <f>IFERROR(AI39*$BJ39*(1+($BL39-1)*AI$30)*($D$27*$BK39+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI37*$BJ37*(1+($BL37-1)*AI$30)*($D$27*$BK37+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ61" s="18">
-        <f>IFERROR(AJ39*$BJ39*(1+($BL39-1)*AJ$30)*($D$27*$BK39+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ37*$BJ37*(1+($BL37-1)*AJ$30)*($D$27*$BK37+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK61" s="18">
-        <f>IFERROR(AK39*$BJ39*(1+($BL39-1)*AK$30)*($D$27*$BK39+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK37*$BJ37*(1+($BL37-1)*AK$30)*($D$27*$BK37+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL61" s="18">
-        <f>IFERROR(AL39*$BJ39*(1+($BL39-1)*AL$30)*($D$27*$BK39+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL37*$BJ37*(1+($BL37-1)*AL$30)*($D$27*$BK37+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM61" s="18">
-        <f>IFERROR(AM39*$BJ39*(1+($BL39-1)*AM$30)*($D$27*$BK39+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM37*$BJ37*(1+($BL37-1)*AM$30)*($D$27*$BK37+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN61" s="18">
-        <f>IFERROR(AN39*$BJ39*(1+($BL39-1)*AN$30)*($D$27*$BK39+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN37*$BJ37*(1+($BL37-1)*AN$30)*($D$27*$BK37+(1-$D$27)*AN$29),"")</f>
+        <v/>
+      </c>
+      <c r="AO61" s="18">
+        <f>IFERROR(AO37*$BJ37*(1+($BL37-1)*AO$30)*($D$27*$BK37+(1-$D$27)*AO$29),"")</f>
+        <v/>
+      </c>
+      <c r="AP61" s="18">
+        <f>IFERROR(AP37*$BJ37*(1+($BL37-1)*AP$30)*($D$27*$BK37+(1-$D$27)*AP$29),"")</f>
+        <v/>
+      </c>
+      <c r="AQ61" s="18">
+        <f>IFERROR(AQ37*$BJ37*(1+($BL37-1)*AQ$30)*($D$27*$BK37+(1-$D$27)*AQ$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260202800947</t>
+          <t>20251219800433</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LNGC 1척</t>
-        </is>
+          <t>컨테이너선 4척</t>
+        </is>
+      </c>
+      <c r="AD62" s="18">
+        <f>IFERROR(AD38*$BJ38*(1+($BL38-1)*AD$30)*($D$27*$BK38+(1-$D$27)*AD$29),"")</f>
+        <v/>
       </c>
       <c r="AE62" s="18">
-        <f>IFERROR(AE40*$BJ40*(1+($BL40-1)*AE$30)*($D$27*$BK40+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE38*$BJ38*(1+($BL38-1)*AE$30)*($D$27*$BK38+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF62" s="18">
-        <f>IFERROR(AF40*$BJ40*(1+($BL40-1)*AF$30)*($D$27*$BK40+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF38*$BJ38*(1+($BL38-1)*AF$30)*($D$27*$BK38+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG62" s="18">
-        <f>IFERROR(AG40*$BJ40*(1+($BL40-1)*AG$30)*($D$27*$BK40+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG38*$BJ38*(1+($BL38-1)*AG$30)*($D$27*$BK38+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH62" s="18">
-        <f>IFERROR(AH40*$BJ40*(1+($BL40-1)*AH$30)*($D$27*$BK40+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH38*$BJ38*(1+($BL38-1)*AH$30)*($D$27*$BK38+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI62" s="18">
-        <f>IFERROR(AI40*$BJ40*(1+($BL40-1)*AI$30)*($D$27*$BK40+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI38*$BJ38*(1+($BL38-1)*AI$30)*($D$27*$BK38+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ62" s="18">
-        <f>IFERROR(AJ40*$BJ40*(1+($BL40-1)*AJ$30)*($D$27*$BK40+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ38*$BJ38*(1+($BL38-1)*AJ$30)*($D$27*$BK38+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK62" s="18">
-        <f>IFERROR(AK40*$BJ40*(1+($BL40-1)*AK$30)*($D$27*$BK40+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK38*$BJ38*(1+($BL38-1)*AK$30)*($D$27*$BK38+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL62" s="18">
-        <f>IFERROR(AL40*$BJ40*(1+($BL40-1)*AL$30)*($D$27*$BK40+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL38*$BJ38*(1+($BL38-1)*AL$30)*($D$27*$BK38+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM62" s="18">
-        <f>IFERROR(AM40*$BJ40*(1+($BL40-1)*AM$30)*($D$27*$BK40+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM38*$BJ38*(1+($BL38-1)*AM$30)*($D$27*$BK38+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN62" s="18">
-        <f>IFERROR(AN40*$BJ40*(1+($BL40-1)*AN$30)*($D$27*$BK40+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN38*$BJ38*(1+($BL38-1)*AN$30)*($D$27*$BK38+(1-$D$27)*AN$29),"")</f>
+        <v/>
+      </c>
+      <c r="AO62" s="18">
+        <f>IFERROR(AO38*$BJ38*(1+($BL38-1)*AO$30)*($D$27*$BK38+(1-$D$27)*AO$29),"")</f>
+        <v/>
+      </c>
+      <c r="AP62" s="18">
+        <f>IFERROR(AP38*$BJ38*(1+($BL38-1)*AP$30)*($D$27*$BK38+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260304800002</t>
+          <t>20260116800207</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>157,000 DWT 원유운반선 4척</t>
-        </is>
-      </c>
-      <c r="AD63" s="18">
-        <f>IFERROR(AD41*$BJ41*(1+($BL41-1)*AD$30)*($D$27*$BK41+(1-$D$27)*AD$29),"")</f>
-        <v/>
+          <t>VLGC 1척</t>
+        </is>
       </c>
       <c r="AE63" s="18">
-        <f>IFERROR(AE41*$BJ41*(1+($BL41-1)*AE$30)*($D$27*$BK41+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE39*$BJ39*(1+($BL39-1)*AE$30)*($D$27*$BK39+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF63" s="18">
-        <f>IFERROR(AF41*$BJ41*(1+($BL41-1)*AF$30)*($D$27*$BK41+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF39*$BJ39*(1+($BL39-1)*AF$30)*($D$27*$BK39+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG63" s="18">
-        <f>IFERROR(AG41*$BJ41*(1+($BL41-1)*AG$30)*($D$27*$BK41+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG39*$BJ39*(1+($BL39-1)*AG$30)*($D$27*$BK39+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH63" s="18">
-        <f>IFERROR(AH41*$BJ41*(1+($BL41-1)*AH$30)*($D$27*$BK41+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH39*$BJ39*(1+($BL39-1)*AH$30)*($D$27*$BK39+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI63" s="18">
-        <f>IFERROR(AI41*$BJ41*(1+($BL41-1)*AI$30)*($D$27*$BK41+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI39*$BJ39*(1+($BL39-1)*AI$30)*($D$27*$BK39+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ63" s="18">
-        <f>IFERROR(AJ41*$BJ41*(1+($BL41-1)*AJ$30)*($D$27*$BK41+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ39*$BJ39*(1+($BL39-1)*AJ$30)*($D$27*$BK39+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK63" s="18">
-        <f>IFERROR(AK41*$BJ41*(1+($BL41-1)*AK$30)*($D$27*$BK41+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK39*$BJ39*(1+($BL39-1)*AK$30)*($D$27*$BK39+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL63" s="18">
-        <f>IFERROR(AL41*$BJ41*(1+($BL41-1)*AL$30)*($D$27*$BK41+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL39*$BJ39*(1+($BL39-1)*AL$30)*($D$27*$BK39+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM63" s="18">
-        <f>IFERROR(AM41*$BJ41*(1+($BL41-1)*AM$30)*($D$27*$BK41+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM39*$BJ39*(1+($BL39-1)*AM$30)*($D$27*$BK39+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN63" s="18">
-        <f>IFERROR(AN41*$BJ41*(1+($BL41-1)*AN$30)*($D$27*$BK41+(1-$D$27)*AN$29),"")</f>
-        <v/>
-      </c>
-      <c r="AO63" s="18">
-        <f>IFERROR(AO41*$BJ41*(1+($BL41-1)*AO$30)*($D$27*$BK41+(1-$D$27)*AO$29),"")</f>
-        <v/>
-      </c>
-      <c r="AP63" s="18">
-        <f>IFERROR(AP41*$BJ41*(1+($BL41-1)*AP$30)*($D$27*$BK41+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AN39*$BJ39*(1+($BL39-1)*AN$30)*($D$27*$BK39+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260306800225</t>
+          <t>20260202800947</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>157,000 DWT 원유운반선 2척</t>
+          <t>LNGC 1척</t>
         </is>
       </c>
       <c r="AE64" s="18">
-        <f>IFERROR(AE42*$BJ42*(1+($BL42-1)*AE$30)*($D$27*$BK42+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE40*$BJ40*(1+($BL40-1)*AE$30)*($D$27*$BK40+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF64" s="18">
-        <f>IFERROR(AF42*$BJ42*(1+($BL42-1)*AF$30)*($D$27*$BK42+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF40*$BJ40*(1+($BL40-1)*AF$30)*($D$27*$BK40+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG64" s="18">
-        <f>IFERROR(AG42*$BJ42*(1+($BL42-1)*AG$30)*($D$27*$BK42+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG40*$BJ40*(1+($BL40-1)*AG$30)*($D$27*$BK40+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH64" s="18">
-        <f>IFERROR(AH42*$BJ42*(1+($BL42-1)*AH$30)*($D$27*$BK42+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH40*$BJ40*(1+($BL40-1)*AH$30)*($D$27*$BK40+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI64" s="18">
-        <f>IFERROR(AI42*$BJ42*(1+($BL42-1)*AI$30)*($D$27*$BK42+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI40*$BJ40*(1+($BL40-1)*AI$30)*($D$27*$BK40+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ64" s="18">
-        <f>IFERROR(AJ42*$BJ42*(1+($BL42-1)*AJ$30)*($D$27*$BK42+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ40*$BJ40*(1+($BL40-1)*AJ$30)*($D$27*$BK40+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK64" s="18">
-        <f>IFERROR(AK42*$BJ42*(1+($BL42-1)*AK$30)*($D$27*$BK42+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK40*$BJ40*(1+($BL40-1)*AK$30)*($D$27*$BK40+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL64" s="18">
-        <f>IFERROR(AL42*$BJ42*(1+($BL42-1)*AL$30)*($D$27*$BK42+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL40*$BJ40*(1+($BL40-1)*AL$30)*($D$27*$BK40+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM64" s="18">
-        <f>IFERROR(AM42*$BJ42*(1+($BL42-1)*AM$30)*($D$27*$BK42+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM40*$BJ40*(1+($BL40-1)*AM$30)*($D$27*$BK40+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN64" s="18">
-        <f>IFERROR(AN42*$BJ42*(1+($BL42-1)*AN$30)*($D$27*$BK42+(1-$D$27)*AN$29),"")</f>
-        <v/>
-      </c>
-      <c r="AO64" s="18">
-        <f>IFERROR(AO42*$BJ42*(1+($BL42-1)*AO$30)*($D$27*$BK42+(1-$D$27)*AO$29),"")</f>
-        <v/>
-      </c>
-      <c r="AP64" s="18">
-        <f>IFERROR(AP42*$BJ42*(1+($BL42-1)*AP$30)*($D$27*$BK42+(1-$D$27)*AP$29),"")</f>
-        <v/>
-      </c>
-      <c r="AQ64" s="18">
-        <f>IFERROR(AQ42*$BJ42*(1+($BL42-1)*AQ$30)*($D$27*$BK42+(1-$D$27)*AQ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AR64" s="18">
-        <f>IFERROR(AR42*$BJ42*(1+($BL42-1)*AR$30)*($D$27*$BK42+(1-$D$27)*AR$29),"")</f>
+        <f>IFERROR(AN40*$BJ40*(1+($BL40-1)*AN$30)*($D$27*$BK40+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260310800414</t>
+          <t>20260304800002</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LPGC 2척</t>
-        </is>
+          <t>157,000 DWT 원유운반선 4척</t>
+        </is>
+      </c>
+      <c r="AD65" s="18">
+        <f>IFERROR(AD41*$BJ41*(1+($BL41-1)*AD$30)*($D$27*$BK41+(1-$D$27)*AD$29),"")</f>
+        <v/>
       </c>
       <c r="AE65" s="18">
-        <f>IFERROR(AE43*$BJ43*(1+($BL43-1)*AE$30)*($D$27*$BK43+(1-$D$27)*AE$29),"")</f>
+        <f>IFERROR(AE41*$BJ41*(1+($BL41-1)*AE$30)*($D$27*$BK41+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
       <c r="AF65" s="18">
-        <f>IFERROR(AF43*$BJ43*(1+($BL43-1)*AF$30)*($D$27*$BK43+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF41*$BJ41*(1+($BL41-1)*AF$30)*($D$27*$BK41+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG65" s="18">
-        <f>IFERROR(AG43*$BJ43*(1+($BL43-1)*AG$30)*($D$27*$BK43+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG41*$BJ41*(1+($BL41-1)*AG$30)*($D$27*$BK41+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH65" s="18">
-        <f>IFERROR(AH43*$BJ43*(1+($BL43-1)*AH$30)*($D$27*$BK43+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH41*$BJ41*(1+($BL41-1)*AH$30)*($D$27*$BK41+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI65" s="18">
-        <f>IFERROR(AI43*$BJ43*(1+($BL43-1)*AI$30)*($D$27*$BK43+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI41*$BJ41*(1+($BL41-1)*AI$30)*($D$27*$BK41+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ65" s="18">
-        <f>IFERROR(AJ43*$BJ43*(1+($BL43-1)*AJ$30)*($D$27*$BK43+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ41*$BJ41*(1+($BL41-1)*AJ$30)*($D$27*$BK41+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK65" s="18">
-        <f>IFERROR(AK43*$BJ43*(1+($BL43-1)*AK$30)*($D$27*$BK43+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK41*$BJ41*(1+($BL41-1)*AK$30)*($D$27*$BK41+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL65" s="18">
-        <f>IFERROR(AL43*$BJ43*(1+($BL43-1)*AL$30)*($D$27*$BK43+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL41*$BJ41*(1+($BL41-1)*AL$30)*($D$27*$BK41+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM65" s="18">
-        <f>IFERROR(AM43*$BJ43*(1+($BL43-1)*AM$30)*($D$27*$BK43+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM41*$BJ41*(1+($BL41-1)*AM$30)*($D$27*$BK41+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN65" s="18">
-        <f>IFERROR(AN43*$BJ43*(1+($BL43-1)*AN$30)*($D$27*$BK43+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN41*$BJ41*(1+($BL41-1)*AN$30)*($D$27*$BK41+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO65" s="18">
-        <f>IFERROR(AO43*$BJ43*(1+($BL43-1)*AO$30)*($D$27*$BK43+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO41*$BJ41*(1+($BL41-1)*AO$30)*($D$27*$BK41+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP65" s="18">
-        <f>IFERROR(AP43*$BJ43*(1+($BL43-1)*AP$30)*($D$27*$BK43+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP41*$BJ41*(1+($BL41-1)*AP$30)*($D$27*$BK41+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260403800582</t>
+          <t>20260306800225</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -45258,67 +45320,75 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LPGC 2척</t>
-        </is>
+          <t>157,000 DWT 원유운반선 2척</t>
+        </is>
+      </c>
+      <c r="AE66" s="18">
+        <f>IFERROR(AE42*$BJ42*(1+($BL42-1)*AE$30)*($D$27*$BK42+(1-$D$27)*AE$29),"")</f>
+        <v/>
       </c>
       <c r="AF66" s="18">
-        <f>IFERROR(AF44*$BJ44*(1+($BL44-1)*AF$30)*($D$27*$BK44+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF42*$BJ42*(1+($BL42-1)*AF$30)*($D$27*$BK42+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG66" s="18">
-        <f>IFERROR(AG44*$BJ44*(1+($BL44-1)*AG$30)*($D$27*$BK44+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG42*$BJ42*(1+($BL42-1)*AG$30)*($D$27*$BK42+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH66" s="18">
-        <f>IFERROR(AH44*$BJ44*(1+($BL44-1)*AH$30)*($D$27*$BK44+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH42*$BJ42*(1+($BL42-1)*AH$30)*($D$27*$BK42+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI66" s="18">
-        <f>IFERROR(AI44*$BJ44*(1+($BL44-1)*AI$30)*($D$27*$BK44+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI42*$BJ42*(1+($BL42-1)*AI$30)*($D$27*$BK42+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ66" s="18">
-        <f>IFERROR(AJ44*$BJ44*(1+($BL44-1)*AJ$30)*($D$27*$BK44+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ42*$BJ42*(1+($BL42-1)*AJ$30)*($D$27*$BK42+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK66" s="18">
-        <f>IFERROR(AK44*$BJ44*(1+($BL44-1)*AK$30)*($D$27*$BK44+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK42*$BJ42*(1+($BL42-1)*AK$30)*($D$27*$BK42+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL66" s="18">
-        <f>IFERROR(AL44*$BJ44*(1+($BL44-1)*AL$30)*($D$27*$BK44+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL42*$BJ42*(1+($BL42-1)*AL$30)*($D$27*$BK42+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM66" s="18">
-        <f>IFERROR(AM44*$BJ44*(1+($BL44-1)*AM$30)*($D$27*$BK44+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM42*$BJ42*(1+($BL42-1)*AM$30)*($D$27*$BK42+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN66" s="18">
-        <f>IFERROR(AN44*$BJ44*(1+($BL44-1)*AN$30)*($D$27*$BK44+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN42*$BJ42*(1+($BL42-1)*AN$30)*($D$27*$BK42+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO66" s="18">
-        <f>IFERROR(AO44*$BJ44*(1+($BL44-1)*AO$30)*($D$27*$BK44+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO42*$BJ42*(1+($BL42-1)*AO$30)*($D$27*$BK42+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP66" s="18">
-        <f>IFERROR(AP44*$BJ44*(1+($BL44-1)*AP$30)*($D$27*$BK44+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP42*$BJ42*(1+($BL42-1)*AP$30)*($D$27*$BK42+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
       <c r="AQ66" s="18">
-        <f>IFERROR(AQ44*$BJ44*(1+($BL44-1)*AQ$30)*($D$27*$BK44+(1-$D$27)*AQ$29),"")</f>
+        <f>IFERROR(AQ42*$BJ42*(1+($BL42-1)*AQ$30)*($D$27*$BK42+(1-$D$27)*AQ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AR66" s="18">
+        <f>IFERROR(AR42*$BJ42*(1+($BL42-1)*AR$30)*($D$27*$BK42+(1-$D$27)*AR$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260408800703</t>
+          <t>20260310800414</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -45326,70 +45396,62 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LNGC 2척</t>
-        </is>
+          <t>LPGC 2척</t>
+        </is>
+      </c>
+      <c r="AE67" s="18">
+        <f>IFERROR(AE43*$BJ43*(1+($BL43-1)*AE$30)*($D$27*$BK43+(1-$D$27)*AE$29),"")</f>
+        <v/>
       </c>
       <c r="AF67" s="18">
-        <f>IFERROR(AF45*$BJ45*(1+($BL45-1)*AF$30)*($D$27*$BK45+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF43*$BJ43*(1+($BL43-1)*AF$30)*($D$27*$BK43+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG67" s="18">
-        <f>IFERROR(AG45*$BJ45*(1+($BL45-1)*AG$30)*($D$27*$BK45+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG43*$BJ43*(1+($BL43-1)*AG$30)*($D$27*$BK43+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH67" s="18">
-        <f>IFERROR(AH45*$BJ45*(1+($BL45-1)*AH$30)*($D$27*$BK45+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH43*$BJ43*(1+($BL43-1)*AH$30)*($D$27*$BK43+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI67" s="18">
-        <f>IFERROR(AI45*$BJ45*(1+($BL45-1)*AI$30)*($D$27*$BK45+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI43*$BJ43*(1+($BL43-1)*AI$30)*($D$27*$BK43+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ67" s="18">
-        <f>IFERROR(AJ45*$BJ45*(1+($BL45-1)*AJ$30)*($D$27*$BK45+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ43*$BJ43*(1+($BL43-1)*AJ$30)*($D$27*$BK43+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK67" s="18">
-        <f>IFERROR(AK45*$BJ45*(1+($BL45-1)*AK$30)*($D$27*$BK45+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK43*$BJ43*(1+($BL43-1)*AK$30)*($D$27*$BK43+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL67" s="18">
-        <f>IFERROR(AL45*$BJ45*(1+($BL45-1)*AL$30)*($D$27*$BK45+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL43*$BJ43*(1+($BL43-1)*AL$30)*($D$27*$BK43+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM67" s="18">
-        <f>IFERROR(AM45*$BJ45*(1+($BL45-1)*AM$30)*($D$27*$BK45+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM43*$BJ43*(1+($BL43-1)*AM$30)*($D$27*$BK43+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN67" s="18">
-        <f>IFERROR(AN45*$BJ45*(1+($BL45-1)*AN$30)*($D$27*$BK45+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN43*$BJ43*(1+($BL43-1)*AN$30)*($D$27*$BK43+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO67" s="18">
-        <f>IFERROR(AO45*$BJ45*(1+($BL45-1)*AO$30)*($D$27*$BK45+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO43*$BJ43*(1+($BL43-1)*AO$30)*($D$27*$BK43+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP67" s="18">
-        <f>IFERROR(AP45*$BJ45*(1+($BL45-1)*AP$30)*($D$27*$BK45+(1-$D$27)*AP$29),"")</f>
-        <v/>
-      </c>
-      <c r="AQ67" s="18">
-        <f>IFERROR(AQ45*$BJ45*(1+($BL45-1)*AQ$30)*($D$27*$BK45+(1-$D$27)*AQ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AR67" s="18">
-        <f>IFERROR(AR45*$BJ45*(1+($BL45-1)*AR$30)*($D$27*$BK45+(1-$D$27)*AR$29),"")</f>
-        <v/>
-      </c>
-      <c r="AS67" s="18">
-        <f>IFERROR(AS45*$BJ45*(1+($BL45-1)*AS$30)*($D$27*$BK45+(1-$D$27)*AS$29),"")</f>
+        <f>IFERROR(AP43*$BJ43*(1+($BL43-1)*AP$30)*($D$27*$BK43+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260416800167</t>
+          <t>20260403800582</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -45406,62 +45468,58 @@
         </is>
       </c>
       <c r="AF68" s="18">
-        <f>IFERROR(AF46*$BJ46*(1+($BL46-1)*AF$30)*($D$27*$BK46+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF44*$BJ44*(1+($BL44-1)*AF$30)*($D$27*$BK44+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG68" s="18">
-        <f>IFERROR(AG46*$BJ46*(1+($BL46-1)*AG$30)*($D$27*$BK46+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG44*$BJ44*(1+($BL44-1)*AG$30)*($D$27*$BK44+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH68" s="18">
-        <f>IFERROR(AH46*$BJ46*(1+($BL46-1)*AH$30)*($D$27*$BK46+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH44*$BJ44*(1+($BL44-1)*AH$30)*($D$27*$BK44+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI68" s="18">
-        <f>IFERROR(AI46*$BJ46*(1+($BL46-1)*AI$30)*($D$27*$BK46+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI44*$BJ44*(1+($BL44-1)*AI$30)*($D$27*$BK44+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ68" s="18">
-        <f>IFERROR(AJ46*$BJ46*(1+($BL46-1)*AJ$30)*($D$27*$BK46+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ44*$BJ44*(1+($BL44-1)*AJ$30)*($D$27*$BK44+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK68" s="18">
-        <f>IFERROR(AK46*$BJ46*(1+($BL46-1)*AK$30)*($D$27*$BK46+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK44*$BJ44*(1+($BL44-1)*AK$30)*($D$27*$BK44+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL68" s="18">
-        <f>IFERROR(AL46*$BJ46*(1+($BL46-1)*AL$30)*($D$27*$BK46+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL44*$BJ44*(1+($BL44-1)*AL$30)*($D$27*$BK44+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM68" s="18">
-        <f>IFERROR(AM46*$BJ46*(1+($BL46-1)*AM$30)*($D$27*$BK46+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM44*$BJ44*(1+($BL44-1)*AM$30)*($D$27*$BK44+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN68" s="18">
-        <f>IFERROR(AN46*$BJ46*(1+($BL46-1)*AN$30)*($D$27*$BK46+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN44*$BJ44*(1+($BL44-1)*AN$30)*($D$27*$BK44+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO68" s="18">
-        <f>IFERROR(AO46*$BJ46*(1+($BL46-1)*AO$30)*($D$27*$BK46+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO44*$BJ44*(1+($BL44-1)*AO$30)*($D$27*$BK44+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP68" s="18">
-        <f>IFERROR(AP46*$BJ46*(1+($BL46-1)*AP$30)*($D$27*$BK46+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP44*$BJ44*(1+($BL44-1)*AP$30)*($D$27*$BK44+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
       <c r="AQ68" s="18">
-        <f>IFERROR(AQ46*$BJ46*(1+($BL46-1)*AQ$30)*($D$27*$BK46+(1-$D$27)*AQ$29),"")</f>
-        <v/>
-      </c>
-      <c r="AR68" s="18">
-        <f>IFERROR(AR46*$BJ46*(1+($BL46-1)*AR$30)*($D$27*$BK46+(1-$D$27)*AR$29),"")</f>
+        <f>IFERROR(AQ44*$BJ44*(1+($BL44-1)*AQ$30)*($D$27*$BK44+(1-$D$27)*AQ$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260513800195</t>
+          <t>20260408800703</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -45478,66 +45536,66 @@
         </is>
       </c>
       <c r="AF69" s="18">
-        <f>IFERROR(AF47*$BJ47*(1+($BL47-1)*AF$30)*($D$27*$BK47+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF45*$BJ45*(1+($BL45-1)*AF$30)*($D$27*$BK45+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG69" s="18">
-        <f>IFERROR(AG47*$BJ47*(1+($BL47-1)*AG$30)*($D$27*$BK47+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG45*$BJ45*(1+($BL45-1)*AG$30)*($D$27*$BK45+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH69" s="18">
-        <f>IFERROR(AH47*$BJ47*(1+($BL47-1)*AH$30)*($D$27*$BK47+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH45*$BJ45*(1+($BL45-1)*AH$30)*($D$27*$BK45+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI69" s="18">
-        <f>IFERROR(AI47*$BJ47*(1+($BL47-1)*AI$30)*($D$27*$BK47+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI45*$BJ45*(1+($BL45-1)*AI$30)*($D$27*$BK45+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ69" s="18">
-        <f>IFERROR(AJ47*$BJ47*(1+($BL47-1)*AJ$30)*($D$27*$BK47+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ45*$BJ45*(1+($BL45-1)*AJ$30)*($D$27*$BK45+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK69" s="18">
-        <f>IFERROR(AK47*$BJ47*(1+($BL47-1)*AK$30)*($D$27*$BK47+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK45*$BJ45*(1+($BL45-1)*AK$30)*($D$27*$BK45+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL69" s="18">
-        <f>IFERROR(AL47*$BJ47*(1+($BL47-1)*AL$30)*($D$27*$BK47+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL45*$BJ45*(1+($BL45-1)*AL$30)*($D$27*$BK45+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM69" s="18">
-        <f>IFERROR(AM47*$BJ47*(1+($BL47-1)*AM$30)*($D$27*$BK47+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM45*$BJ45*(1+($BL45-1)*AM$30)*($D$27*$BK45+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN69" s="18">
-        <f>IFERROR(AN47*$BJ47*(1+($BL47-1)*AN$30)*($D$27*$BK47+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN45*$BJ45*(1+($BL45-1)*AN$30)*($D$27*$BK45+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO69" s="18">
-        <f>IFERROR(AO47*$BJ47*(1+($BL47-1)*AO$30)*($D$27*$BK47+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO45*$BJ45*(1+($BL45-1)*AO$30)*($D$27*$BK45+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP69" s="18">
-        <f>IFERROR(AP47*$BJ47*(1+($BL47-1)*AP$30)*($D$27*$BK47+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP45*$BJ45*(1+($BL45-1)*AP$30)*($D$27*$BK45+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
       <c r="AQ69" s="18">
-        <f>IFERROR(AQ47*$BJ47*(1+($BL47-1)*AQ$30)*($D$27*$BK47+(1-$D$27)*AQ$29),"")</f>
+        <f>IFERROR(AQ45*$BJ45*(1+($BL45-1)*AQ$30)*($D$27*$BK45+(1-$D$27)*AQ$29),"")</f>
         <v/>
       </c>
       <c r="AR69" s="18">
-        <f>IFERROR(AR47*$BJ47*(1+($BL47-1)*AR$30)*($D$27*$BK47+(1-$D$27)*AR$29),"")</f>
+        <f>IFERROR(AR45*$BJ45*(1+($BL45-1)*AR$30)*($D$27*$BK45+(1-$D$27)*AR$29),"")</f>
         <v/>
       </c>
       <c r="AS69" s="18">
-        <f>IFERROR(AS47*$BJ47*(1+($BL47-1)*AS$30)*($D$27*$BK47+(1-$D$27)*AS$29),"")</f>
+        <f>IFERROR(AS45*$BJ45*(1+($BL45-1)*AS$30)*($D$27*$BK45+(1-$D$27)*AS$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260521800360</t>
+          <t>20260416800167</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -45546,83 +45604,75 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VLAC 6척</t>
+          <t>LPGC 2척</t>
         </is>
       </c>
       <c r="AF70" s="18">
-        <f>IFERROR(AF48*$BJ48*(1+($BL48-1)*AF$30)*($D$27*$BK48+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF46*$BJ46*(1+($BL46-1)*AF$30)*($D$27*$BK46+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG70" s="18">
-        <f>IFERROR(AG48*$BJ48*(1+($BL48-1)*AG$30)*($D$27*$BK48+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG46*$BJ46*(1+($BL46-1)*AG$30)*($D$27*$BK46+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH70" s="18">
-        <f>IFERROR(AH48*$BJ48*(1+($BL48-1)*AH$30)*($D$27*$BK48+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH46*$BJ46*(1+($BL46-1)*AH$30)*($D$27*$BK46+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI70" s="18">
-        <f>IFERROR(AI48*$BJ48*(1+($BL48-1)*AI$30)*($D$27*$BK48+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI46*$BJ46*(1+($BL46-1)*AI$30)*($D$27*$BK46+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ70" s="18">
-        <f>IFERROR(AJ48*$BJ48*(1+($BL48-1)*AJ$30)*($D$27*$BK48+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ46*$BJ46*(1+($BL46-1)*AJ$30)*($D$27*$BK46+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK70" s="18">
-        <f>IFERROR(AK48*$BJ48*(1+($BL48-1)*AK$30)*($D$27*$BK48+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK46*$BJ46*(1+($BL46-1)*AK$30)*($D$27*$BK46+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL70" s="18">
-        <f>IFERROR(AL48*$BJ48*(1+($BL48-1)*AL$30)*($D$27*$BK48+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL46*$BJ46*(1+($BL46-1)*AL$30)*($D$27*$BK46+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM70" s="18">
-        <f>IFERROR(AM48*$BJ48*(1+($BL48-1)*AM$30)*($D$27*$BK48+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM46*$BJ46*(1+($BL46-1)*AM$30)*($D$27*$BK46+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN70" s="18">
-        <f>IFERROR(AN48*$BJ48*(1+($BL48-1)*AN$30)*($D$27*$BK48+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN46*$BJ46*(1+($BL46-1)*AN$30)*($D$27*$BK46+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO70" s="18">
-        <f>IFERROR(AO48*$BJ48*(1+($BL48-1)*AO$30)*($D$27*$BK48+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO46*$BJ46*(1+($BL46-1)*AO$30)*($D$27*$BK46+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP70" s="18">
-        <f>IFERROR(AP48*$BJ48*(1+($BL48-1)*AP$30)*($D$27*$BK48+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP46*$BJ46*(1+($BL46-1)*AP$30)*($D$27*$BK46+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
       <c r="AQ70" s="18">
-        <f>IFERROR(AQ48*$BJ48*(1+($BL48-1)*AQ$30)*($D$27*$BK48+(1-$D$27)*AQ$29),"")</f>
+        <f>IFERROR(AQ46*$BJ46*(1+($BL46-1)*AQ$30)*($D$27*$BK46+(1-$D$27)*AQ$29),"")</f>
         <v/>
       </c>
       <c r="AR70" s="18">
-        <f>IFERROR(AR48*$BJ48*(1+($BL48-1)*AR$30)*($D$27*$BK48+(1-$D$27)*AR$29),"")</f>
-        <v/>
-      </c>
-      <c r="AS70" s="18">
-        <f>IFERROR(AS48*$BJ48*(1+($BL48-1)*AS$30)*($D$27*$BK48+(1-$D$27)*AS$29),"")</f>
-        <v/>
-      </c>
-      <c r="AT70" s="18">
-        <f>IFERROR(AT48*$BJ48*(1+($BL48-1)*AT$30)*($D$27*$BK48+(1-$D$27)*AT$29),"")</f>
+        <f>IFERROR(AR46*$BJ46*(1+($BL46-1)*AR$30)*($D$27*$BK46+(1-$D$27)*AR$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260629800351</t>
+          <t>20260513800195</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -45630,74 +45680,70 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LPGC 2척</t>
+          <t>LNGC 2척</t>
         </is>
       </c>
       <c r="AF71" s="18">
-        <f>IFERROR(AF49*$BJ49*(1+($BL49-1)*AF$30)*($D$27*$BK49+(1-$D$27)*AF$29),"")</f>
+        <f>IFERROR(AF47*$BJ47*(1+($BL47-1)*AF$30)*($D$27*$BK47+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
       <c r="AG71" s="18">
-        <f>IFERROR(AG49*$BJ49*(1+($BL49-1)*AG$30)*($D$27*$BK49+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG47*$BJ47*(1+($BL47-1)*AG$30)*($D$27*$BK47+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH71" s="18">
-        <f>IFERROR(AH49*$BJ49*(1+($BL49-1)*AH$30)*($D$27*$BK49+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH47*$BJ47*(1+($BL47-1)*AH$30)*($D$27*$BK47+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI71" s="18">
-        <f>IFERROR(AI49*$BJ49*(1+($BL49-1)*AI$30)*($D$27*$BK49+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI47*$BJ47*(1+($BL47-1)*AI$30)*($D$27*$BK47+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ71" s="18">
-        <f>IFERROR(AJ49*$BJ49*(1+($BL49-1)*AJ$30)*($D$27*$BK49+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ47*$BJ47*(1+($BL47-1)*AJ$30)*($D$27*$BK47+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK71" s="18">
-        <f>IFERROR(AK49*$BJ49*(1+($BL49-1)*AK$30)*($D$27*$BK49+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK47*$BJ47*(1+($BL47-1)*AK$30)*($D$27*$BK47+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL71" s="18">
-        <f>IFERROR(AL49*$BJ49*(1+($BL49-1)*AL$30)*($D$27*$BK49+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL47*$BJ47*(1+($BL47-1)*AL$30)*($D$27*$BK47+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM71" s="18">
-        <f>IFERROR(AM49*$BJ49*(1+($BL49-1)*AM$30)*($D$27*$BK49+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM47*$BJ47*(1+($BL47-1)*AM$30)*($D$27*$BK47+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN71" s="18">
-        <f>IFERROR(AN49*$BJ49*(1+($BL49-1)*AN$30)*($D$27*$BK49+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN47*$BJ47*(1+($BL47-1)*AN$30)*($D$27*$BK47+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO71" s="18">
-        <f>IFERROR(AO49*$BJ49*(1+($BL49-1)*AO$30)*($D$27*$BK49+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO47*$BJ47*(1+($BL47-1)*AO$30)*($D$27*$BK47+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP71" s="18">
-        <f>IFERROR(AP49*$BJ49*(1+($BL49-1)*AP$30)*($D$27*$BK49+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP47*$BJ47*(1+($BL47-1)*AP$30)*($D$27*$BK47+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
       <c r="AQ71" s="18">
-        <f>IFERROR(AQ49*$BJ49*(1+($BL49-1)*AQ$30)*($D$27*$BK49+(1-$D$27)*AQ$29),"")</f>
+        <f>IFERROR(AQ47*$BJ47*(1+($BL47-1)*AQ$30)*($D$27*$BK47+(1-$D$27)*AQ$29),"")</f>
         <v/>
       </c>
       <c r="AR71" s="18">
-        <f>IFERROR(AR49*$BJ49*(1+($BL49-1)*AR$30)*($D$27*$BK49+(1-$D$27)*AR$29),"")</f>
+        <f>IFERROR(AR47*$BJ47*(1+($BL47-1)*AR$30)*($D$27*$BK47+(1-$D$27)*AR$29),"")</f>
         <v/>
       </c>
       <c r="AS71" s="18">
-        <f>IFERROR(AS49*$BJ49*(1+($BL49-1)*AS$30)*($D$27*$BK49+(1-$D$27)*AS$29),"")</f>
-        <v/>
-      </c>
-      <c r="AT71" s="18">
-        <f>IFERROR(AT49*$BJ49*(1+($BL49-1)*AT$30)*($D$27*$BK49+(1-$D$27)*AT$29),"")</f>
+        <f>IFERROR(AS47*$BJ47*(1+($BL47-1)*AS$30)*($D$27*$BK47+(1-$D$27)*AS$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260713800202</t>
+          <t>20260521800360</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -45706,1018 +45752,1077 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VLAC 3척</t>
-        </is>
+          <t>VLAC 6척</t>
+        </is>
+      </c>
+      <c r="AF72" s="18">
+        <f>IFERROR(AF48*$BJ48*(1+($BL48-1)*AF$30)*($D$27*$BK48+(1-$D$27)*AF$29),"")</f>
+        <v/>
       </c>
       <c r="AG72" s="18">
-        <f>IFERROR(AG50*$BJ50*(1+($BL50-1)*AG$30)*($D$27*$BK50+(1-$D$27)*AG$29),"")</f>
+        <f>IFERROR(AG48*$BJ48*(1+($BL48-1)*AG$30)*($D$27*$BK48+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
       <c r="AH72" s="18">
-        <f>IFERROR(AH50*$BJ50*(1+($BL50-1)*AH$30)*($D$27*$BK50+(1-$D$27)*AH$29),"")</f>
+        <f>IFERROR(AH48*$BJ48*(1+($BL48-1)*AH$30)*($D$27*$BK48+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
       <c r="AI72" s="18">
-        <f>IFERROR(AI50*$BJ50*(1+($BL50-1)*AI$30)*($D$27*$BK50+(1-$D$27)*AI$29),"")</f>
+        <f>IFERROR(AI48*$BJ48*(1+($BL48-1)*AI$30)*($D$27*$BK48+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
       <c r="AJ72" s="18">
-        <f>IFERROR(AJ50*$BJ50*(1+($BL50-1)*AJ$30)*($D$27*$BK50+(1-$D$27)*AJ$29),"")</f>
+        <f>IFERROR(AJ48*$BJ48*(1+($BL48-1)*AJ$30)*($D$27*$BK48+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
       <c r="AK72" s="18">
-        <f>IFERROR(AK50*$BJ50*(1+($BL50-1)*AK$30)*($D$27*$BK50+(1-$D$27)*AK$29),"")</f>
+        <f>IFERROR(AK48*$BJ48*(1+($BL48-1)*AK$30)*($D$27*$BK48+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
       <c r="AL72" s="18">
-        <f>IFERROR(AL50*$BJ50*(1+($BL50-1)*AL$30)*($D$27*$BK50+(1-$D$27)*AL$29),"")</f>
+        <f>IFERROR(AL48*$BJ48*(1+($BL48-1)*AL$30)*($D$27*$BK48+(1-$D$27)*AL$29),"")</f>
         <v/>
       </c>
       <c r="AM72" s="18">
-        <f>IFERROR(AM50*$BJ50*(1+($BL50-1)*AM$30)*($D$27*$BK50+(1-$D$27)*AM$29),"")</f>
+        <f>IFERROR(AM48*$BJ48*(1+($BL48-1)*AM$30)*($D$27*$BK48+(1-$D$27)*AM$29),"")</f>
         <v/>
       </c>
       <c r="AN72" s="18">
-        <f>IFERROR(AN50*$BJ50*(1+($BL50-1)*AN$30)*($D$27*$BK50+(1-$D$27)*AN$29),"")</f>
+        <f>IFERROR(AN48*$BJ48*(1+($BL48-1)*AN$30)*($D$27*$BK48+(1-$D$27)*AN$29),"")</f>
         <v/>
       </c>
       <c r="AO72" s="18">
-        <f>IFERROR(AO50*$BJ50*(1+($BL50-1)*AO$30)*($D$27*$BK50+(1-$D$27)*AO$29),"")</f>
+        <f>IFERROR(AO48*$BJ48*(1+($BL48-1)*AO$30)*($D$27*$BK48+(1-$D$27)*AO$29),"")</f>
         <v/>
       </c>
       <c r="AP72" s="18">
-        <f>IFERROR(AP50*$BJ50*(1+($BL50-1)*AP$30)*($D$27*$BK50+(1-$D$27)*AP$29),"")</f>
+        <f>IFERROR(AP48*$BJ48*(1+($BL48-1)*AP$30)*($D$27*$BK48+(1-$D$27)*AP$29),"")</f>
         <v/>
       </c>
       <c r="AQ72" s="18">
-        <f>IFERROR(AQ50*$BJ50*(1+($BL50-1)*AQ$30)*($D$27*$BK50+(1-$D$27)*AQ$29),"")</f>
+        <f>IFERROR(AQ48*$BJ48*(1+($BL48-1)*AQ$30)*($D$27*$BK48+(1-$D$27)*AQ$29),"")</f>
         <v/>
       </c>
       <c r="AR72" s="18">
-        <f>IFERROR(AR50*$BJ50*(1+($BL50-1)*AR$30)*($D$27*$BK50+(1-$D$27)*AR$29),"")</f>
+        <f>IFERROR(AR48*$BJ48*(1+($BL48-1)*AR$30)*($D$27*$BK48+(1-$D$27)*AR$29),"")</f>
         <v/>
       </c>
       <c r="AS72" s="18">
-        <f>IFERROR(AS50*$BJ50*(1+($BL50-1)*AS$30)*($D$27*$BK50+(1-$D$27)*AS$29),"")</f>
+        <f>IFERROR(AS48*$BJ48*(1+($BL48-1)*AS$30)*($D$27*$BK48+(1-$D$27)*AS$29),"")</f>
         <v/>
       </c>
       <c r="AT72" s="18">
-        <f>IFERROR(AT50*$BJ50*(1+($BL50-1)*AT$30)*($D$27*$BK50+(1-$D$27)*AT$29),"")</f>
-        <v/>
-      </c>
-      <c r="AU72" s="18">
-        <f>IFERROR(AU50*$BJ50*(1+($BL50-1)*AU$30)*($D$27*$BK50+(1-$D$27)*AU$29),"")</f>
-        <v/>
-      </c>
-      <c r="AV72" s="18">
-        <f>IFERROR(AV50*$BJ50*(1+($BL50-1)*AV$30)*($D$27*$BK50+(1-$D$27)*AV$29),"")</f>
+        <f>IFERROR(AT48*$BJ48*(1+($BL48-1)*AT$30)*($D$27*$BK48+(1-$D$27)*AT$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260903800523</t>
+          <t>20260629800351</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OFFSH</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FPSO Hull 1기</t>
-        </is>
-      </c>
-      <c r="L73" s="18">
-        <f>IFERROR(L51*$BJ51*(1+($BL51-1)*L$30)*($D$27*$BK51+(1-$D$27)*L$29),"")</f>
-        <v/>
-      </c>
-      <c r="M73" s="18">
-        <f>IFERROR(M51*$BJ51*(1+($BL51-1)*M$30)*($D$27*$BK51+(1-$D$27)*M$29),"")</f>
-        <v/>
-      </c>
-      <c r="N73" s="18">
-        <f>IFERROR(N51*$BJ51*(1+($BL51-1)*N$30)*($D$27*$BK51+(1-$D$27)*N$29),"")</f>
-        <v/>
-      </c>
-      <c r="O73" s="18">
-        <f>IFERROR(O51*$BJ51*(1+($BL51-1)*O$30)*($D$27*$BK51+(1-$D$27)*O$29),"")</f>
-        <v/>
-      </c>
-      <c r="P73" s="18">
-        <f>IFERROR(P51*$BJ51*(1+($BL51-1)*P$30)*($D$27*$BK51+(1-$D$27)*P$29),"")</f>
-        <v/>
-      </c>
-      <c r="Q73" s="18">
-        <f>IFERROR(Q51*$BJ51*(1+($BL51-1)*Q$30)*($D$27*$BK51+(1-$D$27)*Q$29),"")</f>
-        <v/>
-      </c>
-      <c r="R73" s="18">
-        <f>IFERROR(R51*$BJ51*(1+($BL51-1)*R$30)*($D$27*$BK51+(1-$D$27)*R$29),"")</f>
-        <v/>
-      </c>
-      <c r="S73" s="18">
-        <f>IFERROR(S51*$BJ51*(1+($BL51-1)*S$30)*($D$27*$BK51+(1-$D$27)*S$29),"")</f>
-        <v/>
-      </c>
-      <c r="T73" s="18">
-        <f>IFERROR(T51*$BJ51*(1+($BL51-1)*T$30)*($D$27*$BK51+(1-$D$27)*T$29),"")</f>
-        <v/>
-      </c>
-      <c r="U73" s="18">
-        <f>IFERROR(U51*$BJ51*(1+($BL51-1)*U$30)*($D$27*$BK51+(1-$D$27)*U$29),"")</f>
-        <v/>
-      </c>
-      <c r="V73" s="18">
-        <f>IFERROR(V51*$BJ51*(1+($BL51-1)*V$30)*($D$27*$BK51+(1-$D$27)*V$29),"")</f>
-        <v/>
-      </c>
-      <c r="W73" s="18">
-        <f>IFERROR(W51*$BJ51*(1+($BL51-1)*W$30)*($D$27*$BK51+(1-$D$27)*W$29),"")</f>
-        <v/>
-      </c>
-      <c r="X73" s="18">
-        <f>IFERROR(X51*$BJ51*(1+($BL51-1)*X$30)*($D$27*$BK51+(1-$D$27)*X$29),"")</f>
-        <v/>
-      </c>
-      <c r="Y73" s="18">
-        <f>IFERROR(Y51*$BJ51*(1+($BL51-1)*Y$30)*($D$27*$BK51+(1-$D$27)*Y$29),"")</f>
-        <v/>
-      </c>
-      <c r="Z73" s="18">
-        <f>IFERROR(Z51*$BJ51*(1+($BL51-1)*Z$30)*($D$27*$BK51+(1-$D$27)*Z$29),"")</f>
-        <v/>
-      </c>
-      <c r="AA73" s="18">
-        <f>IFERROR(AA51*$BJ51*(1+($BL51-1)*AA$30)*($D$27*$BK51+(1-$D$27)*AA$29),"")</f>
-        <v/>
-      </c>
-      <c r="AB73" s="18">
-        <f>IFERROR(AB51*$BJ51*(1+($BL51-1)*AB$30)*($D$27*$BK51+(1-$D$27)*AB$29),"")</f>
+          <t>LPGC 2척</t>
+        </is>
+      </c>
+      <c r="AF73" s="18">
+        <f>IFERROR(AF49*$BJ49*(1+($BL49-1)*AF$30)*($D$27*$BK49+(1-$D$27)*AF$29),"")</f>
+        <v/>
+      </c>
+      <c r="AG73" s="18">
+        <f>IFERROR(AG49*$BJ49*(1+($BL49-1)*AG$30)*($D$27*$BK49+(1-$D$27)*AG$29),"")</f>
+        <v/>
+      </c>
+      <c r="AH73" s="18">
+        <f>IFERROR(AH49*$BJ49*(1+($BL49-1)*AH$30)*($D$27*$BK49+(1-$D$27)*AH$29),"")</f>
+        <v/>
+      </c>
+      <c r="AI73" s="18">
+        <f>IFERROR(AI49*$BJ49*(1+($BL49-1)*AI$30)*($D$27*$BK49+(1-$D$27)*AI$29),"")</f>
+        <v/>
+      </c>
+      <c r="AJ73" s="18">
+        <f>IFERROR(AJ49*$BJ49*(1+($BL49-1)*AJ$30)*($D$27*$BK49+(1-$D$27)*AJ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AK73" s="18">
+        <f>IFERROR(AK49*$BJ49*(1+($BL49-1)*AK$30)*($D$27*$BK49+(1-$D$27)*AK$29),"")</f>
+        <v/>
+      </c>
+      <c r="AL73" s="18">
+        <f>IFERROR(AL49*$BJ49*(1+($BL49-1)*AL$30)*($D$27*$BK49+(1-$D$27)*AL$29),"")</f>
+        <v/>
+      </c>
+      <c r="AM73" s="18">
+        <f>IFERROR(AM49*$BJ49*(1+($BL49-1)*AM$30)*($D$27*$BK49+(1-$D$27)*AM$29),"")</f>
+        <v/>
+      </c>
+      <c r="AN73" s="18">
+        <f>IFERROR(AN49*$BJ49*(1+($BL49-1)*AN$30)*($D$27*$BK49+(1-$D$27)*AN$29),"")</f>
+        <v/>
+      </c>
+      <c r="AO73" s="18">
+        <f>IFERROR(AO49*$BJ49*(1+($BL49-1)*AO$30)*($D$27*$BK49+(1-$D$27)*AO$29),"")</f>
+        <v/>
+      </c>
+      <c r="AP73" s="18">
+        <f>IFERROR(AP49*$BJ49*(1+($BL49-1)*AP$30)*($D$27*$BK49+(1-$D$27)*AP$29),"")</f>
+        <v/>
+      </c>
+      <c r="AQ73" s="18">
+        <f>IFERROR(AQ49*$BJ49*(1+($BL49-1)*AQ$30)*($D$27*$BK49+(1-$D$27)*AQ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AR73" s="18">
+        <f>IFERROR(AR49*$BJ49*(1+($BL49-1)*AR$30)*($D$27*$BK49+(1-$D$27)*AR$29),"")</f>
+        <v/>
+      </c>
+      <c r="AS73" s="18">
+        <f>IFERROR(AS49*$BJ49*(1+($BL49-1)*AS$30)*($D$27*$BK49+(1-$D$27)*AS$29),"")</f>
+        <v/>
+      </c>
+      <c r="AT73" s="18">
+        <f>IFERROR(AT49*$BJ49*(1+($BL49-1)*AT$30)*($D$27*$BK49+(1-$D$27)*AT$29),"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>20260713800202</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VLAC 3척</t>
+        </is>
+      </c>
+      <c r="AG74" s="18">
+        <f>IFERROR(AG50*$BJ50*(1+($BL50-1)*AG$30)*($D$27*$BK50+(1-$D$27)*AG$29),"")</f>
+        <v/>
+      </c>
+      <c r="AH74" s="18">
+        <f>IFERROR(AH50*$BJ50*(1+($BL50-1)*AH$30)*($D$27*$BK50+(1-$D$27)*AH$29),"")</f>
+        <v/>
+      </c>
+      <c r="AI74" s="18">
+        <f>IFERROR(AI50*$BJ50*(1+($BL50-1)*AI$30)*($D$27*$BK50+(1-$D$27)*AI$29),"")</f>
+        <v/>
+      </c>
+      <c r="AJ74" s="18">
+        <f>IFERROR(AJ50*$BJ50*(1+($BL50-1)*AJ$30)*($D$27*$BK50+(1-$D$27)*AJ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AK74" s="18">
+        <f>IFERROR(AK50*$BJ50*(1+($BL50-1)*AK$30)*($D$27*$BK50+(1-$D$27)*AK$29),"")</f>
+        <v/>
+      </c>
+      <c r="AL74" s="18">
+        <f>IFERROR(AL50*$BJ50*(1+($BL50-1)*AL$30)*($D$27*$BK50+(1-$D$27)*AL$29),"")</f>
+        <v/>
+      </c>
+      <c r="AM74" s="18">
+        <f>IFERROR(AM50*$BJ50*(1+($BL50-1)*AM$30)*($D$27*$BK50+(1-$D$27)*AM$29),"")</f>
+        <v/>
+      </c>
+      <c r="AN74" s="18">
+        <f>IFERROR(AN50*$BJ50*(1+($BL50-1)*AN$30)*($D$27*$BK50+(1-$D$27)*AN$29),"")</f>
+        <v/>
+      </c>
+      <c r="AO74" s="18">
+        <f>IFERROR(AO50*$BJ50*(1+($BL50-1)*AO$30)*($D$27*$BK50+(1-$D$27)*AO$29),"")</f>
+        <v/>
+      </c>
+      <c r="AP74" s="18">
+        <f>IFERROR(AP50*$BJ50*(1+($BL50-1)*AP$30)*($D$27*$BK50+(1-$D$27)*AP$29),"")</f>
+        <v/>
+      </c>
+      <c r="AQ74" s="18">
+        <f>IFERROR(AQ50*$BJ50*(1+($BL50-1)*AQ$30)*($D$27*$BK50+(1-$D$27)*AQ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AR74" s="18">
+        <f>IFERROR(AR50*$BJ50*(1+($BL50-1)*AR$30)*($D$27*$BK50+(1-$D$27)*AR$29),"")</f>
+        <v/>
+      </c>
+      <c r="AS74" s="18">
+        <f>IFERROR(AS50*$BJ50*(1+($BL50-1)*AS$30)*($D$27*$BK50+(1-$D$27)*AS$29),"")</f>
+        <v/>
+      </c>
+      <c r="AT74" s="18">
+        <f>IFERROR(AT50*$BJ50*(1+($BL50-1)*AT$30)*($D$27*$BK50+(1-$D$27)*AT$29),"")</f>
+        <v/>
+      </c>
+      <c r="AU74" s="18">
+        <f>IFERROR(AU50*$BJ50*(1+($BL50-1)*AU$30)*($D$27*$BK50+(1-$D$27)*AU$29),"")</f>
+        <v/>
+      </c>
+      <c r="AV74" s="18">
+        <f>IFERROR(AV50*$BJ50*(1+($BL50-1)*AV$30)*($D$27*$BK50+(1-$D$27)*AV$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260903800523</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>FPSO Hull 1기</t>
+        </is>
+      </c>
+      <c r="L75" s="18">
+        <f>IFERROR(L51*$BJ51*(1+($BL51-1)*L$30)*($D$27*$BK51+(1-$D$27)*L$29),"")</f>
+        <v/>
+      </c>
+      <c r="M75" s="18">
+        <f>IFERROR(M51*$BJ51*(1+($BL51-1)*M$30)*($D$27*$BK51+(1-$D$27)*M$29),"")</f>
+        <v/>
+      </c>
+      <c r="N75" s="18">
+        <f>IFERROR(N51*$BJ51*(1+($BL51-1)*N$30)*($D$27*$BK51+(1-$D$27)*N$29),"")</f>
+        <v/>
+      </c>
+      <c r="O75" s="18">
+        <f>IFERROR(O51*$BJ51*(1+($BL51-1)*O$30)*($D$27*$BK51+(1-$D$27)*O$29),"")</f>
+        <v/>
+      </c>
+      <c r="P75" s="18">
+        <f>IFERROR(P51*$BJ51*(1+($BL51-1)*P$30)*($D$27*$BK51+(1-$D$27)*P$29),"")</f>
+        <v/>
+      </c>
+      <c r="Q75" s="18">
+        <f>IFERROR(Q51*$BJ51*(1+($BL51-1)*Q$30)*($D$27*$BK51+(1-$D$27)*Q$29),"")</f>
+        <v/>
+      </c>
+      <c r="R75" s="18">
+        <f>IFERROR(R51*$BJ51*(1+($BL51-1)*R$30)*($D$27*$BK51+(1-$D$27)*R$29),"")</f>
+        <v/>
+      </c>
+      <c r="S75" s="18">
+        <f>IFERROR(S51*$BJ51*(1+($BL51-1)*S$30)*($D$27*$BK51+(1-$D$27)*S$29),"")</f>
+        <v/>
+      </c>
+      <c r="T75" s="18">
+        <f>IFERROR(T51*$BJ51*(1+($BL51-1)*T$30)*($D$27*$BK51+(1-$D$27)*T$29),"")</f>
+        <v/>
+      </c>
+      <c r="U75" s="18">
+        <f>IFERROR(U51*$BJ51*(1+($BL51-1)*U$30)*($D$27*$BK51+(1-$D$27)*U$29),"")</f>
+        <v/>
+      </c>
+      <c r="V75" s="18">
+        <f>IFERROR(V51*$BJ51*(1+($BL51-1)*V$30)*($D$27*$BK51+(1-$D$27)*V$29),"")</f>
+        <v/>
+      </c>
+      <c r="W75" s="18">
+        <f>IFERROR(W51*$BJ51*(1+($BL51-1)*W$30)*($D$27*$BK51+(1-$D$27)*W$29),"")</f>
+        <v/>
+      </c>
+      <c r="X75" s="18">
+        <f>IFERROR(X51*$BJ51*(1+($BL51-1)*X$30)*($D$27*$BK51+(1-$D$27)*X$29),"")</f>
+        <v/>
+      </c>
+      <c r="Y75" s="18">
+        <f>IFERROR(Y51*$BJ51*(1+($BL51-1)*Y$30)*($D$27*$BK51+(1-$D$27)*Y$29),"")</f>
+        <v/>
+      </c>
+      <c r="Z75" s="18">
+        <f>IFERROR(Z51*$BJ51*(1+($BL51-1)*Z$30)*($D$27*$BK51+(1-$D$27)*Z$29),"")</f>
+        <v/>
+      </c>
+      <c r="AA75" s="18">
+        <f>IFERROR(AA51*$BJ51*(1+($BL51-1)*AA$30)*($D$27*$BK51+(1-$D$27)*AA$29),"")</f>
+        <v/>
+      </c>
+      <c r="AB75" s="18">
+        <f>IFERROR(AB51*$BJ51*(1+($BL51-1)*AB$30)*($D$27*$BK51+(1-$D$27)*AB$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>20261006800410</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>보령화력 1~8호기 저탄장 옥내화 공사</t>
         </is>
       </c>
-      <c r="M74" s="18">
+      <c r="M76" s="18">
         <f>IFERROR(M52*$BJ52*(1+($BL52-1)*M$30)*($D$27*$BK52+(1-$D$27)*M$29),"")</f>
         <v/>
       </c>
-      <c r="N74" s="18">
+      <c r="N76" s="18">
         <f>IFERROR(N52*$BJ52*(1+($BL52-1)*N$30)*($D$27*$BK52+(1-$D$27)*N$29),"")</f>
         <v/>
       </c>
-      <c r="O74" s="18">
+      <c r="O76" s="18">
         <f>IFERROR(O52*$BJ52*(1+($BL52-1)*O$30)*($D$27*$BK52+(1-$D$27)*O$29),"")</f>
         <v/>
       </c>
-      <c r="P74" s="18">
+      <c r="P76" s="18">
         <f>IFERROR(P52*$BJ52*(1+($BL52-1)*P$30)*($D$27*$BK52+(1-$D$27)*P$29),"")</f>
         <v/>
       </c>
-      <c r="Q74" s="18">
+      <c r="Q76" s="18">
         <f>IFERROR(Q52*$BJ52*(1+($BL52-1)*Q$30)*($D$27*$BK52+(1-$D$27)*Q$29),"")</f>
         <v/>
       </c>
-      <c r="R74" s="18">
+      <c r="R76" s="18">
         <f>IFERROR(R52*$BJ52*(1+($BL52-1)*R$30)*($D$27*$BK52+(1-$D$27)*R$29),"")</f>
         <v/>
       </c>
-      <c r="S74" s="18">
+      <c r="S76" s="18">
         <f>IFERROR(S52*$BJ52*(1+($BL52-1)*S$30)*($D$27*$BK52+(1-$D$27)*S$29),"")</f>
         <v/>
       </c>
-      <c r="T74" s="18">
+      <c r="T76" s="18">
         <f>IFERROR(T52*$BJ52*(1+($BL52-1)*T$30)*($D$27*$BK52+(1-$D$27)*T$29),"")</f>
         <v/>
       </c>
-      <c r="U74" s="18">
+      <c r="U76" s="18">
         <f>IFERROR(U52*$BJ52*(1+($BL52-1)*U$30)*($D$27*$BK52+(1-$D$27)*U$29),"")</f>
         <v/>
       </c>
-      <c r="V74" s="18">
+      <c r="V76" s="18">
         <f>IFERROR(V52*$BJ52*(1+($BL52-1)*V$30)*($D$27*$BK52+(1-$D$27)*V$29),"")</f>
         <v/>
       </c>
-      <c r="W74" s="18">
+      <c r="W76" s="18">
         <f>IFERROR(W52*$BJ52*(1+($BL52-1)*W$30)*($D$27*$BK52+(1-$D$27)*W$29),"")</f>
         <v/>
       </c>
-      <c r="X74" s="18">
+      <c r="X76" s="18">
         <f>IFERROR(X52*$BJ52*(1+($BL52-1)*X$30)*($D$27*$BK52+(1-$D$27)*X$29),"")</f>
         <v/>
       </c>
-      <c r="Y74" s="18">
+      <c r="Y76" s="18">
         <f>IFERROR(Y52*$BJ52*(1+($BL52-1)*Y$30)*($D$27*$BK52+(1-$D$27)*Y$29),"")</f>
         <v/>
       </c>
-      <c r="Z74" s="18">
+      <c r="Z76" s="18">
         <f>IFERROR(Z52*$BJ52*(1+($BL52-1)*Z$30)*($D$27*$BK52+(1-$D$27)*Z$29),"")</f>
         <v/>
       </c>
-      <c r="AA74" s="18">
+      <c r="AA76" s="18">
         <f>IFERROR(AA52*$BJ52*(1+($BL52-1)*AA$30)*($D$27*$BK52+(1-$D$27)*AA$29),"")</f>
         <v/>
       </c>
-      <c r="AB74" s="18">
+      <c r="AB76" s="18">
         <f>IFERROR(AB52*$BJ52*(1+($BL52-1)*AB$30)*($D$27*$BK52+(1-$D$27)*AB$29),"")</f>
         <v/>
       </c>
-      <c r="AC74" s="18">
+      <c r="AC76" s="18">
         <f>IFERROR(AC52*$BJ52*(1+($BL52-1)*AC$30)*($D$27*$BK52+(1-$D$27)*AC$29),"")</f>
         <v/>
       </c>
-      <c r="AD74" s="18">
+      <c r="AD76" s="18">
         <f>IFERROR(AD52*$BJ52*(1+($BL52-1)*AD$30)*($D$27*$BK52+(1-$D$27)*AD$29),"")</f>
         <v/>
       </c>
-      <c r="AE74" s="18">
+      <c r="AE76" s="18">
         <f>IFERROR(AE52*$BJ52*(1+($BL52-1)*AE$30)*($D$27*$BK52+(1-$D$27)*AE$29),"")</f>
         <v/>
       </c>
-      <c r="AF74" s="18">
+      <c r="AF76" s="18">
         <f>IFERROR(AF52*$BJ52*(1+($BL52-1)*AF$30)*($D$27*$BK52+(1-$D$27)*AF$29),"")</f>
         <v/>
       </c>
-      <c r="AG74" s="18">
+      <c r="AG76" s="18">
         <f>IFERROR(AG52*$BJ52*(1+($BL52-1)*AG$30)*($D$27*$BK52+(1-$D$27)*AG$29),"")</f>
         <v/>
       </c>
-      <c r="AH74" s="18">
+      <c r="AH76" s="18">
         <f>IFERROR(AH52*$BJ52*(1+($BL52-1)*AH$30)*($D$27*$BK52+(1-$D$27)*AH$29),"")</f>
         <v/>
       </c>
-      <c r="AI74" s="18">
+      <c r="AI76" s="18">
         <f>IFERROR(AI52*$BJ52*(1+($BL52-1)*AI$30)*($D$27*$BK52+(1-$D$27)*AI$29),"")</f>
         <v/>
       </c>
-      <c r="AJ74" s="18">
+      <c r="AJ76" s="18">
         <f>IFERROR(AJ52*$BJ52*(1+($BL52-1)*AJ$30)*($D$27*$BK52+(1-$D$27)*AJ$29),"")</f>
         <v/>
       </c>
-      <c r="AK74" s="18">
+      <c r="AK76" s="18">
         <f>IFERROR(AK52*$BJ52*(1+($BL52-1)*AK$30)*($D$27*$BK52+(1-$D$27)*AK$29),"")</f>
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20261020800226</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>컨테이너선 6척</t>
+        </is>
+      </c>
+      <c r="AH77" s="18">
+        <f>IFERROR(AH53*$BJ53*(1+($BL53-1)*AH$30)*($D$27*$BK53+(1-$D$27)*AH$29),"")</f>
+        <v/>
+      </c>
+      <c r="AI77" s="18">
+        <f>IFERROR(AI53*$BJ53*(1+($BL53-1)*AI$30)*($D$27*$BK53+(1-$D$27)*AI$29),"")</f>
+        <v/>
+      </c>
+      <c r="AJ77" s="18">
+        <f>IFERROR(AJ53*$BJ53*(1+($BL53-1)*AJ$30)*($D$27*$BK53+(1-$D$27)*AJ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AK77" s="18">
+        <f>IFERROR(AK53*$BJ53*(1+($BL53-1)*AK$30)*($D$27*$BK53+(1-$D$27)*AK$29),"")</f>
+        <v/>
+      </c>
+      <c r="AL77" s="18">
+        <f>IFERROR(AL53*$BJ53*(1+($BL53-1)*AL$30)*($D$27*$BK53+(1-$D$27)*AL$29),"")</f>
+        <v/>
+      </c>
+      <c r="AM77" s="18">
+        <f>IFERROR(AM53*$BJ53*(1+($BL53-1)*AM$30)*($D$27*$BK53+(1-$D$27)*AM$29),"")</f>
+        <v/>
+      </c>
+      <c r="AN77" s="18">
+        <f>IFERROR(AN53*$BJ53*(1+($BL53-1)*AN$30)*($D$27*$BK53+(1-$D$27)*AN$29),"")</f>
+        <v/>
+      </c>
+      <c r="AO77" s="18">
+        <f>IFERROR(AO53*$BJ53*(1+($BL53-1)*AO$30)*($D$27*$BK53+(1-$D$27)*AO$29),"")</f>
+        <v/>
+      </c>
+      <c r="AP77" s="18">
+        <f>IFERROR(AP53*$BJ53*(1+($BL53-1)*AP$30)*($D$27*$BK53+(1-$D$27)*AP$29),"")</f>
+        <v/>
+      </c>
+      <c r="AQ77" s="18">
+        <f>IFERROR(AQ53*$BJ53*(1+($BL53-1)*AQ$30)*($D$27*$BK53+(1-$D$27)*AQ$29),"")</f>
+        <v/>
+      </c>
+      <c r="AR77" s="18">
+        <f>IFERROR(AR53*$BJ53*(1+($BL53-1)*AR$30)*($D$27*$BK53+(1-$D$27)*AR$29),"")</f>
+        <v/>
+      </c>
+      <c r="AS77" s="18">
+        <f>IFERROR(AS53*$BJ53*(1+($BL53-1)*AS$30)*($D$27*$BK53+(1-$D$27)*AS$29),"")</f>
+        <v/>
+      </c>
+      <c r="AT77" s="18">
+        <f>IFERROR(AT53*$BJ53*(1+($BL53-1)*AT$30)*($D$27*$BK53+(1-$D$27)*AT$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20261021800379</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>컨테이너선 2척</t>
+        </is>
+      </c>
+      <c r="Z78" s="18">
+        <f>IFERROR(Z54*$BJ54*(1+($BL54-1)*Z$30)*($D$27*$BK54+(1-$D$27)*Z$29),"")</f>
+        <v/>
+      </c>
+      <c r="AA78" s="18">
+        <f>IFERROR(AA54*$BJ54*(1+($BL54-1)*AA$30)*($D$27*$BK54+(1-$D$27)*AA$29),"")</f>
+        <v/>
+      </c>
+      <c r="AB78" s="18">
+        <f>IFERROR(AB54*$BJ54*(1+($BL54-1)*AB$30)*($D$27*$BK54+(1-$D$27)*AB$29),"")</f>
+        <v/>
+      </c>
+      <c r="AC78" s="18">
+        <f>IFERROR(AC54*$BJ54*(1+($BL54-1)*AC$30)*($D$27*$BK54+(1-$D$27)*AC$29),"")</f>
+        <v/>
+      </c>
+      <c r="AD78" s="18">
+        <f>IFERROR(AD54*$BJ54*(1+($BL54-1)*AD$30)*($D$27*$BK54+(1-$D$27)*AD$29),"")</f>
+        <v/>
+      </c>
+      <c r="AE78" s="18">
+        <f>IFERROR(AE54*$BJ54*(1+($BL54-1)*AE$30)*($D$27*$BK54+(1-$D$27)*AE$29),"")</f>
+        <v/>
+      </c>
+      <c r="AF78" s="18">
+        <f>IFERROR(AF54*$BJ54*(1+($BL54-1)*AF$30)*($D$27*$BK54+(1-$D$27)*AF$29),"")</f>
+        <v/>
+      </c>
+      <c r="AG78" s="18">
+        <f>IFERROR(AG54*$BJ54*(1+($BL54-1)*AG$30)*($D$27*$BK54+(1-$D$27)*AG$29),"")</f>
+        <v/>
+      </c>
+      <c r="AH78" s="18">
+        <f>IFERROR(AH54*$BJ54*(1+($BL54-1)*AH$30)*($D$27*$BK54+(1-$D$27)*AH$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>usd_incl</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>포함 계약 스케줄 합(백만$, 캡 배율 전)</t>
         </is>
       </c>
-      <c r="E75" s="27">
-        <f>SUMPRODUCT(E33:E52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="F75" s="27">
-        <f>SUMPRODUCT(F33:F52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="G75" s="27">
-        <f>SUMPRODUCT(G33:G52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="H75" s="27">
-        <f>SUMPRODUCT(H33:H52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="I75" s="27">
-        <f>SUMPRODUCT(I33:I52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="J75" s="27">
-        <f>SUMPRODUCT(J33:J52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="K75" s="27">
-        <f>SUMPRODUCT(K33:K52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="L75" s="27">
-        <f>SUMPRODUCT(L33:L52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="M75" s="27">
-        <f>SUMPRODUCT(M33:M52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="N75" s="27">
-        <f>SUMPRODUCT(N33:N52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="O75" s="27">
-        <f>SUMPRODUCT(O33:O52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="P75" s="27">
-        <f>SUMPRODUCT(P33:P52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="Q75" s="27">
-        <f>SUMPRODUCT(Q33:Q52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="R75" s="27">
-        <f>SUMPRODUCT(R33:R52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="S75" s="27">
-        <f>SUMPRODUCT(S33:S52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="T75" s="27">
-        <f>SUMPRODUCT(T33:T52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="U75" s="27">
-        <f>SUMPRODUCT(U33:U52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="V75" s="27">
-        <f>SUMPRODUCT(V33:V52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="W75" s="27">
-        <f>SUMPRODUCT(W33:W52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="X75" s="27">
-        <f>SUMPRODUCT(X33:X52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="Y75" s="27">
-        <f>SUMPRODUCT(Y33:Y52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="Z75" s="27">
-        <f>SUMPRODUCT(Z33:Z52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AA75" s="27">
-        <f>SUMPRODUCT(AA33:AA52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AB75" s="27">
-        <f>SUMPRODUCT(AB33:AB52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AC75" s="27">
-        <f>SUMPRODUCT(AC33:AC52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AD75" s="27">
-        <f>SUMPRODUCT(AD33:AD52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AE75" s="27">
-        <f>SUMPRODUCT(AE33:AE52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AF75" s="27">
-        <f>SUMPRODUCT(AF33:AF52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AG75" s="27">
-        <f>SUMPRODUCT(AG33:AG52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AH75" s="27">
-        <f>SUMPRODUCT(AH33:AH52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AI75" s="27">
-        <f>SUMPRODUCT(AI33:AI52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AJ75" s="27">
-        <f>SUMPRODUCT(AJ33:AJ52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AK75" s="27">
-        <f>SUMPRODUCT(AK33:AK52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AL75" s="27">
-        <f>SUMPRODUCT(AL33:AL52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AM75" s="27">
-        <f>SUMPRODUCT(AM33:AM52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AN75" s="27">
-        <f>SUMPRODUCT(AN33:AN52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AO75" s="27">
-        <f>SUMPRODUCT(AO33:AO52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AP75" s="27">
-        <f>SUMPRODUCT(AP33:AP52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AQ75" s="27">
-        <f>SUMPRODUCT(AQ33:AQ52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AR75" s="27">
-        <f>SUMPRODUCT(AR33:AR52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AS75" s="27">
-        <f>SUMPRODUCT(AS33:AS52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AT75" s="27">
-        <f>SUMPRODUCT(AT33:AT52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AU75" s="27">
-        <f>SUMPRODUCT(AU33:AU52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-      <c r="AV75" s="27">
-        <f>SUMPRODUCT(AV33:AV52,$BJ$33:$BJ$52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="E79" s="27">
+        <f>SUMPRODUCT(E33:E54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="F79" s="27">
+        <f>SUMPRODUCT(F33:F54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="G79" s="27">
+        <f>SUMPRODUCT(G33:G54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="H79" s="27">
+        <f>SUMPRODUCT(H33:H54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="I79" s="27">
+        <f>SUMPRODUCT(I33:I54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="J79" s="27">
+        <f>SUMPRODUCT(J33:J54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="K79" s="27">
+        <f>SUMPRODUCT(K33:K54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="L79" s="27">
+        <f>SUMPRODUCT(L33:L54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="M79" s="27">
+        <f>SUMPRODUCT(M33:M54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="N79" s="27">
+        <f>SUMPRODUCT(N33:N54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="O79" s="27">
+        <f>SUMPRODUCT(O33:O54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="P79" s="27">
+        <f>SUMPRODUCT(P33:P54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="Q79" s="27">
+        <f>SUMPRODUCT(Q33:Q54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="R79" s="27">
+        <f>SUMPRODUCT(R33:R54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="S79" s="27">
+        <f>SUMPRODUCT(S33:S54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="T79" s="27">
+        <f>SUMPRODUCT(T33:T54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="U79" s="27">
+        <f>SUMPRODUCT(U33:U54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="V79" s="27">
+        <f>SUMPRODUCT(V33:V54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="W79" s="27">
+        <f>SUMPRODUCT(W33:W54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="X79" s="27">
+        <f>SUMPRODUCT(X33:X54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="Y79" s="27">
+        <f>SUMPRODUCT(Y33:Y54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="Z79" s="27">
+        <f>SUMPRODUCT(Z33:Z54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AA79" s="27">
+        <f>SUMPRODUCT(AA33:AA54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AB79" s="27">
+        <f>SUMPRODUCT(AB33:AB54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AC79" s="27">
+        <f>SUMPRODUCT(AC33:AC54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AD79" s="27">
+        <f>SUMPRODUCT(AD33:AD54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AE79" s="27">
+        <f>SUMPRODUCT(AE33:AE54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AF79" s="27">
+        <f>SUMPRODUCT(AF33:AF54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AG79" s="27">
+        <f>SUMPRODUCT(AG33:AG54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AH79" s="27">
+        <f>SUMPRODUCT(AH33:AH54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AI79" s="27">
+        <f>SUMPRODUCT(AI33:AI54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AJ79" s="27">
+        <f>SUMPRODUCT(AJ33:AJ54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AK79" s="27">
+        <f>SUMPRODUCT(AK33:AK54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AL79" s="27">
+        <f>SUMPRODUCT(AL33:AL54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AM79" s="27">
+        <f>SUMPRODUCT(AM33:AM54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AN79" s="27">
+        <f>SUMPRODUCT(AN33:AN54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AO79" s="27">
+        <f>SUMPRODUCT(AO33:AO54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AP79" s="27">
+        <f>SUMPRODUCT(AP33:AP54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AQ79" s="27">
+        <f>SUMPRODUCT(AQ33:AQ54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AR79" s="27">
+        <f>SUMPRODUCT(AR33:AR54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AS79" s="27">
+        <f>SUMPRODUCT(AS33:AS54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AT79" s="27">
+        <f>SUMPRODUCT(AT33:AT54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AU79" s="27">
+        <f>SUMPRODUCT(AU33:AU54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+      <c r="AV79" s="27">
+        <f>SUMPRODUCT(AV33:AV54,$BJ$33:$BJ$54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>krw_link</t>
         </is>
       </c>
-      <c r="D76" s="1" t="inlineStr">
+      <c r="D80" s="1" t="inlineStr">
         <is>
           <t>원화 합계(백만원) — subQ 연결 행</t>
         </is>
       </c>
-      <c r="E76" s="18">
-        <f>SUM(E55:E74)</f>
-        <v/>
-      </c>
-      <c r="F76" s="18">
-        <f>SUM(F55:F74)</f>
-        <v/>
-      </c>
-      <c r="G76" s="18">
-        <f>SUM(G55:G74)</f>
-        <v/>
-      </c>
-      <c r="H76" s="18">
-        <f>SUM(H55:H74)</f>
-        <v/>
-      </c>
-      <c r="I76" s="18">
-        <f>SUM(I55:I74)</f>
-        <v/>
-      </c>
-      <c r="J76" s="18">
-        <f>SUM(J55:J74)</f>
-        <v/>
-      </c>
-      <c r="K76" s="18">
-        <f>SUM(K55:K74)</f>
-        <v/>
-      </c>
-      <c r="L76" s="18">
-        <f>SUM(L55:L74)</f>
-        <v/>
-      </c>
-      <c r="M76" s="18">
-        <f>SUM(M55:M74)</f>
-        <v/>
-      </c>
-      <c r="N76" s="18">
-        <f>SUM(N55:N74)</f>
-        <v/>
-      </c>
-      <c r="O76" s="18">
-        <f>SUM(O55:O74)</f>
-        <v/>
-      </c>
-      <c r="P76" s="18">
-        <f>SUM(P55:P74)</f>
-        <v/>
-      </c>
-      <c r="Q76" s="18">
-        <f>SUM(Q55:Q74)</f>
-        <v/>
-      </c>
-      <c r="R76" s="18">
-        <f>SUM(R55:R74)</f>
-        <v/>
-      </c>
-      <c r="S76" s="18">
-        <f>SUM(S55:S74)</f>
-        <v/>
-      </c>
-      <c r="T76" s="18">
-        <f>SUM(T55:T74)</f>
-        <v/>
-      </c>
-      <c r="U76" s="18">
-        <f>SUM(U55:U74)</f>
-        <v/>
-      </c>
-      <c r="V76" s="18">
-        <f>SUM(V55:V74)</f>
-        <v/>
-      </c>
-      <c r="W76" s="18">
-        <f>SUM(W55:W74)</f>
-        <v/>
-      </c>
-      <c r="X76" s="18">
-        <f>SUM(X55:X74)</f>
-        <v/>
-      </c>
-      <c r="Y76" s="18">
-        <f>SUM(Y55:Y74)</f>
-        <v/>
-      </c>
-      <c r="Z76" s="18">
-        <f>SUM(Z55:Z74)</f>
-        <v/>
-      </c>
-      <c r="AA76" s="18">
-        <f>SUM(AA55:AA74)</f>
-        <v/>
-      </c>
-      <c r="AB76" s="18">
-        <f>SUM(AB55:AB74)</f>
-        <v/>
-      </c>
-      <c r="AC76" s="18">
-        <f>SUM(AC55:AC74)</f>
-        <v/>
-      </c>
-      <c r="AD76" s="18">
-        <f>SUM(AD55:AD74)</f>
-        <v/>
-      </c>
-      <c r="AE76" s="18">
-        <f>SUM(AE55:AE74)</f>
-        <v/>
-      </c>
-      <c r="AF76" s="18">
-        <f>SUM(AF55:AF74)</f>
-        <v/>
-      </c>
-      <c r="AG76" s="18">
-        <f>SUM(AG55:AG74)</f>
-        <v/>
-      </c>
-      <c r="AH76" s="18">
-        <f>SUM(AH55:AH74)</f>
-        <v/>
-      </c>
-      <c r="AI76" s="18">
-        <f>SUM(AI55:AI74)</f>
-        <v/>
-      </c>
-      <c r="AJ76" s="18">
-        <f>SUM(AJ55:AJ74)</f>
-        <v/>
-      </c>
-      <c r="AK76" s="18">
-        <f>SUM(AK55:AK74)</f>
-        <v/>
-      </c>
-      <c r="AL76" s="18">
-        <f>SUM(AL55:AL74)</f>
-        <v/>
-      </c>
-      <c r="AM76" s="18">
-        <f>SUM(AM55:AM74)</f>
-        <v/>
-      </c>
-      <c r="AN76" s="18">
-        <f>SUM(AN55:AN74)</f>
-        <v/>
-      </c>
-      <c r="AO76" s="18">
-        <f>SUM(AO55:AO74)</f>
-        <v/>
-      </c>
-      <c r="AP76" s="18">
-        <f>SUM(AP55:AP74)</f>
-        <v/>
-      </c>
-      <c r="AQ76" s="18">
-        <f>SUM(AQ55:AQ74)</f>
-        <v/>
-      </c>
-      <c r="AR76" s="18">
-        <f>SUM(AR55:AR74)</f>
-        <v/>
-      </c>
-      <c r="AS76" s="18">
-        <f>SUM(AS55:AS74)</f>
-        <v/>
-      </c>
-      <c r="AT76" s="18">
-        <f>SUM(AT55:AT74)</f>
-        <v/>
-      </c>
-      <c r="AU76" s="18">
-        <f>SUM(AU55:AU74)</f>
-        <v/>
-      </c>
-      <c r="AV76" s="18">
-        <f>SUM(AV55:AV74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="E80" s="18">
+        <f>SUM(E57:E78)</f>
+        <v/>
+      </c>
+      <c r="F80" s="18">
+        <f>SUM(F57:F78)</f>
+        <v/>
+      </c>
+      <c r="G80" s="18">
+        <f>SUM(G57:G78)</f>
+        <v/>
+      </c>
+      <c r="H80" s="18">
+        <f>SUM(H57:H78)</f>
+        <v/>
+      </c>
+      <c r="I80" s="18">
+        <f>SUM(I57:I78)</f>
+        <v/>
+      </c>
+      <c r="J80" s="18">
+        <f>SUM(J57:J78)</f>
+        <v/>
+      </c>
+      <c r="K80" s="18">
+        <f>SUM(K57:K78)</f>
+        <v/>
+      </c>
+      <c r="L80" s="18">
+        <f>SUM(L57:L78)</f>
+        <v/>
+      </c>
+      <c r="M80" s="18">
+        <f>SUM(M57:M78)</f>
+        <v/>
+      </c>
+      <c r="N80" s="18">
+        <f>SUM(N57:N78)</f>
+        <v/>
+      </c>
+      <c r="O80" s="18">
+        <f>SUM(O57:O78)</f>
+        <v/>
+      </c>
+      <c r="P80" s="18">
+        <f>SUM(P57:P78)</f>
+        <v/>
+      </c>
+      <c r="Q80" s="18">
+        <f>SUM(Q57:Q78)</f>
+        <v/>
+      </c>
+      <c r="R80" s="18">
+        <f>SUM(R57:R78)</f>
+        <v/>
+      </c>
+      <c r="S80" s="18">
+        <f>SUM(S57:S78)</f>
+        <v/>
+      </c>
+      <c r="T80" s="18">
+        <f>SUM(T57:T78)</f>
+        <v/>
+      </c>
+      <c r="U80" s="18">
+        <f>SUM(U57:U78)</f>
+        <v/>
+      </c>
+      <c r="V80" s="18">
+        <f>SUM(V57:V78)</f>
+        <v/>
+      </c>
+      <c r="W80" s="18">
+        <f>SUM(W57:W78)</f>
+        <v/>
+      </c>
+      <c r="X80" s="18">
+        <f>SUM(X57:X78)</f>
+        <v/>
+      </c>
+      <c r="Y80" s="18">
+        <f>SUM(Y57:Y78)</f>
+        <v/>
+      </c>
+      <c r="Z80" s="18">
+        <f>SUM(Z57:Z78)</f>
+        <v/>
+      </c>
+      <c r="AA80" s="18">
+        <f>SUM(AA57:AA78)</f>
+        <v/>
+      </c>
+      <c r="AB80" s="18">
+        <f>SUM(AB57:AB78)</f>
+        <v/>
+      </c>
+      <c r="AC80" s="18">
+        <f>SUM(AC57:AC78)</f>
+        <v/>
+      </c>
+      <c r="AD80" s="18">
+        <f>SUM(AD57:AD78)</f>
+        <v/>
+      </c>
+      <c r="AE80" s="18">
+        <f>SUM(AE57:AE78)</f>
+        <v/>
+      </c>
+      <c r="AF80" s="18">
+        <f>SUM(AF57:AF78)</f>
+        <v/>
+      </c>
+      <c r="AG80" s="18">
+        <f>SUM(AG57:AG78)</f>
+        <v/>
+      </c>
+      <c r="AH80" s="18">
+        <f>SUM(AH57:AH78)</f>
+        <v/>
+      </c>
+      <c r="AI80" s="18">
+        <f>SUM(AI57:AI78)</f>
+        <v/>
+      </c>
+      <c r="AJ80" s="18">
+        <f>SUM(AJ57:AJ78)</f>
+        <v/>
+      </c>
+      <c r="AK80" s="18">
+        <f>SUM(AK57:AK78)</f>
+        <v/>
+      </c>
+      <c r="AL80" s="18">
+        <f>SUM(AL57:AL78)</f>
+        <v/>
+      </c>
+      <c r="AM80" s="18">
+        <f>SUM(AM57:AM78)</f>
+        <v/>
+      </c>
+      <c r="AN80" s="18">
+        <f>SUM(AN57:AN78)</f>
+        <v/>
+      </c>
+      <c r="AO80" s="18">
+        <f>SUM(AO57:AO78)</f>
+        <v/>
+      </c>
+      <c r="AP80" s="18">
+        <f>SUM(AP57:AP78)</f>
+        <v/>
+      </c>
+      <c r="AQ80" s="18">
+        <f>SUM(AQ57:AQ78)</f>
+        <v/>
+      </c>
+      <c r="AR80" s="18">
+        <f>SUM(AR57:AR78)</f>
+        <v/>
+      </c>
+      <c r="AS80" s="18">
+        <f>SUM(AS57:AS78)</f>
+        <v/>
+      </c>
+      <c r="AT80" s="18">
+        <f>SUM(AT57:AT78)</f>
+        <v/>
+      </c>
+      <c r="AU80" s="18">
+        <f>SUM(AU57:AU78)</f>
+        <v/>
+      </c>
+      <c r="AV80" s="18">
+        <f>SUM(AV57:AV78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t>계약 원장(contracts.json 기반 — counted 아닌 계약 포함)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t>rcp</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>ships</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="D83" s="1" t="inlineStr">
         <is>
           <t>amt_krw_m</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E83" s="1" t="inlineStr">
         <is>
           <t>amt_usd_m</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="F83" s="1" t="inlineStr">
         <is>
           <t>fx_at_sign</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
+      <c r="G83" s="1" t="inlineStr">
         <is>
           <t>signed</t>
         </is>
       </c>
-      <c r="H79" s="1" t="inlineStr">
+      <c r="H83" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="I79" s="1" t="inlineStr">
+      <c r="I83" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="J79" s="1" t="inlineStr">
+      <c r="J83" s="1" t="inlineStr">
         <is>
           <t>cohort</t>
         </is>
       </c>
-      <c r="K79" s="1" t="inlineStr">
+      <c r="K83" s="1" t="inlineStr">
         <is>
           <t>cohort_alt</t>
         </is>
       </c>
-      <c r="L79" s="1" t="inlineStr">
+      <c r="L83" s="1" t="inlineStr">
         <is>
           <t>curve</t>
         </is>
       </c>
-      <c r="M79" s="1" t="inlineStr">
+      <c r="M83" s="1" t="inlineStr">
         <is>
           <t>counted</t>
         </is>
       </c>
-      <c r="N79" s="1" t="inlineStr">
+      <c r="N83" s="1" t="inlineStr">
         <is>
           <t>signed_by_origin</t>
         </is>
       </c>
-      <c r="O79" s="1" t="inlineStr">
+      <c r="O83" s="1" t="inlineStr">
         <is>
           <t>estimated_series</t>
         </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20251121800424</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>VLCC</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>4</v>
-      </c>
-      <c r="D80" t="n">
-        <v>762700</v>
-      </c>
-      <c r="E80" t="n">
-        <v>526.294</v>
-      </c>
-      <c r="F80" t="n">
-        <v>1449.19</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2029-08-13</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>④호황</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M80" t="b">
-        <v>1</v>
-      </c>
-      <c r="N80" t="b">
-        <v>1</v>
-      </c>
-      <c r="O80" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20251124800131</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>6</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1603700</v>
-      </c>
-      <c r="E81" t="n">
-        <v>1106.618</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1449.19</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>③중마진</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M81" t="b">
-        <v>1</v>
-      </c>
-      <c r="N81" t="b">
-        <v>1</v>
-      </c>
-      <c r="O81" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20251124800132</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>CONT</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>2</v>
-      </c>
-      <c r="D82" t="n">
-        <v>534600</v>
-      </c>
-      <c r="E82" t="n">
-        <v>368.896</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1449.19</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2028-07-14</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M82" t="b">
-        <v>0</v>
-      </c>
-      <c r="N82" t="b">
-        <v>1</v>
-      </c>
-      <c r="O82" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20251202800104</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>LNGC</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="n">
-        <v>367200</v>
-      </c>
-      <c r="E83" t="n">
-        <v>253.383</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1449.19</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2028-12-31</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>③중마진</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M83" t="b">
-        <v>1</v>
-      </c>
-      <c r="N83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O83" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20251215800970</t>
+          <t>20251121800424</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLCC</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>140700</v>
+        <v>762700</v>
       </c>
       <c r="E84" t="n">
-        <v>117.843</v>
+        <v>526.294</v>
       </c>
       <c r="F84" t="n">
-        <v>1193.96</v>
+        <v>1449.19</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2019-09-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2029-08-13</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>④호황</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -46732,45 +46837,45 @@
         <v>1</v>
       </c>
       <c r="O84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20251219800421</t>
+          <t>20251124800131</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>1047200</v>
+        <v>1603700</v>
       </c>
       <c r="E85" t="n">
-        <v>769.491</v>
+        <v>1106.618</v>
       </c>
       <c r="F85" t="n">
-        <v>1360.9</v>
+        <v>1449.19</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2029-02-02</t>
+          <t>2029-04-30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -46795,13 +46900,13 @@
         <v>1</v>
       </c>
       <c r="O85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20251219800433</t>
+          <t>20251124800132</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -46810,40 +46915,30 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>689600</v>
+        <v>534600</v>
       </c>
       <c r="E86" t="n">
-        <v>475.852</v>
+        <v>368.896</v>
       </c>
       <c r="F86" t="n">
         <v>1449.19</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2028-11-20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>②BEP</t>
+          <t>2028-07-14</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -46852,7 +46947,7 @@
         </is>
       </c>
       <c r="M86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -46864,39 +46959,49 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20251224800162</t>
+          <t>20251202800104</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>375000</v>
+        <v>367200</v>
       </c>
       <c r="E87" t="n">
-        <v>258.765</v>
+        <v>253.383</v>
       </c>
       <c r="F87" t="n">
         <v>1449.19</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2028-07-31</t>
+          <t>2028-12-31</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -46905,51 +47010,48 @@
         </is>
       </c>
       <c r="M87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
       </c>
       <c r="O87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20251226800855</t>
+          <t>20251215800970</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAVAL</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D88" t="n">
-        <v>844700</v>
+        <v>140700</v>
       </c>
       <c r="E88" t="n">
-        <v>582.877</v>
+        <v>117.843</v>
       </c>
       <c r="F88" t="n">
-        <v>1449.19</v>
+        <v>1193.96</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2019-09-03</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2029-12-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -46958,7 +47060,7 @@
         </is>
       </c>
       <c r="M88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
@@ -46970,7 +47072,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260106800156</t>
+          <t>20251219800421</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -46979,30 +47081,40 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1499300</v>
+        <v>1047200</v>
       </c>
       <c r="E89" t="n">
-        <v>1022.631</v>
+        <v>769.491</v>
       </c>
       <c r="F89" t="n">
-        <v>1466.12</v>
+        <v>1360.9</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2029-03-27</t>
+          <t>2029-02-02</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -47011,51 +47123,51 @@
         </is>
       </c>
       <c r="M89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
       </c>
       <c r="O89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260116800207</t>
+          <t>20251219800433</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>175800</v>
+        <v>689600</v>
       </c>
       <c r="E90" t="n">
-        <v>119.908</v>
+        <v>475.852</v>
       </c>
       <c r="F90" t="n">
-        <v>1466.12</v>
+        <v>1449.19</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2028-05-31</t>
+          <t>2028-11-20</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -47065,7 +47177,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -47080,45 +47192,45 @@
         <v>1</v>
       </c>
       <c r="O90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260120800211</t>
+          <t>20251224800162</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>481600</v>
+        <v>375000</v>
       </c>
       <c r="E91" t="n">
-        <v>328.486</v>
+        <v>258.765</v>
       </c>
       <c r="F91" t="n">
-        <v>1466.12</v>
+        <v>1449.19</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2028-07-31</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -47133,55 +47245,45 @@
         <v>1</v>
       </c>
       <c r="O91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260202800947</t>
+          <t>20251226800855</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>357500</v>
+        <v>844700</v>
       </c>
       <c r="E92" t="n">
-        <v>243.841</v>
+        <v>582.877</v>
       </c>
       <c r="F92" t="n">
-        <v>1466.12</v>
+        <v>1449.19</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-12-20</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -47190,19 +47292,19 @@
         </is>
       </c>
       <c r="M92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="b">
         <v>1</v>
       </c>
       <c r="O92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260226800208</t>
+          <t>20260106800156</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -47211,30 +47313,30 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>367800</v>
+        <v>1499300</v>
       </c>
       <c r="E93" t="n">
-        <v>250.866</v>
+        <v>1022.631</v>
       </c>
       <c r="F93" t="n">
         <v>1466.12</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2029-03-27</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -47255,39 +47357,49 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260227800230</t>
+          <t>20260116800207</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>372400</v>
+        <v>175800</v>
       </c>
       <c r="E94" t="n">
-        <v>254.004</v>
+        <v>119.908</v>
       </c>
       <c r="F94" t="n">
         <v>1466.12</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2028-05-31</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -47296,19 +47408,19 @@
         </is>
       </c>
       <c r="M94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
       </c>
       <c r="O94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260304800002</t>
+          <t>20260120800211</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -47317,40 +47429,30 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>529300</v>
+        <v>481600</v>
       </c>
       <c r="E95" t="n">
-        <v>365.239</v>
+        <v>328.486</v>
       </c>
       <c r="F95" t="n">
-        <v>1449.19</v>
+        <v>1466.12</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-06-30</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -47359,19 +47461,19 @@
         </is>
       </c>
       <c r="M95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
       </c>
       <c r="O95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260305800849</t>
+          <t>20260202800947</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -47380,30 +47482,40 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1487200</v>
+        <v>357500</v>
       </c>
       <c r="E96" t="n">
-        <v>1014.378</v>
+        <v>243.841</v>
       </c>
       <c r="F96" t="n">
         <v>1466.12</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -47412,7 +47524,7 @@
         </is>
       </c>
       <c r="M96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -47424,49 +47536,39 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260306800225</t>
+          <t>20260226800208</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>263200</v>
+        <v>367800</v>
       </c>
       <c r="E97" t="n">
-        <v>179.521</v>
+        <v>250.866</v>
       </c>
       <c r="F97" t="n">
         <v>1466.12</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -47475,61 +47577,51 @@
         </is>
       </c>
       <c r="M97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
       </c>
       <c r="O97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260310800414</t>
+          <t>20260227800230</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>340200</v>
+        <v>372400</v>
       </c>
       <c r="E98" t="n">
-        <v>232.041</v>
+        <v>254.004</v>
       </c>
       <c r="F98" t="n">
         <v>1466.12</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2028-12-29</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -47538,7 +47630,7 @@
         </is>
       </c>
       <c r="M98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
@@ -47550,39 +47642,49 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260316800234</t>
+          <t>20260304800002</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>823700</v>
+        <v>529300</v>
       </c>
       <c r="E99" t="n">
-        <v>561.823</v>
+        <v>365.239</v>
       </c>
       <c r="F99" t="n">
-        <v>1466.12</v>
+        <v>1449.19</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -47591,7 +47693,7 @@
         </is>
       </c>
       <c r="M99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -47603,49 +47705,39 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260403800582</t>
+          <t>20260305800849</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>349800</v>
+        <v>1487200</v>
       </c>
       <c r="E100" t="n">
-        <v>232.928</v>
+        <v>1014.378</v>
       </c>
       <c r="F100" t="n">
-        <v>1501.75</v>
+        <v>1466.12</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2029-03-30</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -47654,46 +47746,46 @@
         </is>
       </c>
       <c r="M100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
       </c>
       <c r="O100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260403800587</t>
+          <t>20260306800225</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>611700</v>
+        <v>263200</v>
       </c>
       <c r="E101" t="n">
-        <v>407.325</v>
+        <v>179.521</v>
       </c>
       <c r="F101" t="n">
-        <v>1501.75</v>
+        <v>1466.12</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -47701,57 +47793,67 @@
           <t>2029-05-31</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>③중마진</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>linear_progress</t>
         </is>
       </c>
       <c r="M101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
       </c>
       <c r="O101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20260408800703</t>
+          <t>20260310800414</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>770200</v>
+        <v>340200</v>
       </c>
       <c r="E102" t="n">
-        <v>512.8680000000001</v>
+        <v>232.041</v>
       </c>
       <c r="F102" t="n">
-        <v>1501.75</v>
+        <v>1466.12</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2028-12-29</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -47782,49 +47884,39 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20260416800167</t>
+          <t>20260316800234</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D103" t="n">
-        <v>346600</v>
+        <v>823700</v>
       </c>
       <c r="E103" t="n">
-        <v>230.797</v>
+        <v>561.823</v>
       </c>
       <c r="F103" t="n">
-        <v>1501.75</v>
+        <v>1466.12</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -47833,7 +47925,7 @@
         </is>
       </c>
       <c r="M103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -47845,7 +47937,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20260417800196</t>
+          <t>20260403800582</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -47854,30 +47946,40 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>674700</v>
+        <v>349800</v>
       </c>
       <c r="E104" t="n">
-        <v>449.276</v>
+        <v>232.928</v>
       </c>
       <c r="F104" t="n">
         <v>1501.75</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2029-03-30</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -47886,51 +47988,51 @@
         </is>
       </c>
       <c r="M104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="b">
         <v>1</v>
       </c>
       <c r="O104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20260422800051</t>
+          <t>20260403800587</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NAVAL</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
-        <v>514800</v>
+        <v>611700</v>
       </c>
       <c r="E105" t="n">
-        <v>342.8</v>
+        <v>407.325</v>
       </c>
       <c r="F105" t="n">
         <v>1501.75</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -47945,42 +48047,55 @@
         <v>1</v>
       </c>
       <c r="O105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20260422800184</t>
+          <t>20260408800703</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>LNGC</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>627100</v>
+        <v>770200</v>
       </c>
       <c r="E106" t="n">
-        <v>417.579</v>
+        <v>512.8680000000001</v>
       </c>
       <c r="F106" t="n">
         <v>1501.75</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2030-10-21</t>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -47989,19 +48104,19 @@
         </is>
       </c>
       <c r="M106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
       </c>
       <c r="O106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20260504800307</t>
+          <t>20260416800167</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -48010,30 +48125,40 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>504800</v>
+        <v>346600</v>
       </c>
       <c r="E107" t="n">
-        <v>336.141</v>
+        <v>230.797</v>
       </c>
       <c r="F107" t="n">
         <v>1501.75</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2029-04-30</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -48042,51 +48167,51 @@
         </is>
       </c>
       <c r="M107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
       </c>
       <c r="O107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20260508800186</t>
+          <t>20260417800196</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>1778700</v>
+        <v>674700</v>
       </c>
       <c r="E108" t="n">
-        <v>1184.418</v>
+        <v>449.276</v>
       </c>
       <c r="F108" t="n">
         <v>1501.75</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -48107,49 +48232,39 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20260513800195</t>
+          <t>20260422800051</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>748500</v>
+        <v>514800</v>
       </c>
       <c r="E109" t="n">
-        <v>498.419</v>
+        <v>342.8</v>
       </c>
       <c r="F109" t="n">
         <v>1501.75</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2029-07-23</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -48158,7 +48273,7 @@
         </is>
       </c>
       <c r="M109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -48170,39 +48285,36 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>20260514800347</t>
+          <t>20260422800184</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LNGC</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>2</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D110" t="n">
-        <v>743900</v>
+        <v>627100</v>
       </c>
       <c r="E110" t="n">
-        <v>495.355</v>
+        <v>417.579</v>
       </c>
       <c r="F110" t="n">
         <v>1501.75</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2029-03-30</t>
+          <t>2030-10-21</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -48217,13 +48329,13 @@
         <v>1</v>
       </c>
       <c r="O110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>20260521800360</t>
+          <t>20260504800307</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48232,40 +48344,30 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>1078200</v>
+        <v>504800</v>
       </c>
       <c r="E111" t="n">
-        <v>717.962</v>
+        <v>336.141</v>
       </c>
       <c r="F111" t="n">
         <v>1501.75</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2029-12-20</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -48274,51 +48376,51 @@
         </is>
       </c>
       <c r="M111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
       </c>
       <c r="O111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>20260601800400</t>
+          <t>20260508800186</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>1416100</v>
+        <v>1778700</v>
       </c>
       <c r="E112" t="n">
-        <v>942.967</v>
+        <v>1184.418</v>
       </c>
       <c r="F112" t="n">
         <v>1501.75</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2030-06-30</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -48339,39 +48441,39 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>20260629800351</t>
+          <t>20260513800195</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>366000</v>
+        <v>748500</v>
       </c>
       <c r="E113" t="n">
-        <v>243.716</v>
+        <v>498.419</v>
       </c>
       <c r="F113" t="n">
         <v>1501.75</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2029-12-31</t>
+          <t>2029-07-23</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -48402,7 +48504,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20260701800239</t>
+          <t>20260514800347</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -48411,30 +48513,30 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>492800</v>
+        <v>743900</v>
       </c>
       <c r="E114" t="n">
-        <v>328.15</v>
+        <v>495.355</v>
       </c>
       <c r="F114" t="n">
         <v>1501.75</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
+          <t>2029-03-30</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -48449,45 +48551,55 @@
         <v>1</v>
       </c>
       <c r="O114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20260709800139</t>
+          <t>20260521800360</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>6</v>
       </c>
       <c r="D115" t="n">
-        <v>469900</v>
+        <v>1078200</v>
       </c>
       <c r="E115" t="n">
-        <v>331.207</v>
+        <v>717.962</v>
       </c>
       <c r="F115" t="n">
-        <v>1418.75</v>
+        <v>1501.75</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2029-12-20</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -48496,10 +48608,10 @@
         </is>
       </c>
       <c r="M115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="b">
         <v>1</v>
@@ -48508,7 +48620,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>20260713800202</t>
+          <t>20260601800400</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -48517,40 +48629,30 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>545600</v>
+        <v>1416100</v>
       </c>
       <c r="E116" t="n">
-        <v>384.564</v>
+        <v>942.967</v>
       </c>
       <c r="F116" t="n">
-        <v>1418.75</v>
+        <v>1501.75</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2030-05-31</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>⑤초호황</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>④호황</t>
+          <t>2030-06-30</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -48559,10 +48661,10 @@
         </is>
       </c>
       <c r="M116" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
         <v>1</v>
-      </c>
-      <c r="N116" t="b">
-        <v>0</v>
       </c>
       <c r="O116" t="b">
         <v>1</v>
@@ -48571,36 +48673,49 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20260810800150</t>
+          <t>20260629800351</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>956000</v>
+        <v>366000</v>
       </c>
       <c r="E117" t="n">
-        <v>673.833</v>
+        <v>243.716</v>
       </c>
       <c r="F117" t="n">
-        <v>1418.75</v>
+        <v>1501.75</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2030-07-30</t>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -48609,10 +48724,10 @@
         </is>
       </c>
       <c r="M117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="b">
         <v>0</v>
@@ -48621,39 +48736,39 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>20260824800125</t>
+          <t>20260701800239</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>515400</v>
+        <v>492800</v>
       </c>
       <c r="E118" t="n">
-        <v>363.278</v>
+        <v>328.15</v>
       </c>
       <c r="F118" t="n">
-        <v>1418.75</v>
+        <v>1501.75</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2030-03-31</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -48665,108 +48780,111 @@
         <v>0</v>
       </c>
       <c r="N118" t="b">
+        <v>1</v>
+      </c>
+      <c r="O118" t="b">
         <v>0</v>
-      </c>
-      <c r="O118" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20260903800523</t>
+          <t>20260709800139</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>OFFSH</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C119" t="n">
+        <v>6</v>
+      </c>
+      <c r="D119" t="n">
+        <v>469900</v>
+      </c>
+      <c r="E119" t="n">
+        <v>331.207</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1418.75</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2029-06-30</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M119" t="b">
+        <v>0</v>
+      </c>
+      <c r="N119" t="b">
+        <v>0</v>
+      </c>
+      <c r="O119" t="b">
         <v>1</v>
-      </c>
-      <c r="D119" t="n">
-        <v>878100</v>
-      </c>
-      <c r="E119" t="n">
-        <v>783.039</v>
-      </c>
-      <c r="F119" t="n">
-        <v>1121.4</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>2021-05-08</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>④호황</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>②BEP</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="M119" t="b">
-        <v>1</v>
-      </c>
-      <c r="N119" t="b">
-        <v>1</v>
-      </c>
-      <c r="O119" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20261006800410</t>
+          <t>20260713800202</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>338500</v>
+        <v>545600</v>
       </c>
       <c r="E120" t="n">
-        <v>291.833</v>
+        <v>384.564</v>
       </c>
       <c r="F120" t="n">
-        <v>1159.91</v>
+        <v>1418.75</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2021-09-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2030-05-31</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>④호황</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -48778,48 +48896,45 @@
         <v>1</v>
       </c>
       <c r="N120" t="b">
+        <v>0</v>
+      </c>
+      <c r="O120" t="b">
         <v>1</v>
-      </c>
-      <c r="O120" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>20261013800237</t>
+          <t>20260810800150</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OFFSH</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>1</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D121" t="n">
-        <v>1964800</v>
+        <v>956000</v>
       </c>
       <c r="E121" t="n">
-        <v>1493.361</v>
+        <v>673.833</v>
       </c>
       <c r="F121" t="n">
-        <v>1315.69</v>
+        <v>1418.75</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2030-07-30</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -48831,7 +48946,7 @@
         <v>0</v>
       </c>
       <c r="N121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" t="b">
         <v>0</v>
@@ -48840,7 +48955,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20261015800358</t>
+          <t>20260824800125</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -48852,27 +48967,27 @@
         <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>625800</v>
+        <v>515400</v>
       </c>
       <c r="E122" t="n">
-        <v>466.281</v>
+        <v>363.278</v>
       </c>
       <c r="F122" t="n">
-        <v>1342.11</v>
+        <v>1418.75</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2030-06-30</t>
+          <t>2030-03-31</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -48891,49 +49006,447 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260903800523</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>878100</v>
+      </c>
+      <c r="E123" t="n">
+        <v>783.039</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1121.4</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2021-05-08</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>④호황</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>②BEP</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M123" t="b">
+        <v>1</v>
+      </c>
+      <c r="N123" t="b">
+        <v>1</v>
+      </c>
+      <c r="O123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20261006800410</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>338500</v>
+      </c>
+      <c r="E124" t="n">
+        <v>291.833</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1159.91</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2027-08-31</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M124" t="b">
+        <v>1</v>
+      </c>
+      <c r="N124" t="b">
+        <v>1</v>
+      </c>
+      <c r="O124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20261013800237</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OFFSH</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1964800</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1493.361</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1315.69</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2027-06-01</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
+        <v>1</v>
+      </c>
+      <c r="O125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20261015800358</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4</v>
+      </c>
+      <c r="D126" t="n">
+        <v>625800</v>
+      </c>
+      <c r="E126" t="n">
+        <v>467.891</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1337.49</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2030-06-30</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
+        <v>0</v>
+      </c>
+      <c r="O126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20261020800226</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>6</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1439700</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1076.419</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1337.49</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>④호황</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M127" t="b">
+        <v>1</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
+      </c>
+      <c r="O127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20261020800229</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>479900</v>
+      </c>
+      <c r="E128" t="n">
+        <v>358.806</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1337.49</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="b">
+        <v>0</v>
+      </c>
+      <c r="O128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20261021800379</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="n">
+        <v>317600</v>
+      </c>
+      <c r="E129" t="n">
+        <v>227.458</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1396.3</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>②BEP</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="M129" t="b">
+        <v>1</v>
+      </c>
+      <c r="N129" t="b">
+        <v>1</v>
+      </c>
+      <c r="O129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 23건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>⚠ HD한국조선해양과 HD현대重 동일 계약 24건 — shared_owner=329180 로 표시하고 이 파일의 합계에서 제외(합산 금지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → HEDGE 70% 가정(레퍼런스 SLS 시트 HEDGE 행은 미포 65%·삼성重 100% — 그 사이에 둔 설정값). hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 7%, ③중마진 80%, ④호황 13%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 6%, ③중마진 70%, ④호황 24%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>⚠ 종료일 '-' 1건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>⚠ 정기보고서 부문 매출(3개월분)을 만들 수 없어 화해 없음</t>
         </is>
@@ -49211,32 +49724,32 @@
         <v/>
       </c>
       <c r="H6" s="34" t="n">
-        <v>3980.69</v>
+        <v>3839.71</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>8885.68</v>
+        <v>8497.690000000001</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>15409.2</v>
+        <v>14826.67</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>23032.36</v>
+        <v>22307.74</v>
       </c>
       <c r="L6" s="20">
         <f>SUM(H6:K6)</f>
         <v/>
       </c>
       <c r="M6" s="34" t="n">
-        <v>31236.27</v>
+        <v>30422</v>
       </c>
       <c r="N6" s="34" t="n">
-        <v>39502</v>
+        <v>38650.54</v>
       </c>
       <c r="O6" s="34" t="n">
-        <v>47310.68</v>
+        <v>46474.49</v>
       </c>
       <c r="P6" s="34" t="n">
-        <v>54143.41</v>
+        <v>53374.93</v>
       </c>
       <c r="Q6" s="20">
         <f>SUM(M6:P6)</f>
@@ -49823,32 +50336,32 @@
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>2511.31</v>
+        <v>2369.97</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>5799.41</v>
+        <v>5410.42</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>10312.57</v>
+        <v>9728.549999999999</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>15677.23</v>
+        <v>14950.77</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
-        <v>21519.73</v>
+        <v>20703.45</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>27466.5</v>
+        <v>26612.99</v>
       </c>
       <c r="O18" s="34" t="n">
-        <v>33143.91</v>
+        <v>32305.77</v>
       </c>
       <c r="P18" s="34" t="n">
-        <v>38178.36</v>
+        <v>37408.19</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -50129,32 +50642,32 @@
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>6817.34</v>
+        <v>6676.79</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>14845.59</v>
+        <v>14458.77</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>25254.28</v>
+        <v>24673.42</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>37244.33</v>
+        <v>36521.69</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>50016.68</v>
+        <v>49204.52</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>62772.29</v>
+        <v>61922.83</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>74712.07000000001</v>
+        <v>73877.57000000001</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>85036.96000000001</v>
+        <v>84269.66</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -50605,7 +51118,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -55866,7 +56379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
